--- a/Data/FlightPlan/FPL_29OCT26.xlsx
+++ b/Data/FlightPlan/FPL_29OCT26.xlsx
@@ -185,18 +185,303 @@
     <t>VN-A521</t>
   </si>
   <si>
+    <t>SIN</t>
+  </si>
+  <si>
+    <t>06:50</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>11:15</t>
+  </si>
+  <si>
+    <t>12:25</t>
+  </si>
+  <si>
+    <t>BKK</t>
+  </si>
+  <si>
+    <t>13:25</t>
+  </si>
+  <si>
+    <t>14:55</t>
+  </si>
+  <si>
+    <t>16:05</t>
+  </si>
+  <si>
+    <t>17:35</t>
+  </si>
+  <si>
+    <t>DAD</t>
+  </si>
+  <si>
+    <t>18:30</t>
+  </si>
+  <si>
+    <t>19:50</t>
+  </si>
+  <si>
+    <t>21:45</t>
+  </si>
+  <si>
+    <t>22:15</t>
+  </si>
+  <si>
+    <t>00:25</t>
+  </si>
+  <si>
+    <t>07:50</t>
+  </si>
+  <si>
+    <t>VN-A523</t>
+  </si>
+  <si>
+    <t>NRT</t>
+  </si>
+  <si>
+    <t>08:55</t>
+  </si>
+  <si>
+    <t>13:55</t>
+  </si>
+  <si>
     <t>VII</t>
   </si>
   <si>
+    <t>16:45</t>
+  </si>
+  <si>
+    <t>17:15</t>
+  </si>
+  <si>
+    <t>19:05</t>
+  </si>
+  <si>
+    <t>19:45</t>
+  </si>
+  <si>
+    <t>21:55</t>
+  </si>
+  <si>
+    <t>22:25</t>
+  </si>
+  <si>
+    <t>00:35</t>
+  </si>
+  <si>
+    <t>VN-A524</t>
+  </si>
+  <si>
+    <t>09:15</t>
+  </si>
+  <si>
+    <t>10:45</t>
+  </si>
+  <si>
+    <t>11:45</t>
+  </si>
+  <si>
+    <t>13:10</t>
+  </si>
+  <si>
+    <t>14:25</t>
+  </si>
+  <si>
+    <t>15:45</t>
+  </si>
+  <si>
+    <t>16:15</t>
+  </si>
+  <si>
+    <t>17:40</t>
+  </si>
+  <si>
+    <t>AMD</t>
+  </si>
+  <si>
+    <t>18:50</t>
+  </si>
+  <si>
+    <t>22:50</t>
+  </si>
+  <si>
+    <t>23:50</t>
+  </si>
+  <si>
+    <t>VN-A526</t>
+  </si>
+  <si>
+    <t>KHH</t>
+  </si>
+  <si>
+    <t>12:45</t>
+  </si>
+  <si>
+    <t>PXU</t>
+  </si>
+  <si>
+    <t>15:55</t>
+  </si>
+  <si>
+    <t>17:05</t>
+  </si>
+  <si>
+    <t>18:45</t>
+  </si>
+  <si>
+    <t>01:20</t>
+  </si>
+  <si>
+    <t>08:30</t>
+  </si>
+  <si>
+    <t>VN-A528</t>
+  </si>
+  <si>
+    <t>THD</t>
+  </si>
+  <si>
+    <t>06:35</t>
+  </si>
+  <si>
+    <t>08:35</t>
+  </si>
+  <si>
+    <t>09:05</t>
+  </si>
+  <si>
+    <t>12:00</t>
+  </si>
+  <si>
+    <t>13:40</t>
+  </si>
+  <si>
+    <t>14:50</t>
+  </si>
+  <si>
+    <t>16:30</t>
+  </si>
+  <si>
+    <t>17:50</t>
+  </si>
+  <si>
+    <t>18:20</t>
+  </si>
+  <si>
+    <t>19:25</t>
+  </si>
+  <si>
+    <t>19:55</t>
+  </si>
+  <si>
+    <t>VN-A529</t>
+  </si>
+  <si>
+    <t>04:05</t>
+  </si>
+  <si>
+    <t>08:25</t>
+  </si>
+  <si>
+    <t>HPH</t>
+  </si>
+  <si>
+    <t>11:00</t>
+  </si>
+  <si>
+    <t>15:30</t>
+  </si>
+  <si>
+    <t>BOM</t>
+  </si>
+  <si>
+    <t>18:55</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>00:10</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>14:30</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
     <t>07:10</t>
   </si>
   <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
     <t>10:55</t>
   </si>
   <si>
@@ -209,285 +494,6 @@
     <t>15:15</t>
   </si>
   <si>
-    <t>17:05</t>
-  </si>
-  <si>
-    <t>DAD</t>
-  </si>
-  <si>
-    <t>18:30</t>
-  </si>
-  <si>
-    <t>19:50</t>
-  </si>
-  <si>
-    <t>21:45</t>
-  </si>
-  <si>
-    <t>22:15</t>
-  </si>
-  <si>
-    <t>00:25</t>
-  </si>
-  <si>
-    <t>07:50</t>
-  </si>
-  <si>
-    <t>VN-A523</t>
-  </si>
-  <si>
-    <t>NRT</t>
-  </si>
-  <si>
-    <t>08:55</t>
-  </si>
-  <si>
-    <t>13:55</t>
-  </si>
-  <si>
-    <t>14:55</t>
-  </si>
-  <si>
-    <t>16:45</t>
-  </si>
-  <si>
-    <t>17:15</t>
-  </si>
-  <si>
-    <t>19:05</t>
-  </si>
-  <si>
-    <t>19:45</t>
-  </si>
-  <si>
-    <t>21:55</t>
-  </si>
-  <si>
-    <t>22:25</t>
-  </si>
-  <si>
-    <t>00:35</t>
-  </si>
-  <si>
-    <t>VN-A524</t>
-  </si>
-  <si>
-    <t>BKK</t>
-  </si>
-  <si>
-    <t>09:15</t>
-  </si>
-  <si>
-    <t>10:45</t>
-  </si>
-  <si>
-    <t>11:45</t>
-  </si>
-  <si>
-    <t>13:10</t>
-  </si>
-  <si>
-    <t>14:25</t>
-  </si>
-  <si>
-    <t>15:45</t>
-  </si>
-  <si>
-    <t>16:15</t>
-  </si>
-  <si>
-    <t>17:40</t>
-  </si>
-  <si>
-    <t>AMD</t>
-  </si>
-  <si>
-    <t>18:50</t>
-  </si>
-  <si>
-    <t>22:50</t>
-  </si>
-  <si>
-    <t>23:50</t>
-  </si>
-  <si>
-    <t>VN-A526</t>
-  </si>
-  <si>
-    <t>KHH</t>
-  </si>
-  <si>
-    <t>12:45</t>
-  </si>
-  <si>
-    <t>PXU</t>
-  </si>
-  <si>
-    <t>15:55</t>
-  </si>
-  <si>
-    <t>17:35</t>
-  </si>
-  <si>
-    <t>18:45</t>
-  </si>
-  <si>
-    <t>01:20</t>
-  </si>
-  <si>
-    <t>08:30</t>
-  </si>
-  <si>
-    <t>VN-A528</t>
-  </si>
-  <si>
-    <t>THD</t>
-  </si>
-  <si>
-    <t>06:35</t>
-  </si>
-  <si>
-    <t>08:35</t>
-  </si>
-  <si>
-    <t>09:05</t>
-  </si>
-  <si>
-    <t>12:00</t>
-  </si>
-  <si>
-    <t>13:40</t>
-  </si>
-  <si>
-    <t>14:50</t>
-  </si>
-  <si>
-    <t>16:30</t>
-  </si>
-  <si>
-    <t>17:50</t>
-  </si>
-  <si>
-    <t>18:20</t>
-  </si>
-  <si>
-    <t>19:25</t>
-  </si>
-  <si>
-    <t>19:55</t>
-  </si>
-  <si>
-    <t>VN-A529</t>
-  </si>
-  <si>
-    <t>04:05</t>
-  </si>
-  <si>
-    <t>08:25</t>
-  </si>
-  <si>
-    <t>HPH</t>
-  </si>
-  <si>
-    <t>11:00</t>
-  </si>
-  <si>
-    <t>15:30</t>
-  </si>
-  <si>
-    <t>BOM</t>
-  </si>
-  <si>
-    <t>18:55</t>
-  </si>
-  <si>
-    <t>23:10</t>
-  </si>
-  <si>
-    <t>00:10</t>
-  </si>
-  <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>12:25</t>
-  </si>
-  <si>
-    <t>14:30</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>SIN</t>
-  </si>
-  <si>
-    <t>06:50</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>11:15</t>
-  </si>
-  <si>
-    <t>13:25</t>
-  </si>
-  <si>
-    <t>16:05</t>
-  </si>
-  <si>
     <t>HYD</t>
   </si>
   <si>
@@ -503,6 +509,36 @@
     <t>05:40</t>
   </si>
   <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
     <t>VN-A542</t>
   </si>
   <si>
@@ -527,9 +563,6 @@
     <t>08:15</t>
   </si>
   <si>
-    <t>08:45</t>
-  </si>
-  <si>
     <t>10:10</t>
   </si>
   <si>
@@ -542,9 +575,6 @@
     <t>15:10</t>
   </si>
   <si>
-    <t>17:55</t>
-  </si>
-  <si>
     <t>20:25</t>
   </si>
   <si>
@@ -632,18 +662,9 @@
     <t>08:50</t>
   </si>
   <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
     <t>20:00</t>
   </si>
   <si>
-    <t>22:30</t>
-  </si>
-  <si>
     <t>KHV</t>
   </si>
   <si>
@@ -728,9 +749,6 @@
     <t>UIH</t>
   </si>
   <si>
-    <t>10:00</t>
-  </si>
-  <si>
     <t>13:35</t>
   </si>
   <si>
@@ -767,9 +785,6 @@
     <t>14:10</t>
   </si>
   <si>
-    <t>15:00</t>
-  </si>
-  <si>
     <t>17:10</t>
   </si>
   <si>
@@ -809,16 +824,10 @@
     <t>VN-A639</t>
   </si>
   <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>23:25</t>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>20:15</t>
   </si>
   <si>
     <t>VN-A640</t>
@@ -905,9 +914,6 @@
     <t>VN-A648</t>
   </si>
   <si>
-    <t>20:15</t>
-  </si>
-  <si>
     <t>VN-A649</t>
   </si>
   <si>
@@ -941,12 +947,6 @@
     <t>02:30</t>
   </si>
   <si>
-    <t>VN-A655</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
     <t>VN-A657</t>
   </si>
   <si>
@@ -1208,7 +1208,7 @@
     <t>Total Record(s): 348</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 28, 2026 22:14</t>
+    <t xml:space="preserve">Generated on  Oct 29, 2026 01:42</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2330,7 +2330,7 @@
         <v>13</v>
       </c>
       <c r="B26" s="7">
-        <v>218</v>
+        <v>813</v>
       </c>
       <c t="s" r="C26" s="7">
         <v>14</v>
@@ -2363,7 +2363,7 @@
         <v>13</v>
       </c>
       <c r="B27" s="7">
-        <v>741</v>
+        <v>814</v>
       </c>
       <c t="s" r="C27" s="7">
         <v>14</v>
@@ -2379,10 +2379,10 @@
         <v>58</v>
       </c>
       <c t="s" r="H27" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I27" s="7">
         <v>61</v>
-      </c>
-      <c t="s" r="I27" s="7">
-        <v>30</v>
       </c>
       <c t="s" r="J27" s="7">
         <v>62</v>
@@ -2396,7 +2396,7 @@
         <v>13</v>
       </c>
       <c r="B28" s="7">
-        <v>740</v>
+        <v>807</v>
       </c>
       <c t="s" r="C28" s="7">
         <v>14</v>
@@ -2409,16 +2409,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G28" s="8">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c t="s" r="H28" s="8">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
@@ -2429,7 +2429,7 @@
         <v>13</v>
       </c>
       <c r="B29" s="7">
-        <v>217</v>
+        <v>800</v>
       </c>
       <c t="s" r="C29" s="7">
         <v>14</v>
@@ -2442,16 +2442,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c t="s" r="H29" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2478,13 +2478,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2508,7 +2508,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H31" s="8">
         <v>25</v>
@@ -2517,7 +2517,7 @@
         <v>27</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2547,10 +2547,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2583,7 +2583,7 @@
         <v>35</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2616,22 +2616,22 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
@@ -2649,7 +2649,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -2658,13 +2658,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H36" s="8">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -2682,22 +2682,22 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c t="s" r="H37" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -2715,7 +2715,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -2727,10 +2727,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -2748,7 +2748,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -2760,10 +2760,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -2805,7 +2805,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c t="s" r="I41" s="7">
         <v>88</v>
@@ -2829,13 +2829,13 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>25</v>
@@ -2862,7 +2862,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -2871,7 +2871,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I43" s="7">
         <v>92</v>
@@ -2895,13 +2895,13 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>25</v>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -2961,7 +2961,7 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
@@ -3057,7 +3057,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
@@ -3090,7 +3090,7 @@
         <v>104</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>66</v>
+        <v>105</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3120,7 +3120,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>105</v>
+        <v>67</v>
       </c>
       <c t="s" r="J51" s="7">
         <v>106</v>
@@ -3330,7 +3330,7 @@
         <v>25</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I58" s="7">
         <v>117</v>
@@ -3360,7 +3360,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H59" s="8">
         <v>46</v>
@@ -3396,7 +3396,7 @@
         <v>46</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I60" s="7">
         <v>121</v>
@@ -3696,7 +3696,7 @@
         <v>136</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
@@ -3726,10 +3726,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
@@ -3759,7 +3759,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c t="s" r="J72" s="7">
         <v>140</v>
@@ -3911,9 +3911,13 @@
       <c t="s" r="J77" s="7">
         <v>147</v>
       </c>
-      <c r="K77" s="7"/>
+      <c t="s" r="K77" s="7">
+        <v>148</v>
+      </c>
       <c r="L77" s="7"/>
-      <c r="M77" s="7"/>
+      <c t="s" r="M77" s="7">
+        <v>149</v>
+      </c>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c t="s" r="A78" s="6">
@@ -3936,13 +3940,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H78" s="8">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c t="s" r="I78" s="7">
         <v>141</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -3966,16 +3970,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c t="s" r="H79" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I79" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4008,7 +4012,7 @@
         <v>26</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
@@ -4038,10 +4042,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I81" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c t="s" r="J81" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
@@ -4067,14 +4071,14 @@
         <v>13</v>
       </c>
       <c r="B83" s="7">
-        <v>813</v>
+        <v>218</v>
       </c>
       <c t="s" r="C83" s="7">
         <v>14</v>
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
@@ -4083,13 +4087,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>155</v>
+        <v>137</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
@@ -4100,29 +4104,29 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>814</v>
+        <v>741</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>156</v>
+        <v>30</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="K84" s="7"/>
       <c r="L84" s="7"/>
@@ -4133,29 +4137,29 @@
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>807</v>
+        <v>740</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>78</v>
+        <v>159</v>
       </c>
       <c r="K85" s="7"/>
       <c r="L85" s="7"/>
@@ -4166,26 +4170,26 @@
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>800</v>
+        <v>217</v>
       </c>
       <c t="s" r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c t="s" r="H86" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c t="s" r="J86" s="7">
         <v>105</v>
@@ -4206,7 +4210,7 @@
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
@@ -4215,13 +4219,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4239,22 +4243,22 @@
       </c>
       <c r="D88" s="7"/>
       <c t="s" r="E88" s="7">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="F88" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G88" s="8">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c t="s" r="H88" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I88" s="7">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4280,29 +4284,29 @@
         <v>13</v>
       </c>
       <c r="B90" s="7">
-        <v>939</v>
+        <v>637</v>
       </c>
       <c t="s" r="C90" s="7">
         <v>14</v>
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
@@ -4313,29 +4317,29 @@
         <v>13</v>
       </c>
       <c r="B91" s="7">
-        <v>443</v>
+        <v>310</v>
       </c>
       <c t="s" r="C91" s="7">
         <v>14</v>
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c t="s" r="I91" s="7">
-        <v>95</v>
+        <v>169</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>82</v>
+        <v>158</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4346,45 +4350,63 @@
         <v>13</v>
       </c>
       <c r="B92" s="7">
-        <v>968</v>
+        <v>309</v>
       </c>
       <c t="s" r="C92" s="7">
         <v>14</v>
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>17</v>
+        <v>133</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>16</v>
+        <v>25</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>167</v>
+        <v>21</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
       <c r="M92" s="7"/>
     </row>
     <row r="93" ht="14.25" customHeight="1">
-      <c r="A93" s="6"/>
-      <c r="B93" s="7"/>
-      <c r="C93" s="7"/>
+      <c t="s" r="A93" s="6">
+        <v>13</v>
+      </c>
+      <c r="B93" s="7">
+        <v>306</v>
+      </c>
+      <c t="s" r="C93" s="7">
+        <v>14</v>
+      </c>
       <c r="D93" s="7"/>
-      <c r="E93" s="7"/>
-      <c r="F93" s="7"/>
-      <c r="G93" s="8"/>
-      <c r="H93" s="8"/>
-      <c r="I93" s="7"/>
-      <c r="J93" s="7"/>
+      <c t="s" r="E93" s="7">
+        <v>166</v>
+      </c>
+      <c r="F93" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G93" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H93" s="8">
+        <v>133</v>
+      </c>
+      <c t="s" r="I93" s="7">
+        <v>171</v>
+      </c>
+      <c t="s" r="J93" s="7">
+        <v>127</v>
+      </c>
       <c r="K93" s="7"/>
       <c r="L93" s="7"/>
       <c r="M93" s="7"/>
@@ -4394,29 +4416,29 @@
         <v>13</v>
       </c>
       <c r="B94" s="7">
-        <v>626</v>
+        <v>305</v>
       </c>
       <c t="s" r="C94" s="7">
         <v>14</v>
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c t="s" r="H94" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>170</v>
+        <v>141</v>
       </c>
       <c t="s" r="J94" s="7">
-        <v>171</v>
+        <v>33</v>
       </c>
       <c r="K94" s="7"/>
       <c r="L94" s="7"/>
@@ -4427,29 +4449,29 @@
         <v>13</v>
       </c>
       <c r="B95" s="7">
-        <v>627</v>
+        <v>244</v>
       </c>
       <c t="s" r="C95" s="7">
         <v>14</v>
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G95" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="H95" s="8">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c t="s" r="I95" s="7">
         <v>172</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>173</v>
+        <v>121</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4460,29 +4482,29 @@
         <v>13</v>
       </c>
       <c r="B96" s="7">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c t="s" r="C96" s="7">
         <v>14</v>
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G96" s="8">
-        <v>25</v>
+        <v>110</v>
       </c>
       <c t="s" r="H96" s="8">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c t="s" r="I96" s="7">
+        <v>173</v>
+      </c>
+      <c t="s" r="J96" s="7">
         <v>174</v>
-      </c>
-      <c t="s" r="J96" s="7">
-        <v>175</v>
       </c>
       <c r="K96" s="7"/>
       <c r="L96" s="7"/>
@@ -4493,63 +4515,45 @@
         <v>13</v>
       </c>
       <c r="B97" s="7">
-        <v>243</v>
+        <v>132</v>
       </c>
       <c t="s" r="C97" s="7">
         <v>14</v>
       </c>
       <c r="D97" s="7"/>
       <c t="s" r="E97" s="7">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="F97" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G97" s="8">
-        <v>110</v>
+        <v>25</v>
       </c>
       <c t="s" r="H97" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I97" s="7">
-        <v>91</v>
+        <v>175</v>
       </c>
       <c t="s" r="J97" s="7">
-        <v>176</v>
+        <v>52</v>
       </c>
       <c r="K97" s="7"/>
       <c r="L97" s="7"/>
       <c r="M97" s="7"/>
     </row>
     <row r="98" ht="14.25" customHeight="1">
-      <c t="s" r="A98" s="6">
-        <v>13</v>
-      </c>
-      <c r="B98" s="7">
-        <v>254</v>
-      </c>
-      <c t="s" r="C98" s="7">
-        <v>14</v>
-      </c>
+      <c r="A98" s="6"/>
+      <c r="B98" s="7"/>
+      <c r="C98" s="7"/>
       <c r="D98" s="7"/>
-      <c t="s" r="E98" s="7">
-        <v>169</v>
-      </c>
-      <c r="F98" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G98" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H98" s="8">
-        <v>110</v>
-      </c>
-      <c t="s" r="I98" s="7">
-        <v>104</v>
-      </c>
-      <c t="s" r="J98" s="7">
-        <v>177</v>
-      </c>
+      <c r="E98" s="7"/>
+      <c r="F98" s="7"/>
+      <c r="G98" s="8"/>
+      <c r="H98" s="8"/>
+      <c r="I98" s="7"/>
+      <c r="J98" s="7"/>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c r="M98" s="7"/>
@@ -4559,26 +4563,26 @@
         <v>13</v>
       </c>
       <c r="B99" s="7">
-        <v>255</v>
+        <v>939</v>
       </c>
       <c t="s" r="C99" s="7">
         <v>14</v>
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G99" s="8">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c t="s" r="H99" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>24</v>
+        <v>177</v>
       </c>
       <c t="s" r="J99" s="7">
         <v>178</v>
@@ -4592,78 +4596,78 @@
         <v>13</v>
       </c>
       <c r="B100" s="7">
-        <v>136</v>
+        <v>443</v>
       </c>
       <c t="s" r="C100" s="7">
         <v>14</v>
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G100" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H100" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>49</v>
+        <v>95</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>167</v>
+        <v>83</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
       <c r="M100" s="7"/>
     </row>
     <row r="101" ht="14.25" customHeight="1">
-      <c r="A101" s="6"/>
-      <c r="B101" s="7"/>
-      <c r="C101" s="7"/>
+      <c t="s" r="A101" s="6">
+        <v>13</v>
+      </c>
+      <c r="B101" s="7">
+        <v>968</v>
+      </c>
+      <c t="s" r="C101" s="7">
+        <v>14</v>
+      </c>
       <c r="D101" s="7"/>
-      <c r="E101" s="7"/>
-      <c r="F101" s="7"/>
-      <c r="G101" s="8"/>
-      <c r="H101" s="8"/>
-      <c r="I101" s="7"/>
-      <c r="J101" s="7"/>
+      <c t="s" r="E101" s="7">
+        <v>176</v>
+      </c>
+      <c r="F101" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G101" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H101" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I101" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J101" s="7">
+        <v>180</v>
+      </c>
       <c r="K101" s="7"/>
       <c r="L101" s="7"/>
       <c r="M101" s="7"/>
     </row>
     <row r="102" ht="14.25" customHeight="1">
-      <c t="s" r="A102" s="6">
-        <v>13</v>
-      </c>
-      <c r="B102" s="7">
-        <v>6847</v>
-      </c>
-      <c t="s" r="C102" s="7">
-        <v>179</v>
-      </c>
+      <c r="A102" s="6"/>
+      <c r="B102" s="7"/>
+      <c r="C102" s="7"/>
       <c r="D102" s="7"/>
-      <c t="s" r="E102" s="7">
-        <v>180</v>
-      </c>
-      <c r="F102" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G102" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H102" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="I102" s="7">
-        <v>172</v>
-      </c>
-      <c t="s" r="J102" s="7">
-        <v>89</v>
-      </c>
+      <c r="E102" s="7"/>
+      <c r="F102" s="7"/>
+      <c r="G102" s="8"/>
+      <c r="H102" s="8"/>
+      <c r="I102" s="7"/>
+      <c r="J102" s="7"/>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c r="M102" s="7"/>
@@ -4673,29 +4677,29 @@
         <v>13</v>
       </c>
       <c r="B103" s="7">
-        <v>6848</v>
+        <v>626</v>
       </c>
       <c t="s" r="C103" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c t="s" r="H103" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>43</v>
+        <v>182</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
@@ -4706,29 +4710,29 @@
         <v>13</v>
       </c>
       <c r="B104" s="7">
-        <v>6848</v>
+        <v>627</v>
       </c>
       <c t="s" r="C104" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G104" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>22</v>
+        <v>168</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>161</v>
+        <v>184</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
@@ -4736,48 +4740,66 @@
     </row>
     <row r="105" ht="15" customHeight="1">
       <c t="s" r="A105" s="6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B105" s="7">
-        <v>6849</v>
+        <v>242</v>
       </c>
       <c t="s" r="C105" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>182</v>
+        <v>25</v>
       </c>
       <c t="s" r="H105" s="8">
-        <v>40</v>
+        <v>110</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>108</v>
+        <v>186</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
       <c r="M105" s="7"/>
     </row>
     <row r="106" ht="14.25" customHeight="1">
-      <c r="A106" s="6"/>
-      <c r="B106" s="7"/>
-      <c r="C106" s="7"/>
+      <c t="s" r="A106" s="6">
+        <v>13</v>
+      </c>
+      <c r="B106" s="7">
+        <v>243</v>
+      </c>
+      <c t="s" r="C106" s="7">
+        <v>14</v>
+      </c>
       <c r="D106" s="7"/>
-      <c r="E106" s="7"/>
-      <c r="F106" s="7"/>
-      <c r="G106" s="8"/>
-      <c r="H106" s="8"/>
-      <c r="I106" s="7"/>
-      <c r="J106" s="7"/>
+      <c t="s" r="E106" s="7">
+        <v>181</v>
+      </c>
+      <c r="F106" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G106" s="8">
+        <v>110</v>
+      </c>
+      <c t="s" r="H106" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I106" s="7">
+        <v>91</v>
+      </c>
+      <c t="s" r="J106" s="7">
+        <v>187</v>
+      </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
       <c r="M106" s="7"/>
@@ -4787,14 +4809,14 @@
         <v>13</v>
       </c>
       <c r="B107" s="7">
-        <v>356</v>
+        <v>254</v>
       </c>
       <c t="s" r="C107" s="7">
         <v>14</v>
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -4803,13 +4825,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H107" s="8">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c t="s" r="I107" s="7">
-        <v>168</v>
+        <v>104</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>185</v>
+        <v>172</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -4820,29 +4842,29 @@
         <v>13</v>
       </c>
       <c r="B108" s="7">
-        <v>357</v>
+        <v>255</v>
       </c>
       <c t="s" r="C108" s="7">
         <v>14</v>
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G108" s="8">
-        <v>61</v>
+        <v>110</v>
       </c>
       <c t="s" r="H108" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>53</v>
+        <v>24</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>60</v>
+        <v>188</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -4853,14 +4875,14 @@
         <v>13</v>
       </c>
       <c r="B109" s="7">
-        <v>321</v>
+        <v>136</v>
       </c>
       <c t="s" r="C109" s="7">
         <v>14</v>
       </c>
       <c r="D109" s="7"/>
       <c t="s" r="E109" s="7">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="F109" s="7">
         <v>321</v>
@@ -4869,47 +4891,29 @@
         <v>25</v>
       </c>
       <c t="s" r="H109" s="8">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c t="s" r="I109" s="7">
-        <v>30</v>
+        <v>49</v>
       </c>
       <c t="s" r="J109" s="7">
-        <v>186</v>
+        <v>179</v>
       </c>
       <c r="K109" s="7"/>
       <c r="L109" s="7"/>
       <c r="M109" s="7"/>
     </row>
     <row r="110" ht="15" customHeight="1">
-      <c t="s" r="A110" s="6">
-        <v>13</v>
-      </c>
-      <c r="B110" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="C110" s="7">
-        <v>14</v>
-      </c>
+      <c r="A110" s="6"/>
+      <c r="B110" s="7"/>
+      <c r="C110" s="7"/>
       <c r="D110" s="7"/>
-      <c t="s" r="E110" s="7">
-        <v>184</v>
-      </c>
-      <c r="F110" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G110" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H110" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I110" s="7">
-        <v>19</v>
-      </c>
-      <c t="s" r="J110" s="7">
-        <v>187</v>
-      </c>
+      <c r="E110" s="7"/>
+      <c r="F110" s="7"/>
+      <c r="G110" s="8"/>
+      <c r="H110" s="8"/>
+      <c r="I110" s="7"/>
+      <c r="J110" s="7"/>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c r="M110" s="7"/>
@@ -4919,29 +4923,29 @@
         <v>13</v>
       </c>
       <c r="B111" s="7">
-        <v>274</v>
+        <v>6847</v>
       </c>
       <c t="s" r="C111" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G111" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H111" s="8">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c t="s" r="I111" s="7">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>181</v>
+        <v>89</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -4952,29 +4956,29 @@
         <v>13</v>
       </c>
       <c r="B112" s="7">
-        <v>275</v>
+        <v>6848</v>
       </c>
       <c t="s" r="C112" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G112" s="8">
-        <v>125</v>
+        <v>17</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I112" s="7">
-        <v>188</v>
+        <v>43</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>105</v>
+        <v>191</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -4985,29 +4989,29 @@
         <v>13</v>
       </c>
       <c r="B113" s="7">
-        <v>276</v>
+        <v>6848</v>
       </c>
       <c t="s" r="C113" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H113" s="8">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>142</v>
+        <v>22</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>189</v>
+        <v>163</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5015,32 +5019,32 @@
     </row>
     <row r="114" ht="14.25" customHeight="1">
       <c t="s" r="A114" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B114" s="7">
-        <v>277</v>
+        <v>6849</v>
       </c>
       <c t="s" r="C114" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D114" s="7"/>
       <c t="s" r="E114" s="7">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F114" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G114" s="8">
-        <v>125</v>
+        <v>192</v>
       </c>
       <c t="s" r="H114" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I114" s="7">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c t="s" r="J114" s="7">
-        <v>161</v>
+        <v>108</v>
       </c>
       <c r="K114" s="7"/>
       <c r="L114" s="7"/>
@@ -5066,29 +5070,29 @@
         <v>13</v>
       </c>
       <c r="B116" s="7">
-        <v>933</v>
+        <v>356</v>
       </c>
       <c t="s" r="C116" s="7">
         <v>14</v>
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c t="s" r="H116" s="8">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>30</v>
+        <v>180</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>44</v>
+        <v>195</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5099,29 +5103,29 @@
         <v>13</v>
       </c>
       <c r="B117" s="7">
-        <v>403</v>
+        <v>357</v>
       </c>
       <c t="s" r="C117" s="7">
         <v>14</v>
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G117" s="8">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c t="s" r="H117" s="8">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c t="s" r="I117" s="7">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>79</v>
+        <v>137</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
@@ -5132,29 +5136,29 @@
         <v>13</v>
       </c>
       <c r="B118" s="7">
-        <v>404</v>
+        <v>321</v>
       </c>
       <c t="s" r="C118" s="7">
         <v>14</v>
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G118" s="8">
-        <v>46</v>
+        <v>25</v>
       </c>
       <c t="s" r="H118" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="I118" s="7">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>81</v>
+        <v>196</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5162,48 +5166,66 @@
     </row>
     <row r="119" ht="14.25" customHeight="1">
       <c t="s" r="A119" s="6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B119" s="7">
-        <v>932</v>
+        <v>320</v>
       </c>
       <c t="s" r="C119" s="7">
         <v>14</v>
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G119" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>192</v>
+        <v>19</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>53</v>
+        <v>197</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
       <c r="M119" s="7"/>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="6"/>
-      <c r="B120" s="7"/>
-      <c r="C120" s="7"/>
+      <c t="s" r="A120" s="6">
+        <v>13</v>
+      </c>
+      <c r="B120" s="7">
+        <v>274</v>
+      </c>
+      <c t="s" r="C120" s="7">
+        <v>14</v>
+      </c>
       <c r="D120" s="7"/>
-      <c r="E120" s="7"/>
-      <c r="F120" s="7"/>
-      <c r="G120" s="8"/>
-      <c r="H120" s="8"/>
-      <c r="I120" s="7"/>
-      <c r="J120" s="7"/>
+      <c t="s" r="E120" s="7">
+        <v>194</v>
+      </c>
+      <c r="F120" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G120" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H120" s="8">
+        <v>125</v>
+      </c>
+      <c t="s" r="I120" s="7">
+        <v>178</v>
+      </c>
+      <c t="s" r="J120" s="7">
+        <v>191</v>
+      </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
       <c r="M120" s="7"/>
@@ -5213,29 +5235,29 @@
         <v>13</v>
       </c>
       <c r="B121" s="7">
-        <v>724</v>
+        <v>275</v>
       </c>
       <c t="s" r="C121" s="7">
         <v>14</v>
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G121" s="8">
+        <v>125</v>
+      </c>
+      <c t="s" r="H121" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I121" s="7">
+        <v>198</v>
+      </c>
+      <c t="s" r="J121" s="7">
         <v>67</v>
-      </c>
-      <c t="s" r="H121" s="8">
-        <v>125</v>
-      </c>
-      <c t="s" r="I121" s="7">
-        <v>147</v>
-      </c>
-      <c t="s" r="J121" s="7">
-        <v>22</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5246,29 +5268,29 @@
         <v>13</v>
       </c>
       <c r="B122" s="7">
-        <v>725</v>
+        <v>276</v>
       </c>
       <c t="s" r="C122" s="7">
         <v>14</v>
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H122" s="8">
         <v>125</v>
       </c>
-      <c t="s" r="H122" s="8">
-        <v>67</v>
-      </c>
       <c t="s" r="I122" s="7">
-        <v>94</v>
+        <v>142</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>149</v>
+        <v>199</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5279,78 +5301,78 @@
         <v>13</v>
       </c>
       <c r="B123" s="7">
-        <v>633</v>
+        <v>277</v>
       </c>
       <c t="s" r="C123" s="7">
         <v>14</v>
       </c>
       <c r="D123" s="7"/>
       <c t="s" r="E123" s="7">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F123" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G123" s="8">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c t="s" r="H123" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I123" s="7">
-        <v>45</v>
+        <v>200</v>
       </c>
       <c t="s" r="J123" s="7">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K123" s="7"/>
       <c r="L123" s="7"/>
       <c r="M123" s="7"/>
     </row>
     <row r="124" ht="14.25" customHeight="1">
-      <c t="s" r="A124" s="6">
-        <v>13</v>
-      </c>
-      <c r="B124" s="7">
-        <v>632</v>
-      </c>
-      <c t="s" r="C124" s="7">
-        <v>14</v>
-      </c>
+      <c r="A124" s="6"/>
+      <c r="B124" s="7"/>
+      <c r="C124" s="7"/>
       <c r="D124" s="7"/>
-      <c t="s" r="E124" s="7">
-        <v>193</v>
-      </c>
-      <c r="F124" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G124" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H124" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I124" s="7">
-        <v>194</v>
-      </c>
-      <c t="s" r="J124" s="7">
-        <v>49</v>
-      </c>
+      <c r="E124" s="7"/>
+      <c r="F124" s="7"/>
+      <c r="G124" s="8"/>
+      <c r="H124" s="8"/>
+      <c r="I124" s="7"/>
+      <c r="J124" s="7"/>
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c r="M124" s="7"/>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="6"/>
-      <c r="B125" s="7"/>
-      <c r="C125" s="7"/>
+      <c t="s" r="A125" s="6">
+        <v>13</v>
+      </c>
+      <c r="B125" s="7">
+        <v>933</v>
+      </c>
+      <c t="s" r="C125" s="7">
+        <v>14</v>
+      </c>
       <c r="D125" s="7"/>
-      <c r="E125" s="7"/>
-      <c r="F125" s="7"/>
-      <c r="G125" s="8"/>
-      <c r="H125" s="8"/>
-      <c r="I125" s="7"/>
-      <c r="J125" s="7"/>
+      <c t="s" r="E125" s="7">
+        <v>201</v>
+      </c>
+      <c r="F125" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G125" s="8">
+        <v>76</v>
+      </c>
+      <c t="s" r="H125" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I125" s="7">
+        <v>30</v>
+      </c>
+      <c t="s" r="J125" s="7">
+        <v>44</v>
+      </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
       <c r="M125" s="7"/>
@@ -5360,14 +5382,14 @@
         <v>13</v>
       </c>
       <c r="B126" s="7">
-        <v>1139</v>
+        <v>403</v>
       </c>
       <c t="s" r="C126" s="7">
         <v>14</v>
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5376,13 +5398,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H126" s="8">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>196</v>
+        <v>65</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>197</v>
+        <v>80</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5393,29 +5415,29 @@
         <v>13</v>
       </c>
       <c r="B127" s="7">
-        <v>1138</v>
+        <v>404</v>
       </c>
       <c t="s" r="C127" s="7">
         <v>14</v>
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G127" s="8">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c t="s" r="H127" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>137</v>
+        <v>81</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>138</v>
+        <v>82</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5423,17 +5445,17 @@
     </row>
     <row r="128" ht="14.25" customHeight="1">
       <c t="s" r="A128" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B128" s="7">
-        <v>129</v>
+        <v>932</v>
       </c>
       <c t="s" r="C128" s="7">
         <v>14</v>
       </c>
       <c r="D128" s="7"/>
       <c t="s" r="E128" s="7">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F128" s="7">
         <v>321</v>
@@ -5442,47 +5464,29 @@
         <v>40</v>
       </c>
       <c t="s" r="H128" s="8">
-        <v>25</v>
+        <v>76</v>
       </c>
       <c t="s" r="I128" s="7">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c t="s" r="J128" s="7">
-        <v>199</v>
+        <v>53</v>
       </c>
       <c r="K128" s="7"/>
       <c r="L128" s="7"/>
       <c r="M128" s="7"/>
     </row>
     <row r="129" ht="14.25" customHeight="1">
-      <c t="s" r="A129" s="6">
-        <v>13</v>
-      </c>
-      <c r="B129" s="7">
-        <v>128</v>
-      </c>
-      <c t="s" r="C129" s="7">
-        <v>14</v>
-      </c>
+      <c r="A129" s="6"/>
+      <c r="B129" s="7"/>
+      <c r="C129" s="7"/>
       <c r="D129" s="7"/>
-      <c t="s" r="E129" s="7">
-        <v>195</v>
-      </c>
-      <c r="F129" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G129" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H129" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I129" s="7">
-        <v>200</v>
-      </c>
-      <c t="s" r="J129" s="7">
-        <v>201</v>
-      </c>
+      <c r="E129" s="7"/>
+      <c r="F129" s="7"/>
+      <c r="G129" s="8"/>
+      <c r="H129" s="8"/>
+      <c r="I129" s="7"/>
+      <c r="J129" s="7"/>
       <c r="K129" s="7"/>
       <c r="L129" s="7"/>
       <c r="M129" s="7"/>
@@ -5492,29 +5496,29 @@
         <v>13</v>
       </c>
       <c r="B130" s="7">
-        <v>521</v>
+        <v>724</v>
       </c>
       <c t="s" r="C130" s="7">
         <v>14</v>
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>178</v>
+        <v>147</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>70</v>
+        <v>22</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5525,45 +5529,63 @@
         <v>13</v>
       </c>
       <c r="B131" s="7">
-        <v>522</v>
+        <v>725</v>
       </c>
       <c t="s" r="C131" s="7">
         <v>14</v>
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>67</v>
+        <v>125</v>
       </c>
       <c t="s" r="H131" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="I131" s="7">
-        <v>71</v>
+        <v>94</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>202</v>
+        <v>152</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
       <c r="M131" s="7"/>
     </row>
     <row r="132" ht="14.25" customHeight="1">
-      <c r="A132" s="6"/>
-      <c r="B132" s="7"/>
-      <c r="C132" s="7"/>
+      <c t="s" r="A132" s="6">
+        <v>13</v>
+      </c>
+      <c r="B132" s="7">
+        <v>633</v>
+      </c>
+      <c t="s" r="C132" s="7">
+        <v>14</v>
+      </c>
       <c r="D132" s="7"/>
-      <c r="E132" s="7"/>
-      <c r="F132" s="7"/>
-      <c r="G132" s="8"/>
-      <c r="H132" s="8"/>
-      <c r="I132" s="7"/>
-      <c r="J132" s="7"/>
+      <c t="s" r="E132" s="7">
+        <v>203</v>
+      </c>
+      <c r="F132" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G132" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H132" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I132" s="7">
+        <v>45</v>
+      </c>
+      <c t="s" r="J132" s="7">
+        <v>162</v>
+      </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
       <c r="M132" s="7"/>
@@ -5573,7 +5595,7 @@
         <v>13</v>
       </c>
       <c r="B133" s="7">
-        <v>463</v>
+        <v>632</v>
       </c>
       <c t="s" r="C133" s="7">
         <v>14</v>
@@ -5586,50 +5608,32 @@
         <v>321</v>
       </c>
       <c t="s" r="G133" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="H133" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="I133" s="7">
         <v>204</v>
       </c>
-      <c t="s" r="I133" s="7">
-        <v>205</v>
-      </c>
       <c t="s" r="J133" s="7">
-        <v>206</v>
+        <v>49</v>
       </c>
       <c r="K133" s="7"/>
       <c r="L133" s="7"/>
       <c r="M133" s="7"/>
     </row>
     <row r="134" ht="14.25" customHeight="1">
-      <c t="s" r="A134" s="6">
-        <v>13</v>
-      </c>
-      <c r="B134" s="7">
-        <v>462</v>
-      </c>
-      <c t="s" r="C134" s="7">
-        <v>14</v>
-      </c>
+      <c r="A134" s="6"/>
+      <c r="B134" s="7"/>
+      <c r="C134" s="7"/>
       <c r="D134" s="7"/>
-      <c t="s" r="E134" s="7">
-        <v>203</v>
-      </c>
-      <c r="F134" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G134" s="8">
-        <v>204</v>
-      </c>
-      <c t="s" r="H134" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I134" s="7">
-        <v>165</v>
-      </c>
-      <c t="s" r="J134" s="7">
-        <v>207</v>
-      </c>
+      <c r="E134" s="7"/>
+      <c r="F134" s="7"/>
+      <c r="G134" s="8"/>
+      <c r="H134" s="8"/>
+      <c r="I134" s="7"/>
+      <c r="J134" s="7"/>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c r="M134" s="7"/>
@@ -5639,14 +5643,14 @@
         <v>13</v>
       </c>
       <c r="B135" s="7">
-        <v>143</v>
+        <v>1139</v>
       </c>
       <c t="s" r="C135" s="7">
         <v>14</v>
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5658,10 +5662,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>127</v>
+        <v>207</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -5672,14 +5676,14 @@
         <v>13</v>
       </c>
       <c r="B136" s="7">
-        <v>1321</v>
+        <v>1138</v>
       </c>
       <c t="s" r="C136" s="7">
         <v>14</v>
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5688,13 +5692,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H136" s="8">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>209</v>
+        <v>138</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>48</v>
+        <v>139</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5705,29 +5709,29 @@
         <v>13</v>
       </c>
       <c r="B137" s="7">
-        <v>6842</v>
+        <v>129</v>
       </c>
       <c t="s" r="C137" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G137" s="8">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c t="s" r="H137" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>85</v>
+        <v>209</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5735,48 +5739,66 @@
     </row>
     <row r="138" ht="14.25" customHeight="1">
       <c t="s" r="A138" s="6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B138" s="7">
-        <v>6842</v>
+        <v>128</v>
       </c>
       <c t="s" r="C138" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G138" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="H138" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I138" s="7">
+        <v>210</v>
+      </c>
+      <c t="s" r="J138" s="7">
         <v>211</v>
-      </c>
-      <c t="s" r="I138" s="7">
-        <v>212</v>
-      </c>
-      <c t="s" r="J138" s="7">
-        <v>213</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
       <c r="M138" s="7"/>
     </row>
     <row r="139" ht="14.25" customHeight="1">
-      <c r="A139" s="6"/>
-      <c r="B139" s="7"/>
-      <c r="C139" s="7"/>
+      <c t="s" r="A139" s="6">
+        <v>13</v>
+      </c>
+      <c r="B139" s="7">
+        <v>521</v>
+      </c>
+      <c t="s" r="C139" s="7">
+        <v>14</v>
+      </c>
       <c r="D139" s="7"/>
-      <c r="E139" s="7"/>
-      <c r="F139" s="7"/>
-      <c r="G139" s="8"/>
-      <c r="H139" s="8"/>
-      <c r="I139" s="7"/>
-      <c r="J139" s="7"/>
+      <c t="s" r="E139" s="7">
+        <v>205</v>
+      </c>
+      <c r="F139" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G139" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H139" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="I139" s="7">
+        <v>188</v>
+      </c>
+      <c t="s" r="J139" s="7">
+        <v>71</v>
+      </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
       <c r="M139" s="7"/>
@@ -5786,63 +5808,45 @@
         <v>13</v>
       </c>
       <c r="B140" s="7">
-        <v>451</v>
+        <v>522</v>
       </c>
       <c t="s" r="C140" s="7">
         <v>14</v>
       </c>
       <c r="D140" s="7"/>
       <c t="s" r="E140" s="7">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="F140" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G140" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="H140" s="8">
-        <v>17</v>
+        <v>40</v>
       </c>
       <c t="s" r="I140" s="7">
-        <v>215</v>
+        <v>72</v>
       </c>
       <c t="s" r="J140" s="7">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="K140" s="7"/>
       <c r="L140" s="7"/>
       <c r="M140" s="7"/>
     </row>
     <row r="141" ht="14.25" customHeight="1">
-      <c t="s" r="A141" s="6">
-        <v>13</v>
-      </c>
-      <c r="B141" s="7">
-        <v>450</v>
-      </c>
-      <c t="s" r="C141" s="7">
-        <v>14</v>
-      </c>
+      <c r="A141" s="6"/>
+      <c r="B141" s="7"/>
+      <c r="C141" s="7"/>
       <c r="D141" s="7"/>
-      <c t="s" r="E141" s="7">
-        <v>214</v>
-      </c>
-      <c r="F141" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G141" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H141" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I141" s="7">
-        <v>42</v>
-      </c>
-      <c t="s" r="J141" s="7">
-        <v>89</v>
-      </c>
+      <c r="E141" s="7"/>
+      <c r="F141" s="7"/>
+      <c r="G141" s="8"/>
+      <c r="H141" s="8"/>
+      <c r="I141" s="7"/>
+      <c r="J141" s="7"/>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c r="M141" s="7"/>
@@ -5852,29 +5856,29 @@
         <v>13</v>
       </c>
       <c r="B142" s="7">
-        <v>401</v>
+        <v>463</v>
       </c>
       <c t="s" r="C142" s="7">
         <v>14</v>
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
+        <v>213</v>
+      </c>
+      <c r="F142" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G142" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H142" s="8">
         <v>214</v>
       </c>
-      <c r="F142" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G142" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H142" s="8">
-        <v>46</v>
-      </c>
       <c t="s" r="I142" s="7">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
@@ -5885,29 +5889,29 @@
         <v>13</v>
       </c>
       <c r="B143" s="7">
-        <v>402</v>
+        <v>462</v>
       </c>
       <c t="s" r="C143" s="7">
         <v>14</v>
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
+        <v>213</v>
+      </c>
+      <c r="F143" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G143" s="8">
         <v>214</v>
       </c>
-      <c r="F143" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G143" s="8">
-        <v>46</v>
-      </c>
       <c t="s" r="H143" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>217</v>
+        <v>177</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>22</v>
+        <v>148</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -5918,14 +5922,14 @@
         <v>13</v>
       </c>
       <c r="B144" s="7">
-        <v>423</v>
+        <v>143</v>
       </c>
       <c t="s" r="C144" s="7">
         <v>14</v>
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -5934,13 +5938,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>94</v>
+        <v>170</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -5951,151 +5955,143 @@
         <v>13</v>
       </c>
       <c r="B145" s="7">
-        <v>424</v>
+        <v>1321</v>
       </c>
       <c t="s" r="C145" s="7">
         <v>14</v>
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c t="s" r="H145" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>119</v>
+        <v>217</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>121</v>
+        <v>48</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
       <c r="M145" s="7"/>
     </row>
     <row r="146" ht="14.25" customHeight="1">
-      <c r="A146" s="6"/>
-      <c r="B146" s="7"/>
-      <c r="C146" s="7"/>
+      <c t="s" r="A146" s="6">
+        <v>13</v>
+      </c>
+      <c r="B146" s="7">
+        <v>6842</v>
+      </c>
+      <c t="s" r="C146" s="7">
+        <v>189</v>
+      </c>
       <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="7"/>
-      <c r="G146" s="8"/>
-      <c r="H146" s="8"/>
-      <c r="I146" s="7"/>
-      <c r="J146" s="7"/>
+      <c t="s" r="E146" s="7">
+        <v>213</v>
+      </c>
+      <c r="F146" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G146" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H146" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I146" s="7">
+        <v>174</v>
+      </c>
+      <c t="s" r="J146" s="7">
+        <v>86</v>
+      </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
       <c r="M146" s="7"/>
     </row>
     <row r="147" ht="14.25" customHeight="1">
       <c t="s" r="A147" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B147" s="7">
-        <v>5217</v>
+        <v>6842</v>
       </c>
       <c t="s" r="C147" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
+        <v>213</v>
+      </c>
+      <c r="F147" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G147" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H147" s="8">
         <v>218</v>
       </c>
-      <c r="F147" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G147" s="8">
+      <c t="s" r="I147" s="7">
         <v>219</v>
       </c>
-      <c t="s" r="H147" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I147" s="7">
+      <c t="s" r="J147" s="7">
         <v>220</v>
       </c>
-      <c t="s" r="J147" s="7">
-        <v>221</v>
-      </c>
-      <c t="s" r="K147" s="7">
-        <v>185</v>
-      </c>
+      <c r="K147" s="7"/>
       <c r="L147" s="7"/>
-      <c t="s" r="M147" s="7">
-        <v>173</v>
-      </c>
+      <c r="M147" s="7"/>
     </row>
     <row r="148" ht="14.25" customHeight="1">
-      <c t="s" r="A148" s="6">
-        <v>13</v>
-      </c>
-      <c r="B148" s="7">
-        <v>5217</v>
-      </c>
-      <c t="s" r="C148" s="7">
-        <v>14</v>
-      </c>
+      <c r="A148" s="6"/>
+      <c r="B148" s="7"/>
+      <c r="C148" s="7"/>
       <c r="D148" s="7"/>
-      <c t="s" r="E148" s="7">
-        <v>218</v>
-      </c>
-      <c r="F148" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G148" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H148" s="8">
-        <v>222</v>
-      </c>
-      <c t="s" r="I148" s="7">
-        <v>108</v>
-      </c>
-      <c t="s" r="J148" s="7">
-        <v>155</v>
-      </c>
-      <c t="s" r="K148" s="7">
-        <v>89</v>
-      </c>
+      <c r="E148" s="7"/>
+      <c r="F148" s="7"/>
+      <c r="G148" s="8"/>
+      <c r="H148" s="8"/>
+      <c r="I148" s="7"/>
+      <c r="J148" s="7"/>
+      <c r="K148" s="7"/>
       <c r="L148" s="7"/>
-      <c t="s" r="M148" s="7">
-        <v>175</v>
-      </c>
+      <c r="M148" s="7"/>
     </row>
     <row r="149" ht="14.25" customHeight="1">
       <c t="s" r="A149" s="6">
         <v>13</v>
       </c>
       <c r="B149" s="7">
-        <v>6862</v>
+        <v>451</v>
       </c>
       <c t="s" r="C149" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D149" s="7"/>
       <c t="s" r="E149" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F149" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G149" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H149" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="I149" s="7">
         <v>222</v>
       </c>
-      <c t="s" r="H149" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I149" s="7">
+      <c t="s" r="J149" s="7">
         <v>223</v>
-      </c>
-      <c t="s" r="J149" s="7">
-        <v>50</v>
       </c>
       <c r="K149" s="7"/>
       <c r="L149" s="7"/>
@@ -6106,45 +6102,63 @@
         <v>13</v>
       </c>
       <c r="B150" s="7">
-        <v>6862</v>
+        <v>450</v>
       </c>
       <c t="s" r="C150" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G150" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="H150" s="8">
-        <v>224</v>
+        <v>40</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>225</v>
+        <v>42</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>135</v>
+        <v>89</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c r="M150" s="7"/>
     </row>
     <row r="151" ht="14.25" customHeight="1">
-      <c r="A151" s="6"/>
-      <c r="B151" s="7"/>
-      <c r="C151" s="7"/>
+      <c t="s" r="A151" s="6">
+        <v>13</v>
+      </c>
+      <c r="B151" s="7">
+        <v>401</v>
+      </c>
+      <c t="s" r="C151" s="7">
+        <v>14</v>
+      </c>
       <c r="D151" s="7"/>
-      <c r="E151" s="7"/>
-      <c r="F151" s="7"/>
-      <c r="G151" s="8"/>
-      <c r="H151" s="8"/>
-      <c r="I151" s="7"/>
-      <c r="J151" s="7"/>
+      <c t="s" r="E151" s="7">
+        <v>221</v>
+      </c>
+      <c r="F151" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G151" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H151" s="8">
+        <v>46</v>
+      </c>
+      <c t="s" r="I151" s="7">
+        <v>148</v>
+      </c>
+      <c t="s" r="J151" s="7">
+        <v>170</v>
+      </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c r="M151" s="7"/>
@@ -6154,29 +6168,29 @@
         <v>13</v>
       </c>
       <c r="B152" s="7">
-        <v>91</v>
+        <v>402</v>
       </c>
       <c t="s" r="C152" s="7">
         <v>14</v>
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G152" s="8">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>108</v>
+        <v>224</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6187,29 +6201,29 @@
         <v>13</v>
       </c>
       <c r="B153" s="7">
-        <v>92</v>
+        <v>423</v>
       </c>
       <c t="s" r="C153" s="7">
         <v>14</v>
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>227</v>
+        <v>40</v>
       </c>
       <c t="s" r="H153" s="8">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c t="s" r="J153" s="7">
-        <v>228</v>
+        <v>118</v>
       </c>
       <c r="K153" s="7"/>
       <c r="L153" s="7"/>
@@ -6220,29 +6234,29 @@
         <v>13</v>
       </c>
       <c r="B154" s="7">
-        <v>822</v>
+        <v>424</v>
       </c>
       <c t="s" r="C154" s="7">
         <v>14</v>
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G154" s="8">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>75</v>
+        <v>40</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>225</v>
+        <v>119</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>18</v>
+        <v>121</v>
       </c>
       <c r="K154" s="7"/>
       <c r="L154" s="7"/>
@@ -6268,95 +6282,103 @@
         <v>13</v>
       </c>
       <c r="B156" s="7">
-        <v>528</v>
+        <v>5217</v>
       </c>
       <c t="s" r="C156" s="7">
         <v>14</v>
       </c>
       <c r="D156" s="7"/>
       <c t="s" r="E156" s="7">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F156" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G156" s="8">
-        <v>67</v>
+        <v>226</v>
       </c>
       <c t="s" r="H156" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I156" s="7">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c t="s" r="J156" s="7">
-        <v>88</v>
-      </c>
-      <c r="K156" s="7"/>
+        <v>228</v>
+      </c>
+      <c t="s" r="K156" s="7">
+        <v>195</v>
+      </c>
       <c r="L156" s="7"/>
-      <c r="M156" s="7"/>
+      <c t="s" r="M156" s="7">
+        <v>184</v>
+      </c>
     </row>
     <row r="157" ht="14.25" customHeight="1">
       <c t="s" r="A157" s="6">
         <v>13</v>
       </c>
       <c r="B157" s="7">
-        <v>527</v>
+        <v>5217</v>
       </c>
       <c t="s" r="C157" s="7">
         <v>14</v>
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
+        <v>225</v>
+      </c>
+      <c r="F157" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G157" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H157" s="8">
         <v>229</v>
       </c>
-      <c r="F157" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G157" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H157" s="8">
-        <v>67</v>
-      </c>
       <c t="s" r="I157" s="7">
-        <v>230</v>
+        <v>108</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>19</v>
-      </c>
-      <c r="K157" s="7"/>
+        <v>60</v>
+      </c>
+      <c t="s" r="K157" s="7">
+        <v>89</v>
+      </c>
       <c r="L157" s="7"/>
-      <c r="M157" s="7"/>
+      <c t="s" r="M157" s="7">
+        <v>186</v>
+      </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
       <c t="s" r="A158" s="6">
         <v>13</v>
       </c>
       <c r="B158" s="7">
-        <v>5880</v>
+        <v>6862</v>
       </c>
       <c t="s" r="C158" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
+        <v>225</v>
+      </c>
+      <c r="F158" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G158" s="8">
         <v>229</v>
       </c>
-      <c r="F158" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G158" s="8">
-        <v>67</v>
-      </c>
       <c t="s" r="H158" s="8">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>116</v>
+        <v>50</v>
       </c>
       <c r="K158" s="7"/>
       <c r="L158" s="7"/>
@@ -6367,111 +6389,111 @@
         <v>13</v>
       </c>
       <c r="B159" s="7">
-        <v>5881</v>
+        <v>6862</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H159" s="8">
         <v>231</v>
       </c>
-      <c t="s" r="H159" s="8">
-        <v>67</v>
-      </c>
       <c t="s" r="I159" s="7">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>23</v>
+        <v>135</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
       <c r="M159" s="7"/>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c t="s" r="A160" s="6">
-        <v>13</v>
-      </c>
-      <c r="B160" s="7">
-        <v>5840</v>
-      </c>
-      <c t="s" r="C160" s="7">
-        <v>179</v>
-      </c>
+      <c r="A160" s="6"/>
+      <c r="B160" s="7"/>
+      <c r="C160" s="7"/>
       <c r="D160" s="7"/>
-      <c t="s" r="E160" s="7">
-        <v>229</v>
-      </c>
-      <c r="F160" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G160" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H160" s="8">
-        <v>234</v>
-      </c>
-      <c t="s" r="I160" s="7">
-        <v>49</v>
-      </c>
-      <c t="s" r="J160" s="7">
-        <v>235</v>
-      </c>
+      <c r="E160" s="7"/>
+      <c r="F160" s="7"/>
+      <c r="G160" s="8"/>
+      <c r="H160" s="8"/>
+      <c r="I160" s="7"/>
+      <c r="J160" s="7"/>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
       <c r="M160" s="7"/>
     </row>
     <row r="161" ht="14.25" customHeight="1">
       <c t="s" r="A161" s="6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B161" s="7">
-        <v>5841</v>
+        <v>91</v>
       </c>
       <c t="s" r="C161" s="7">
-        <v>179</v>
+        <v>14</v>
       </c>
       <c r="D161" s="7"/>
       <c t="s" r="E161" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="F161" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G161" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H161" s="8">
         <v>234</v>
       </c>
-      <c t="s" r="H161" s="8">
-        <v>67</v>
-      </c>
       <c t="s" r="I161" s="7">
-        <v>183</v>
+        <v>108</v>
       </c>
       <c t="s" r="J161" s="7">
-        <v>236</v>
+        <v>32</v>
       </c>
       <c r="K161" s="7"/>
       <c r="L161" s="7"/>
       <c r="M161" s="7"/>
     </row>
     <row r="162" ht="14.25" customHeight="1">
-      <c r="A162" s="6"/>
-      <c r="B162" s="7"/>
-      <c r="C162" s="7"/>
+      <c t="s" r="A162" s="6">
+        <v>13</v>
+      </c>
+      <c r="B162" s="7">
+        <v>92</v>
+      </c>
+      <c t="s" r="C162" s="7">
+        <v>14</v>
+      </c>
       <c r="D162" s="7"/>
-      <c r="E162" s="7"/>
-      <c r="F162" s="7"/>
-      <c r="G162" s="8"/>
-      <c r="H162" s="8"/>
-      <c r="I162" s="7"/>
-      <c r="J162" s="7"/>
+      <c t="s" r="E162" s="7">
+        <v>233</v>
+      </c>
+      <c r="F162" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G162" s="8">
+        <v>234</v>
+      </c>
+      <c t="s" r="H162" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I162" s="7">
+        <v>152</v>
+      </c>
+      <c t="s" r="J162" s="7">
+        <v>235</v>
+      </c>
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c r="M162" s="7"/>
@@ -6481,63 +6503,45 @@
         <v>13</v>
       </c>
       <c r="B163" s="7">
-        <v>431</v>
+        <v>822</v>
       </c>
       <c t="s" r="C163" s="7">
         <v>14</v>
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="H163" s="8">
-        <v>238</v>
+        <v>76</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>124</v>
+        <v>232</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>239</v>
+        <v>18</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
       <c r="M163" s="7"/>
     </row>
     <row r="164" ht="14.25" customHeight="1">
-      <c t="s" r="A164" s="6">
-        <v>13</v>
-      </c>
-      <c r="B164" s="7">
-        <v>430</v>
-      </c>
-      <c t="s" r="C164" s="7">
-        <v>14</v>
-      </c>
+      <c r="A164" s="6"/>
+      <c r="B164" s="7"/>
+      <c r="C164" s="7"/>
       <c r="D164" s="7"/>
-      <c t="s" r="E164" s="7">
-        <v>237</v>
-      </c>
-      <c r="F164" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G164" s="8">
-        <v>238</v>
-      </c>
-      <c t="s" r="H164" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I164" s="7">
-        <v>186</v>
-      </c>
-      <c t="s" r="J164" s="7">
-        <v>187</v>
-      </c>
+      <c r="E164" s="7"/>
+      <c r="F164" s="7"/>
+      <c r="G164" s="8"/>
+      <c r="H164" s="8"/>
+      <c r="I164" s="7"/>
+      <c r="J164" s="7"/>
       <c r="K164" s="7"/>
       <c r="L164" s="7"/>
       <c r="M164" s="7"/>
@@ -6547,29 +6551,29 @@
         <v>13</v>
       </c>
       <c r="B165" s="7">
-        <v>523</v>
+        <v>528</v>
       </c>
       <c t="s" r="C165" s="7">
         <v>14</v>
       </c>
       <c r="D165" s="7"/>
       <c t="s" r="E165" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F165" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G165" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="H165" s="8">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c t="s" r="I165" s="7">
-        <v>240</v>
+        <v>228</v>
       </c>
       <c t="s" r="J165" s="7">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="K165" s="7"/>
       <c r="L165" s="7"/>
@@ -6580,29 +6584,29 @@
         <v>13</v>
       </c>
       <c r="B166" s="7">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c t="s" r="C166" s="7">
         <v>14</v>
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
+        <v>236</v>
+      </c>
+      <c r="F166" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G166" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H166" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="I166" s="7">
         <v>237</v>
       </c>
-      <c r="F166" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G166" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H166" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I166" s="7">
-        <v>241</v>
-      </c>
       <c t="s" r="J166" s="7">
-        <v>79</v>
+        <v>19</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
@@ -6613,29 +6617,29 @@
         <v>13</v>
       </c>
       <c r="B167" s="7">
-        <v>461</v>
+        <v>5880</v>
       </c>
       <c t="s" r="C167" s="7">
         <v>14</v>
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G167" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>200</v>
+        <v>239</v>
       </c>
       <c t="s" r="J167" s="7">
-        <v>201</v>
+        <v>116</v>
       </c>
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
@@ -6646,111 +6650,111 @@
         <v>13</v>
       </c>
       <c r="B168" s="7">
-        <v>460</v>
+        <v>5881</v>
       </c>
       <c t="s" r="C168" s="7">
         <v>14</v>
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>204</v>
+        <v>238</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>209</v>
+        <v>240</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>242</v>
+        <v>23</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c r="M168" s="7"/>
     </row>
     <row r="169" ht="14.25" customHeight="1">
-      <c r="A169" s="6"/>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
+      <c t="s" r="A169" s="6">
+        <v>13</v>
+      </c>
+      <c r="B169" s="7">
+        <v>5840</v>
+      </c>
+      <c t="s" r="C169" s="7">
+        <v>189</v>
+      </c>
       <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-      <c r="G169" s="8"/>
-      <c r="H169" s="8"/>
-      <c r="I169" s="7"/>
-      <c r="J169" s="7"/>
+      <c t="s" r="E169" s="7">
+        <v>236</v>
+      </c>
+      <c r="F169" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G169" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H169" s="8">
+        <v>241</v>
+      </c>
+      <c t="s" r="I169" s="7">
+        <v>49</v>
+      </c>
+      <c t="s" r="J169" s="7">
+        <v>242</v>
+      </c>
       <c r="K169" s="7"/>
       <c r="L169" s="7"/>
       <c r="M169" s="7"/>
     </row>
     <row r="170" ht="15" customHeight="1">
       <c t="s" r="A170" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B170" s="7">
-        <v>925</v>
+        <v>5841</v>
       </c>
       <c t="s" r="C170" s="7">
-        <v>14</v>
+        <v>189</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
+        <v>236</v>
+      </c>
+      <c r="F170" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G170" s="8">
+        <v>241</v>
+      </c>
+      <c t="s" r="H170" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="I170" s="7">
+        <v>193</v>
+      </c>
+      <c t="s" r="J170" s="7">
         <v>243</v>
-      </c>
-      <c r="F170" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G170" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="H170" s="8">
-        <v>125</v>
-      </c>
-      <c t="s" r="I170" s="7">
-        <v>135</v>
-      </c>
-      <c t="s" r="J170" s="7">
-        <v>174</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
       <c r="M170" s="7"/>
     </row>
     <row r="171" ht="14.25" customHeight="1">
-      <c t="s" r="A171" s="6">
-        <v>13</v>
-      </c>
-      <c r="B171" s="7">
-        <v>671</v>
-      </c>
-      <c t="s" r="C171" s="7">
-        <v>14</v>
-      </c>
+      <c r="A171" s="6"/>
+      <c r="B171" s="7"/>
+      <c r="C171" s="7"/>
       <c r="D171" s="7"/>
-      <c t="s" r="E171" s="7">
-        <v>243</v>
-      </c>
-      <c r="F171" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G171" s="8">
-        <v>125</v>
-      </c>
-      <c t="s" r="H171" s="8">
-        <v>61</v>
-      </c>
-      <c t="s" r="I171" s="7">
-        <v>244</v>
-      </c>
-      <c t="s" r="J171" s="7">
-        <v>208</v>
-      </c>
+      <c r="E171" s="7"/>
+      <c r="F171" s="7"/>
+      <c r="G171" s="8"/>
+      <c r="H171" s="8"/>
+      <c r="I171" s="7"/>
+      <c r="J171" s="7"/>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
       <c r="M171" s="7"/>
@@ -6760,29 +6764,29 @@
         <v>13</v>
       </c>
       <c r="B172" s="7">
-        <v>670</v>
+        <v>431</v>
       </c>
       <c t="s" r="C172" s="7">
         <v>14</v>
       </c>
       <c r="D172" s="7"/>
       <c t="s" r="E172" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F172" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G172" s="8">
-        <v>61</v>
+        <v>40</v>
       </c>
       <c t="s" r="H172" s="8">
-        <v>125</v>
+        <v>245</v>
       </c>
       <c t="s" r="I172" s="7">
-        <v>217</v>
+        <v>124</v>
       </c>
       <c t="s" r="J172" s="7">
-        <v>127</v>
+        <v>169</v>
       </c>
       <c r="K172" s="7"/>
       <c r="L172" s="7"/>
@@ -6793,29 +6797,29 @@
         <v>13</v>
       </c>
       <c r="B173" s="7">
-        <v>489</v>
+        <v>430</v>
       </c>
       <c t="s" r="C173" s="7">
         <v>14</v>
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G173" s="8">
-        <v>125</v>
+        <v>245</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>141</v>
+        <v>196</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>142</v>
+        <v>197</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
@@ -6826,45 +6830,63 @@
         <v>13</v>
       </c>
       <c r="B174" s="7">
-        <v>488</v>
+        <v>523</v>
       </c>
       <c t="s" r="C174" s="7">
         <v>14</v>
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c t="s" r="H174" s="8">
-        <v>125</v>
+        <v>68</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>246</v>
+        <v>65</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c r="M174" s="7"/>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="6"/>
-      <c r="B175" s="7"/>
-      <c r="C175" s="7"/>
+      <c t="s" r="A175" s="6">
+        <v>13</v>
+      </c>
+      <c r="B175" s="7">
+        <v>524</v>
+      </c>
+      <c t="s" r="C175" s="7">
+        <v>14</v>
+      </c>
       <c r="D175" s="7"/>
-      <c r="E175" s="7"/>
-      <c r="F175" s="7"/>
-      <c r="G175" s="8"/>
-      <c r="H175" s="8"/>
-      <c r="I175" s="7"/>
-      <c r="J175" s="7"/>
+      <c t="s" r="E175" s="7">
+        <v>244</v>
+      </c>
+      <c r="F175" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G175" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H175" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I175" s="7">
+        <v>247</v>
+      </c>
+      <c t="s" r="J175" s="7">
+        <v>80</v>
+      </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c r="M175" s="7"/>
@@ -6874,14 +6896,14 @@
         <v>13</v>
       </c>
       <c r="B176" s="7">
-        <v>421</v>
+        <v>461</v>
       </c>
       <c t="s" r="C176" s="7">
         <v>14</v>
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -6890,124 +6912,94 @@
         <v>40</v>
       </c>
       <c t="s" r="H176" s="8">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>248</v>
+        <v>210</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>60</v>
-      </c>
-      <c t="s" r="K176" s="7">
-        <v>249</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="K176" s="7"/>
       <c r="L176" s="7"/>
-      <c t="s" r="M176" s="7">
-        <v>88</v>
-      </c>
+      <c r="M176" s="7"/>
     </row>
     <row r="177" ht="14.25" customHeight="1">
       <c t="s" r="A177" s="6">
         <v>13</v>
       </c>
       <c r="B177" s="7">
-        <v>422</v>
+        <v>460</v>
       </c>
       <c t="s" r="C177" s="7">
         <v>14</v>
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G177" s="8">
-        <v>103</v>
+        <v>214</v>
       </c>
       <c t="s" r="H177" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I177" s="7">
-        <v>30</v>
+        <v>217</v>
       </c>
       <c t="s" r="J177" s="7">
-        <v>19</v>
-      </c>
-      <c t="s" r="K177" s="7">
-        <v>230</v>
-      </c>
+        <v>248</v>
+      </c>
+      <c r="K177" s="7"/>
       <c r="L177" s="7"/>
-      <c t="s" r="M177" s="7">
-        <v>250</v>
-      </c>
+      <c r="M177" s="7"/>
     </row>
     <row r="178" ht="14.25" customHeight="1">
-      <c t="s" r="A178" s="6">
-        <v>13</v>
-      </c>
-      <c r="B178" s="7">
-        <v>149</v>
-      </c>
-      <c t="s" r="C178" s="7">
-        <v>14</v>
-      </c>
+      <c r="A178" s="6"/>
+      <c r="B178" s="7"/>
+      <c r="C178" s="7"/>
       <c r="D178" s="7"/>
-      <c t="s" r="E178" s="7">
-        <v>247</v>
-      </c>
-      <c r="F178" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G178" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H178" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I178" s="7">
-        <v>244</v>
-      </c>
-      <c t="s" r="J178" s="7">
-        <v>217</v>
-      </c>
-      <c t="s" r="K178" s="7">
-        <v>114</v>
-      </c>
+      <c r="E178" s="7"/>
+      <c r="F178" s="7"/>
+      <c r="G178" s="8"/>
+      <c r="H178" s="8"/>
+      <c r="I178" s="7"/>
+      <c r="J178" s="7"/>
+      <c r="K178" s="7"/>
       <c r="L178" s="7"/>
-      <c t="s" r="M178" s="7">
-        <v>251</v>
-      </c>
+      <c r="M178" s="7"/>
     </row>
     <row r="179" ht="14.25" customHeight="1">
       <c t="s" r="A179" s="6">
         <v>13</v>
       </c>
       <c r="B179" s="7">
-        <v>152</v>
+        <v>925</v>
       </c>
       <c t="s" r="C179" s="7">
         <v>14</v>
       </c>
       <c r="D179" s="7"/>
       <c t="s" r="E179" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F179" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G179" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="H179" s="8">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c t="s" r="I179" s="7">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c t="s" r="J179" s="7">
-        <v>253</v>
+        <v>185</v>
       </c>
       <c r="K179" s="7"/>
       <c r="L179" s="7"/>
@@ -7018,45 +7010,63 @@
         <v>13</v>
       </c>
       <c r="B180" s="7">
-        <v>153</v>
+        <v>671</v>
       </c>
       <c t="s" r="C180" s="7">
         <v>14</v>
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G180" s="8">
-        <v>40</v>
+        <v>125</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>25</v>
+        <v>150</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>194</v>
+        <v>170</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c r="M180" s="7"/>
     </row>
     <row r="181" ht="14.25" customHeight="1">
-      <c r="A181" s="6"/>
-      <c r="B181" s="7"/>
-      <c r="C181" s="7"/>
+      <c t="s" r="A181" s="6">
+        <v>13</v>
+      </c>
+      <c r="B181" s="7">
+        <v>670</v>
+      </c>
+      <c t="s" r="C181" s="7">
+        <v>14</v>
+      </c>
       <c r="D181" s="7"/>
-      <c r="E181" s="7"/>
-      <c r="F181" s="7"/>
-      <c r="G181" s="8"/>
-      <c r="H181" s="8"/>
-      <c r="I181" s="7"/>
-      <c r="J181" s="7"/>
+      <c t="s" r="E181" s="7">
+        <v>249</v>
+      </c>
+      <c r="F181" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G181" s="8">
+        <v>150</v>
+      </c>
+      <c t="s" r="H181" s="8">
+        <v>125</v>
+      </c>
+      <c t="s" r="I181" s="7">
+        <v>224</v>
+      </c>
+      <c t="s" r="J181" s="7">
+        <v>127</v>
+      </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c r="M181" s="7"/>
@@ -7066,29 +7076,29 @@
         <v>13</v>
       </c>
       <c r="B182" s="7">
-        <v>134</v>
+        <v>489</v>
       </c>
       <c t="s" r="C182" s="7">
         <v>14</v>
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>40</v>
+        <v>214</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>256</v>
+        <v>141</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>59</v>
+        <v>142</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7099,63 +7109,45 @@
         <v>13</v>
       </c>
       <c r="B183" s="7">
-        <v>135</v>
+        <v>488</v>
       </c>
       <c t="s" r="C183" s="7">
         <v>14</v>
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>40</v>
+        <v>214</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
       <c r="M183" s="7"/>
     </row>
     <row r="184" ht="14.25" customHeight="1">
-      <c t="s" r="A184" s="6">
-        <v>13</v>
-      </c>
-      <c r="B184" s="7">
-        <v>638</v>
-      </c>
-      <c t="s" r="C184" s="7">
-        <v>14</v>
-      </c>
+      <c r="A184" s="6"/>
+      <c r="B184" s="7"/>
+      <c r="C184" s="7"/>
       <c r="D184" s="7"/>
-      <c t="s" r="E184" s="7">
-        <v>255</v>
-      </c>
-      <c r="F184" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G184" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H184" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I184" s="7">
-        <v>186</v>
-      </c>
-      <c t="s" r="J184" s="7">
-        <v>138</v>
-      </c>
+      <c r="E184" s="7"/>
+      <c r="F184" s="7"/>
+      <c r="G184" s="8"/>
+      <c r="H184" s="8"/>
+      <c r="I184" s="7"/>
+      <c r="J184" s="7"/>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
       <c r="M184" s="7"/>
@@ -7165,113 +7157,125 @@
         <v>13</v>
       </c>
       <c r="B185" s="7">
-        <v>639</v>
+        <v>421</v>
       </c>
       <c t="s" r="C185" s="7">
         <v>14</v>
       </c>
       <c r="D185" s="7"/>
       <c t="s" r="E185" s="7">
+        <v>253</v>
+      </c>
+      <c r="F185" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G185" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H185" s="8">
+        <v>103</v>
+      </c>
+      <c t="s" r="I185" s="7">
+        <v>254</v>
+      </c>
+      <c t="s" r="J185" s="7">
+        <v>137</v>
+      </c>
+      <c t="s" r="K185" s="7">
         <v>255</v>
       </c>
-      <c r="F185" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G185" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H185" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I185" s="7">
-        <v>258</v>
-      </c>
-      <c t="s" r="J185" s="7">
-        <v>259</v>
-      </c>
-      <c r="K185" s="7"/>
       <c r="L185" s="7"/>
-      <c r="M185" s="7"/>
+      <c t="s" r="M185" s="7">
+        <v>88</v>
+      </c>
     </row>
     <row r="186" ht="14.25" customHeight="1">
       <c t="s" r="A186" s="6">
         <v>13</v>
       </c>
       <c r="B186" s="7">
-        <v>262</v>
+        <v>422</v>
       </c>
       <c t="s" r="C186" s="7">
         <v>14</v>
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G186" s="8">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>261</v>
+        <v>30</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>262</v>
-      </c>
-      <c r="K186" s="7"/>
+        <v>19</v>
+      </c>
+      <c t="s" r="K186" s="7">
+        <v>237</v>
+      </c>
       <c r="L186" s="7"/>
-      <c r="M186" s="7"/>
+      <c t="s" r="M186" s="7">
+        <v>256</v>
+      </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
       <c t="s" r="A187" s="6">
         <v>13</v>
       </c>
       <c r="B187" s="7">
-        <v>263</v>
+        <v>149</v>
       </c>
       <c t="s" r="C187" s="7">
         <v>14</v>
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>260</v>
+        <v>40</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I187" s="7">
-        <v>263</v>
+        <v>250</v>
       </c>
       <c t="s" r="J187" s="7">
-        <v>68</v>
-      </c>
-      <c r="K187" s="7"/>
+        <v>224</v>
+      </c>
+      <c t="s" r="K187" s="7">
+        <v>114</v>
+      </c>
       <c r="L187" s="7"/>
-      <c r="M187" s="7"/>
+      <c t="s" r="M187" s="7">
+        <v>257</v>
+      </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
       <c t="s" r="A188" s="6">
         <v>13</v>
       </c>
       <c r="B188" s="7">
-        <v>252</v>
+        <v>152</v>
       </c>
       <c t="s" r="C188" s="7">
         <v>14</v>
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7280,13 +7284,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H188" s="8">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>120</v>
+        <v>149</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>150</v>
+        <v>258</v>
       </c>
       <c r="K188" s="7"/>
       <c r="L188" s="7"/>
@@ -7297,29 +7301,29 @@
         <v>13</v>
       </c>
       <c r="B189" s="7">
-        <v>253</v>
+        <v>153</v>
       </c>
       <c t="s" r="C189" s="7">
         <v>14</v>
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G189" s="8">
-        <v>110</v>
+        <v>40</v>
       </c>
       <c t="s" r="H189" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>83</v>
+        <v>259</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>225</v>
+        <v>204</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7345,29 +7349,29 @@
         <v>13</v>
       </c>
       <c r="B191" s="7">
-        <v>703</v>
+        <v>134</v>
       </c>
       <c t="s" r="C191" s="7">
         <v>14</v>
       </c>
       <c r="D191" s="7"/>
       <c t="s" r="E191" s="7">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F191" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G191" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="H191" s="8">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c t="s" r="I191" s="7">
-        <v>174</v>
+        <v>261</v>
       </c>
       <c t="s" r="J191" s="7">
-        <v>187</v>
+        <v>156</v>
       </c>
       <c r="K191" s="7"/>
       <c r="L191" s="7"/>
@@ -7378,29 +7382,29 @@
         <v>13</v>
       </c>
       <c r="B192" s="7">
-        <v>702</v>
+        <v>135</v>
       </c>
       <c t="s" r="C192" s="7">
         <v>14</v>
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G192" s="8">
-        <v>204</v>
+        <v>40</v>
       </c>
       <c t="s" r="H192" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>251</v>
+        <v>262</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
@@ -7411,29 +7415,29 @@
         <v>13</v>
       </c>
       <c r="B193" s="7">
-        <v>514</v>
+        <v>638</v>
       </c>
       <c t="s" r="C193" s="7">
         <v>14</v>
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G193" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="H193" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>263</v>
+        <v>196</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>45</v>
+        <v>139</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
@@ -7444,29 +7448,29 @@
         <v>13</v>
       </c>
       <c r="B194" s="7">
-        <v>513</v>
+        <v>639</v>
       </c>
       <c t="s" r="C194" s="7">
         <v>14</v>
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
+        <v>260</v>
+      </c>
+      <c r="F194" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G194" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H194" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I194" s="7">
+        <v>263</v>
+      </c>
+      <c t="s" r="J194" s="7">
         <v>264</v>
-      </c>
-      <c r="F194" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G194" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H194" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="I194" s="7">
-        <v>106</v>
-      </c>
-      <c t="s" r="J194" s="7">
-        <v>189</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
@@ -7477,29 +7481,29 @@
         <v>13</v>
       </c>
       <c r="B195" s="7">
-        <v>516</v>
+        <v>262</v>
       </c>
       <c t="s" r="C195" s="7">
         <v>14</v>
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="H195" s="8">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>190</v>
+        <v>266</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>83</v>
+        <v>267</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7510,45 +7514,63 @@
         <v>13</v>
       </c>
       <c r="B196" s="7">
-        <v>1513</v>
+        <v>263</v>
       </c>
       <c t="s" r="C196" s="7">
         <v>14</v>
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G196" s="8">
-        <v>40</v>
+        <v>265</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>84</v>
+        <v>268</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>162</v>
+        <v>69</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
       <c r="M196" s="7"/>
     </row>
     <row r="197" ht="14.25" customHeight="1">
-      <c r="A197" s="6"/>
-      <c r="B197" s="7"/>
-      <c r="C197" s="7"/>
+      <c t="s" r="A197" s="6">
+        <v>13</v>
+      </c>
+      <c r="B197" s="7">
+        <v>252</v>
+      </c>
+      <c t="s" r="C197" s="7">
+        <v>14</v>
+      </c>
       <c r="D197" s="7"/>
-      <c r="E197" s="7"/>
-      <c r="F197" s="7"/>
-      <c r="G197" s="8"/>
-      <c r="H197" s="8"/>
-      <c r="I197" s="7"/>
-      <c r="J197" s="7"/>
+      <c t="s" r="E197" s="7">
+        <v>260</v>
+      </c>
+      <c r="F197" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G197" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H197" s="8">
+        <v>110</v>
+      </c>
+      <c t="s" r="I197" s="7">
+        <v>120</v>
+      </c>
+      <c t="s" r="J197" s="7">
+        <v>153</v>
+      </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
       <c r="M197" s="7"/>
@@ -7558,63 +7580,45 @@
         <v>13</v>
       </c>
       <c r="B198" s="7">
-        <v>637</v>
+        <v>253</v>
       </c>
       <c t="s" r="C198" s="7">
         <v>14</v>
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G198" s="8">
-        <v>67</v>
+        <v>110</v>
       </c>
       <c t="s" r="H198" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>266</v>
+        <v>84</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>172</v>
+        <v>232</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
       <c r="M198" s="7"/>
     </row>
     <row r="199" ht="14.25" customHeight="1">
-      <c t="s" r="A199" s="6">
-        <v>13</v>
-      </c>
-      <c r="B199" s="7">
-        <v>310</v>
-      </c>
-      <c t="s" r="C199" s="7">
-        <v>14</v>
-      </c>
+      <c r="A199" s="6"/>
+      <c r="B199" s="7"/>
+      <c r="C199" s="7"/>
       <c r="D199" s="7"/>
-      <c t="s" r="E199" s="7">
-        <v>265</v>
-      </c>
-      <c r="F199" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G199" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H199" s="8">
-        <v>133</v>
-      </c>
-      <c t="s" r="I199" s="7">
-        <v>239</v>
-      </c>
-      <c t="s" r="J199" s="7">
-        <v>63</v>
-      </c>
+      <c r="E199" s="7"/>
+      <c r="F199" s="7"/>
+      <c r="G199" s="8"/>
+      <c r="H199" s="8"/>
+      <c r="I199" s="7"/>
+      <c r="J199" s="7"/>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
       <c r="M199" s="7"/>
@@ -7624,29 +7628,29 @@
         <v>13</v>
       </c>
       <c r="B200" s="7">
-        <v>309</v>
+        <v>703</v>
       </c>
       <c t="s" r="C200" s="7">
         <v>14</v>
       </c>
       <c r="D200" s="7"/>
       <c t="s" r="E200" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F200" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G200" s="8">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c t="s" r="H200" s="8">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c t="s" r="I200" s="7">
-        <v>21</v>
+        <v>185</v>
       </c>
       <c t="s" r="J200" s="7">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="K200" s="7"/>
       <c r="L200" s="7"/>
@@ -7657,29 +7661,29 @@
         <v>13</v>
       </c>
       <c r="B201" s="7">
-        <v>306</v>
+        <v>702</v>
       </c>
       <c t="s" r="C201" s="7">
         <v>14</v>
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>267</v>
+        <v>186</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>127</v>
+        <v>257</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
@@ -7690,29 +7694,29 @@
         <v>13</v>
       </c>
       <c r="B202" s="7">
-        <v>305</v>
+        <v>514</v>
       </c>
       <c t="s" r="C202" s="7">
         <v>14</v>
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>133</v>
+        <v>68</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>141</v>
+        <v>268</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>33</v>
+        <v>45</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7723,29 +7727,29 @@
         <v>13</v>
       </c>
       <c r="B203" s="7">
-        <v>244</v>
+        <v>513</v>
       </c>
       <c t="s" r="C203" s="7">
         <v>14</v>
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H203" s="8">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>177</v>
+        <v>106</v>
       </c>
       <c t="s" r="J203" s="7">
-        <v>121</v>
+        <v>199</v>
       </c>
       <c r="K203" s="7"/>
       <c r="L203" s="7"/>
@@ -7756,29 +7760,29 @@
         <v>13</v>
       </c>
       <c r="B204" s="7">
-        <v>251</v>
+        <v>516</v>
       </c>
       <c t="s" r="C204" s="7">
         <v>14</v>
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G204" s="8">
-        <v>110</v>
+        <v>68</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>268</v>
+        <v>200</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>210</v>
+        <v>84</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -7789,29 +7793,29 @@
         <v>13</v>
       </c>
       <c r="B205" s="7">
-        <v>132</v>
+        <v>1513</v>
       </c>
       <c t="s" r="C205" s="7">
         <v>14</v>
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H205" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>269</v>
+        <v>85</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>52</v>
+        <v>164</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -7837,7 +7841,7 @@
         <v>13</v>
       </c>
       <c r="B207" s="7">
-        <v>991</v>
+        <v>137</v>
       </c>
       <c t="s" r="C207" s="7">
         <v>14</v>
@@ -7850,16 +7854,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G207" s="8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c t="s" r="H207" s="8">
-        <v>222</v>
+        <v>25</v>
       </c>
       <c t="s" r="I207" s="7">
-        <v>18</v>
+        <v>271</v>
       </c>
       <c t="s" r="J207" s="7">
-        <v>271</v>
+        <v>183</v>
       </c>
       <c r="K207" s="7"/>
       <c r="L207" s="7"/>
@@ -7870,7 +7874,7 @@
         <v>13</v>
       </c>
       <c r="B208" s="7">
-        <v>730</v>
+        <v>148</v>
       </c>
       <c t="s" r="C208" s="7">
         <v>14</v>
@@ -7883,31 +7887,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G208" s="8">
-        <v>222</v>
+        <v>25</v>
       </c>
       <c t="s" r="H208" s="8">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>62</v>
+        <v>42</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>175</v>
-      </c>
-      <c t="s" r="K208" s="7">
-        <v>272</v>
-      </c>
+        <v>146</v>
+      </c>
+      <c r="K208" s="7"/>
       <c r="L208" s="7"/>
-      <c t="s" r="M208" s="7">
-        <v>208</v>
-      </c>
+      <c r="M208" s="7"/>
     </row>
     <row r="209" ht="14.25" customHeight="1">
       <c t="s" r="A209" s="6">
         <v>13</v>
       </c>
       <c r="B209" s="7">
-        <v>731</v>
+        <v>441</v>
       </c>
       <c t="s" r="C209" s="7">
         <v>14</v>
@@ -7920,31 +7920,27 @@
         <v>321</v>
       </c>
       <c t="s" r="G209" s="8">
-        <v>125</v>
+        <v>40</v>
       </c>
       <c t="s" r="H209" s="8">
-        <v>222</v>
+        <v>17</v>
       </c>
       <c t="s" r="I209" s="7">
-        <v>91</v>
+        <v>62</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>78</v>
-      </c>
-      <c t="s" r="K209" s="7">
-        <v>217</v>
-      </c>
+        <v>140</v>
+      </c>
+      <c r="K209" s="7"/>
       <c r="L209" s="7"/>
-      <c t="s" r="M209" s="7">
-        <v>188</v>
-      </c>
+      <c r="M209" s="7"/>
     </row>
     <row r="210" ht="15" customHeight="1">
       <c t="s" r="A210" s="6">
         <v>13</v>
       </c>
       <c r="B210" s="7">
-        <v>601</v>
+        <v>442</v>
       </c>
       <c t="s" r="C210" s="7">
         <v>14</v>
@@ -7957,16 +7953,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G210" s="8">
-        <v>222</v>
+        <v>17</v>
       </c>
       <c t="s" r="H210" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>80</v>
+        <v>191</v>
       </c>
       <c t="s" r="J210" s="7">
-        <v>119</v>
+        <v>258</v>
       </c>
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
@@ -7977,7 +7973,7 @@
         <v>13</v>
       </c>
       <c r="B211" s="7">
-        <v>280</v>
+        <v>1409</v>
       </c>
       <c t="s" r="C211" s="7">
         <v>14</v>
@@ -7990,16 +7986,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G211" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H211" s="8">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8010,7 +8006,7 @@
         <v>13</v>
       </c>
       <c r="B212" s="7">
-        <v>281</v>
+        <v>1410</v>
       </c>
       <c t="s" r="C212" s="7">
         <v>14</v>
@@ -8023,16 +8019,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G212" s="8">
-        <v>125</v>
+        <v>46</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I212" s="7">
-        <v>70</v>
+        <v>144</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8058,29 +8054,29 @@
         <v>13</v>
       </c>
       <c r="B214" s="7">
-        <v>308</v>
+        <v>991</v>
       </c>
       <c t="s" r="C214" s="7">
         <v>14</v>
       </c>
       <c r="D214" s="7"/>
       <c t="s" r="E214" s="7">
+        <v>273</v>
+      </c>
+      <c r="F214" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G214" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="H214" s="8">
+        <v>229</v>
+      </c>
+      <c t="s" r="I214" s="7">
+        <v>18</v>
+      </c>
+      <c t="s" r="J214" s="7">
         <v>274</v>
-      </c>
-      <c r="F214" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G214" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H214" s="8">
-        <v>133</v>
-      </c>
-      <c t="s" r="I214" s="7">
-        <v>59</v>
-      </c>
-      <c t="s" r="J214" s="7">
-        <v>112</v>
       </c>
       <c r="K214" s="7"/>
       <c r="L214" s="7"/>
@@ -8091,95 +8087,103 @@
         <v>13</v>
       </c>
       <c r="B215" s="7">
-        <v>307</v>
+        <v>730</v>
       </c>
       <c t="s" r="C215" s="7">
         <v>14</v>
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G215" s="8">
-        <v>133</v>
+        <v>229</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c t="s" r="I215" s="7">
-        <v>113</v>
+        <v>157</v>
       </c>
       <c t="s" r="J215" s="7">
         <v>186</v>
       </c>
-      <c r="K215" s="7"/>
+      <c t="s" r="K215" s="7">
+        <v>275</v>
+      </c>
       <c r="L215" s="7"/>
-      <c r="M215" s="7"/>
+      <c t="s" r="M215" s="7">
+        <v>170</v>
+      </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
       <c t="s" r="A216" s="6">
         <v>13</v>
       </c>
       <c r="B216" s="7">
-        <v>803</v>
+        <v>731</v>
       </c>
       <c t="s" r="C216" s="7">
         <v>14</v>
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>25</v>
+        <v>125</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c t="s" r="I216" s="7">
-        <v>207</v>
+        <v>91</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>43</v>
-      </c>
-      <c r="K216" s="7"/>
+        <v>65</v>
+      </c>
+      <c t="s" r="K216" s="7">
+        <v>224</v>
+      </c>
       <c r="L216" s="7"/>
-      <c r="M216" s="7"/>
+      <c t="s" r="M216" s="7">
+        <v>198</v>
+      </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
       <c t="s" r="A217" s="6">
         <v>13</v>
       </c>
       <c r="B217" s="7">
-        <v>804</v>
+        <v>601</v>
       </c>
       <c t="s" r="C217" s="7">
         <v>14</v>
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>87</v>
+        <v>229</v>
       </c>
       <c t="s" r="H217" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>44</v>
+        <v>81</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="K217" s="7"/>
       <c r="L217" s="7"/>
@@ -8190,14 +8194,14 @@
         <v>13</v>
       </c>
       <c r="B218" s="7">
-        <v>362</v>
+        <v>280</v>
       </c>
       <c t="s" r="C218" s="7">
         <v>14</v>
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8206,13 +8210,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H218" s="8">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>262</v>
+        <v>26</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>80</v>
+        <v>276</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8223,63 +8227,45 @@
         <v>13</v>
       </c>
       <c r="B219" s="7">
-        <v>363</v>
+        <v>281</v>
       </c>
       <c t="s" r="C219" s="7">
         <v>14</v>
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G219" s="8">
-        <v>46</v>
+        <v>125</v>
       </c>
       <c t="s" r="H219" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I219" s="7">
-        <v>275</v>
+        <v>71</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
       <c r="M219" s="7"/>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c t="s" r="A220" s="6">
-        <v>13</v>
-      </c>
-      <c r="B220" s="7">
-        <v>224</v>
-      </c>
-      <c t="s" r="C220" s="7">
-        <v>14</v>
-      </c>
+      <c r="A220" s="6"/>
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
       <c r="D220" s="7"/>
-      <c t="s" r="E220" s="7">
-        <v>274</v>
-      </c>
-      <c r="F220" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G220" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H220" s="8">
-        <v>58</v>
-      </c>
-      <c t="s" r="I220" s="7">
-        <v>276</v>
-      </c>
-      <c t="s" r="J220" s="7">
-        <v>277</v>
-      </c>
+      <c r="E220" s="7"/>
+      <c r="F220" s="7"/>
+      <c r="G220" s="8"/>
+      <c r="H220" s="8"/>
+      <c r="I220" s="7"/>
+      <c r="J220" s="7"/>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
       <c r="M220" s="7"/>
@@ -8289,45 +8275,63 @@
         <v>13</v>
       </c>
       <c r="B221" s="7">
-        <v>225</v>
+        <v>308</v>
       </c>
       <c t="s" r="C221" s="7">
         <v>14</v>
       </c>
       <c r="D221" s="7"/>
       <c t="s" r="E221" s="7">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="F221" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G221" s="8">
-        <v>58</v>
+        <v>25</v>
       </c>
       <c t="s" r="H221" s="8">
-        <v>25</v>
+        <v>133</v>
       </c>
       <c t="s" r="I221" s="7">
-        <v>278</v>
+        <v>156</v>
       </c>
       <c t="s" r="J221" s="7">
-        <v>279</v>
+        <v>112</v>
       </c>
       <c r="K221" s="7"/>
       <c r="L221" s="7"/>
       <c r="M221" s="7"/>
     </row>
     <row r="222" ht="14.25" customHeight="1">
-      <c r="A222" s="6"/>
-      <c r="B222" s="7"/>
-      <c r="C222" s="7"/>
+      <c t="s" r="A222" s="6">
+        <v>13</v>
+      </c>
+      <c r="B222" s="7">
+        <v>307</v>
+      </c>
+      <c t="s" r="C222" s="7">
+        <v>14</v>
+      </c>
       <c r="D222" s="7"/>
-      <c r="E222" s="7"/>
-      <c r="F222" s="7"/>
-      <c r="G222" s="8"/>
-      <c r="H222" s="8"/>
-      <c r="I222" s="7"/>
-      <c r="J222" s="7"/>
+      <c t="s" r="E222" s="7">
+        <v>277</v>
+      </c>
+      <c r="F222" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G222" s="8">
+        <v>133</v>
+      </c>
+      <c t="s" r="H222" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I222" s="7">
+        <v>113</v>
+      </c>
+      <c t="s" r="J222" s="7">
+        <v>196</v>
+      </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c r="M222" s="7"/>
@@ -8337,29 +8341,29 @@
         <v>13</v>
       </c>
       <c r="B223" s="7">
-        <v>125</v>
+        <v>803</v>
       </c>
       <c t="s" r="C223" s="7">
         <v>14</v>
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="H223" s="8">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>174</v>
+        <v>148</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>64</v>
+        <v>43</v>
       </c>
       <c r="K223" s="7"/>
       <c r="L223" s="7"/>
@@ -8370,26 +8374,26 @@
         <v>13</v>
       </c>
       <c r="B224" s="7">
-        <v>124</v>
+        <v>804</v>
       </c>
       <c t="s" r="C224" s="7">
         <v>14</v>
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G224" s="8">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c t="s" r="H224" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>208</v>
+        <v>44</v>
       </c>
       <c t="s" r="J224" s="7">
         <v>127</v>
@@ -8403,29 +8407,29 @@
         <v>13</v>
       </c>
       <c r="B225" s="7">
-        <v>913</v>
+        <v>362</v>
       </c>
       <c t="s" r="C225" s="7">
         <v>14</v>
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G225" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="H225" s="8">
-        <v>281</v>
+        <v>46</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>142</v>
+        <v>81</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8436,29 +8440,29 @@
         <v>13</v>
       </c>
       <c r="B226" s="7">
-        <v>914</v>
+        <v>363</v>
       </c>
       <c t="s" r="C226" s="7">
         <v>14</v>
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G226" s="8">
-        <v>281</v>
+        <v>46</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>81</v>
+        <v>278</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>282</v>
+        <v>143</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8469,29 +8473,29 @@
         <v>13</v>
       </c>
       <c r="B227" s="7">
-        <v>6034</v>
+        <v>224</v>
       </c>
       <c t="s" r="C227" s="7">
         <v>14</v>
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
+        <v>277</v>
+      </c>
+      <c r="F227" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G227" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H227" s="8">
+        <v>79</v>
+      </c>
+      <c t="s" r="I227" s="7">
+        <v>279</v>
+      </c>
+      <c t="s" r="J227" s="7">
         <v>280</v>
-      </c>
-      <c r="F227" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G227" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H227" s="8">
-        <v>283</v>
-      </c>
-      <c t="s" r="I227" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="J227" s="7">
-        <v>284</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8499,32 +8503,32 @@
     </row>
     <row r="228" ht="14.25" customHeight="1">
       <c t="s" r="A228" s="6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B228" s="7">
-        <v>6035</v>
+        <v>225</v>
       </c>
       <c t="s" r="C228" s="7">
         <v>14</v>
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G228" s="8">
-        <v>283</v>
+        <v>79</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8550,29 +8554,29 @@
         <v>13</v>
       </c>
       <c r="B230" s="7">
-        <v>989</v>
+        <v>125</v>
       </c>
       <c t="s" r="C230" s="7">
         <v>14</v>
       </c>
       <c r="D230" s="7"/>
       <c t="s" r="E230" s="7">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F230" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G230" s="8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c t="s" r="H230" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="I230" s="7">
-        <v>108</v>
+        <v>185</v>
       </c>
       <c t="s" r="J230" s="7">
-        <v>126</v>
+        <v>159</v>
       </c>
       <c r="K230" s="7"/>
       <c r="L230" s="7"/>
@@ -8583,29 +8587,29 @@
         <v>13</v>
       </c>
       <c r="B231" s="7">
-        <v>5884</v>
+        <v>124</v>
       </c>
       <c t="s" r="C231" s="7">
         <v>14</v>
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G231" s="8">
-        <v>67</v>
+        <v>25</v>
       </c>
       <c t="s" r="H231" s="8">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>44</v>
+        <v>170</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>262</v>
+        <v>127</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
@@ -8616,29 +8620,29 @@
         <v>13</v>
       </c>
       <c r="B232" s="7">
-        <v>5885</v>
+        <v>913</v>
       </c>
       <c t="s" r="C232" s="7">
         <v>14</v>
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G232" s="8">
-        <v>231</v>
+        <v>40</v>
       </c>
       <c t="s" r="H232" s="8">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>200</v>
+        <v>267</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>288</v>
+        <v>142</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8646,114 +8650,114 @@
     </row>
     <row r="233" ht="14.25" customHeight="1">
       <c t="s" r="A233" s="6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B233" s="7">
-        <v>988</v>
+        <v>914</v>
       </c>
       <c t="s" r="C233" s="7">
         <v>14</v>
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G233" s="8">
-        <v>67</v>
+        <v>284</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>16</v>
+        <v>40</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>289</v>
+        <v>82</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>154</v>
+        <v>285</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
       <c r="M233" s="7"/>
     </row>
     <row r="234" ht="14.25" customHeight="1">
-      <c r="A234" s="6"/>
-      <c r="B234" s="7"/>
-      <c r="C234" s="7"/>
+      <c t="s" r="A234" s="6">
+        <v>13</v>
+      </c>
+      <c r="B234" s="7">
+        <v>6034</v>
+      </c>
+      <c t="s" r="C234" s="7">
+        <v>14</v>
+      </c>
       <c r="D234" s="7"/>
-      <c r="E234" s="7"/>
-      <c r="F234" s="7"/>
-      <c r="G234" s="8"/>
-      <c r="H234" s="8"/>
-      <c r="I234" s="7"/>
-      <c r="J234" s="7"/>
+      <c t="s" r="E234" s="7">
+        <v>283</v>
+      </c>
+      <c r="F234" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G234" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H234" s="8">
+        <v>286</v>
+      </c>
+      <c t="s" r="I234" s="7">
+        <v>179</v>
+      </c>
+      <c t="s" r="J234" s="7">
+        <v>287</v>
+      </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
       <c r="M234" s="7"/>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c t="s" r="A235" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B235" s="7">
-        <v>961</v>
+        <v>6035</v>
       </c>
       <c t="s" r="C235" s="7">
         <v>14</v>
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G235" s="8">
-        <v>34</v>
+        <v>286</v>
       </c>
       <c t="s" r="H235" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>19</v>
+        <v>288</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>251</v>
+        <v>289</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
       <c r="M235" s="7"/>
     </row>
     <row r="236" ht="14.25" customHeight="1">
-      <c t="s" r="A236" s="6">
-        <v>13</v>
-      </c>
-      <c r="B236" s="7">
-        <v>465</v>
-      </c>
-      <c t="s" r="C236" s="7">
-        <v>14</v>
-      </c>
+      <c r="A236" s="6"/>
+      <c r="B236" s="7"/>
+      <c r="C236" s="7"/>
       <c r="D236" s="7"/>
-      <c t="s" r="E236" s="7">
-        <v>290</v>
-      </c>
-      <c r="F236" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G236" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H236" s="8">
-        <v>204</v>
-      </c>
-      <c t="s" r="I236" s="7">
-        <v>176</v>
-      </c>
-      <c t="s" r="J236" s="7">
-        <v>200</v>
-      </c>
+      <c r="E236" s="7"/>
+      <c r="F236" s="7"/>
+      <c r="G236" s="8"/>
+      <c r="H236" s="8"/>
+      <c r="I236" s="7"/>
+      <c r="J236" s="7"/>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
       <c r="M236" s="7"/>
@@ -8763,7 +8767,7 @@
         <v>13</v>
       </c>
       <c r="B237" s="7">
-        <v>464</v>
+        <v>989</v>
       </c>
       <c t="s" r="C237" s="7">
         <v>14</v>
@@ -8776,16 +8780,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G237" s="8">
-        <v>204</v>
+        <v>16</v>
       </c>
       <c t="s" r="H237" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="I237" s="7">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c t="s" r="J237" s="7">
-        <v>209</v>
+        <v>126</v>
       </c>
       <c r="K237" s="7"/>
       <c r="L237" s="7"/>
@@ -8796,7 +8800,7 @@
         <v>13</v>
       </c>
       <c r="B238" s="7">
-        <v>133</v>
+        <v>5884</v>
       </c>
       <c t="s" r="C238" s="7">
         <v>14</v>
@@ -8809,98 +8813,98 @@
         <v>321</v>
       </c>
       <c t="s" r="G238" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>25</v>
+        <v>238</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>268</v>
+        <v>44</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c r="M238" s="7"/>
     </row>
     <row r="239" ht="14.25" customHeight="1">
-      <c r="A239" s="6"/>
-      <c r="B239" s="7"/>
-      <c r="C239" s="7"/>
+      <c t="s" r="A239" s="6">
+        <v>13</v>
+      </c>
+      <c r="B239" s="7">
+        <v>5885</v>
+      </c>
+      <c t="s" r="C239" s="7">
+        <v>14</v>
+      </c>
       <c r="D239" s="7"/>
-      <c r="E239" s="7"/>
-      <c r="F239" s="7"/>
-      <c r="G239" s="8"/>
-      <c r="H239" s="8"/>
-      <c r="I239" s="7"/>
-      <c r="J239" s="7"/>
+      <c t="s" r="E239" s="7">
+        <v>290</v>
+      </c>
+      <c r="F239" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G239" s="8">
+        <v>238</v>
+      </c>
+      <c t="s" r="H239" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="I239" s="7">
+        <v>210</v>
+      </c>
+      <c t="s" r="J239" s="7">
+        <v>291</v>
+      </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c r="M239" s="7"/>
     </row>
     <row r="240" ht="15" customHeight="1">
       <c t="s" r="A240" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B240" s="7">
-        <v>809</v>
+        <v>988</v>
       </c>
       <c t="s" r="C240" s="7">
         <v>14</v>
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
+        <v>290</v>
+      </c>
+      <c r="F240" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G240" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H240" s="8">
+        <v>16</v>
+      </c>
+      <c t="s" r="I240" s="7">
         <v>292</v>
       </c>
-      <c r="F240" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G240" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H240" s="8">
-        <v>293</v>
-      </c>
-      <c t="s" r="I240" s="7">
-        <v>156</v>
-      </c>
       <c t="s" r="J240" s="7">
-        <v>91</v>
+        <v>59</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
       <c r="M240" s="7"/>
     </row>
     <row r="241" ht="14.25" customHeight="1">
-      <c t="s" r="A241" s="6">
-        <v>13</v>
-      </c>
-      <c r="B241" s="7">
-        <v>808</v>
-      </c>
-      <c t="s" r="C241" s="7">
-        <v>14</v>
-      </c>
+      <c r="A241" s="6"/>
+      <c r="B241" s="7"/>
+      <c r="C241" s="7"/>
       <c r="D241" s="7"/>
-      <c t="s" r="E241" s="7">
-        <v>292</v>
-      </c>
-      <c r="F241" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G241" s="8">
-        <v>293</v>
-      </c>
-      <c t="s" r="H241" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I241" s="7">
-        <v>251</v>
-      </c>
-      <c t="s" r="J241" s="7">
-        <v>158</v>
-      </c>
+      <c r="E241" s="7"/>
+      <c r="F241" s="7"/>
+      <c r="G241" s="8"/>
+      <c r="H241" s="8"/>
+      <c r="I241" s="7"/>
+      <c r="J241" s="7"/>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
       <c r="M241" s="7"/>
@@ -8910,29 +8914,29 @@
         <v>13</v>
       </c>
       <c r="B242" s="7">
-        <v>154</v>
+        <v>961</v>
       </c>
       <c t="s" r="C242" s="7">
         <v>14</v>
       </c>
       <c r="D242" s="7"/>
       <c t="s" r="E242" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F242" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G242" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="H242" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I242" s="7">
-        <v>288</v>
+        <v>19</v>
       </c>
       <c t="s" r="J242" s="7">
-        <v>27</v>
+        <v>257</v>
       </c>
       <c r="K242" s="7"/>
       <c r="L242" s="7"/>
@@ -8943,14 +8947,14 @@
         <v>13</v>
       </c>
       <c r="B243" s="7">
-        <v>155</v>
+        <v>465</v>
       </c>
       <c t="s" r="C243" s="7">
         <v>14</v>
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -8959,29 +8963,47 @@
         <v>40</v>
       </c>
       <c t="s" r="H243" s="8">
-        <v>25</v>
+        <v>214</v>
       </c>
       <c t="s" r="I243" s="7">
-        <v>282</v>
+        <v>187</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>294</v>
+        <v>210</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c r="M243" s="7"/>
     </row>
     <row r="244" ht="14.25" customHeight="1">
-      <c r="A244" s="6"/>
-      <c r="B244" s="7"/>
-      <c r="C244" s="7"/>
+      <c t="s" r="A244" s="6">
+        <v>13</v>
+      </c>
+      <c r="B244" s="7">
+        <v>464</v>
+      </c>
+      <c t="s" r="C244" s="7">
+        <v>14</v>
+      </c>
       <c r="D244" s="7"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="7"/>
-      <c r="G244" s="8"/>
-      <c r="H244" s="8"/>
-      <c r="I244" s="7"/>
-      <c r="J244" s="7"/>
+      <c t="s" r="E244" s="7">
+        <v>293</v>
+      </c>
+      <c r="F244" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G244" s="8">
+        <v>214</v>
+      </c>
+      <c t="s" r="H244" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I244" s="7">
+        <v>118</v>
+      </c>
+      <c t="s" r="J244" s="7">
+        <v>217</v>
+      </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
       <c r="M244" s="7"/>
@@ -8991,63 +9013,45 @@
         <v>13</v>
       </c>
       <c r="B245" s="7">
-        <v>329</v>
+        <v>133</v>
       </c>
       <c t="s" r="C245" s="7">
         <v>14</v>
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H245" s="8">
-        <v>17</v>
+        <v>25</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>154</v>
+        <v>173</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>73</v>
+        <v>294</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
       <c r="M245" s="7"/>
     </row>
     <row r="246" ht="14.25" customHeight="1">
-      <c t="s" r="A246" s="6">
-        <v>13</v>
-      </c>
-      <c r="B246" s="7">
-        <v>844</v>
-      </c>
-      <c t="s" r="C246" s="7">
-        <v>14</v>
-      </c>
+      <c r="A246" s="6"/>
+      <c r="B246" s="7"/>
+      <c r="C246" s="7"/>
       <c r="D246" s="7"/>
-      <c t="s" r="E246" s="7">
-        <v>295</v>
-      </c>
-      <c r="F246" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G246" s="8">
-        <v>17</v>
-      </c>
-      <c t="s" r="H246" s="8">
-        <v>296</v>
-      </c>
-      <c t="s" r="I246" s="7">
-        <v>206</v>
-      </c>
-      <c t="s" r="J246" s="7">
-        <v>157</v>
-      </c>
+      <c r="E246" s="7"/>
+      <c r="F246" s="7"/>
+      <c r="G246" s="8"/>
+      <c r="H246" s="8"/>
+      <c r="I246" s="7"/>
+      <c r="J246" s="7"/>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
       <c r="M246" s="7"/>
@@ -9057,7 +9061,7 @@
         <v>13</v>
       </c>
       <c r="B247" s="7">
-        <v>845</v>
+        <v>809</v>
       </c>
       <c t="s" r="C247" s="7">
         <v>14</v>
@@ -9070,16 +9074,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G247" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H247" s="8">
         <v>296</v>
       </c>
-      <c t="s" r="H247" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I247" s="7">
-        <v>92</v>
+        <v>61</v>
       </c>
       <c t="s" r="J247" s="7">
-        <v>80</v>
+        <v>91</v>
       </c>
       <c r="K247" s="7"/>
       <c r="L247" s="7"/>
@@ -9090,7 +9094,7 @@
         <v>13</v>
       </c>
       <c r="B248" s="7">
-        <v>440</v>
+        <v>808</v>
       </c>
       <c t="s" r="C248" s="7">
         <v>14</v>
@@ -9103,32 +9107,50 @@
         <v>321</v>
       </c>
       <c t="s" r="G248" s="8">
-        <v>17</v>
+        <v>296</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>161</v>
+        <v>66</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c r="M248" s="7"/>
     </row>
     <row r="249" ht="14.25" customHeight="1">
-      <c r="A249" s="6"/>
-      <c r="B249" s="7"/>
-      <c r="C249" s="7"/>
+      <c t="s" r="A249" s="6">
+        <v>13</v>
+      </c>
+      <c r="B249" s="7">
+        <v>154</v>
+      </c>
+      <c t="s" r="C249" s="7">
+        <v>14</v>
+      </c>
       <c r="D249" s="7"/>
-      <c r="E249" s="7"/>
-      <c r="F249" s="7"/>
-      <c r="G249" s="8"/>
-      <c r="H249" s="8"/>
-      <c r="I249" s="7"/>
-      <c r="J249" s="7"/>
+      <c t="s" r="E249" s="7">
+        <v>295</v>
+      </c>
+      <c r="F249" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G249" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H249" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I249" s="7">
+        <v>291</v>
+      </c>
+      <c t="s" r="J249" s="7">
+        <v>27</v>
+      </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c r="M249" s="7"/>
@@ -9138,63 +9160,45 @@
         <v>13</v>
       </c>
       <c r="B250" s="7">
-        <v>774</v>
+        <v>155</v>
       </c>
       <c t="s" r="C250" s="7">
         <v>14</v>
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
+        <v>295</v>
+      </c>
+      <c r="F250" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G250" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H250" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="I250" s="7">
+        <v>285</v>
+      </c>
+      <c t="s" r="J250" s="7">
         <v>297</v>
-      </c>
-      <c r="F250" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G250" s="8">
-        <v>222</v>
-      </c>
-      <c t="s" r="H250" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I250" s="7">
-        <v>115</v>
-      </c>
-      <c t="s" r="J250" s="7">
-        <v>127</v>
       </c>
       <c r="K250" s="7"/>
       <c r="L250" s="7"/>
       <c r="M250" s="7"/>
     </row>
     <row r="251" ht="14.25" customHeight="1">
-      <c t="s" r="A251" s="6">
-        <v>13</v>
-      </c>
-      <c r="B251" s="7">
-        <v>771</v>
-      </c>
-      <c t="s" r="C251" s="7">
-        <v>14</v>
-      </c>
+      <c r="A251" s="6"/>
+      <c r="B251" s="7"/>
+      <c r="C251" s="7"/>
       <c r="D251" s="7"/>
-      <c t="s" r="E251" s="7">
-        <v>297</v>
-      </c>
-      <c r="F251" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G251" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H251" s="8">
-        <v>222</v>
-      </c>
-      <c t="s" r="I251" s="7">
-        <v>158</v>
-      </c>
-      <c t="s" r="J251" s="7">
-        <v>177</v>
-      </c>
+      <c r="E251" s="7"/>
+      <c r="F251" s="7"/>
+      <c r="G251" s="8"/>
+      <c r="H251" s="8"/>
+      <c r="I251" s="7"/>
+      <c r="J251" s="7"/>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
       <c r="M251" s="7"/>
@@ -9204,45 +9208,63 @@
         <v>13</v>
       </c>
       <c r="B252" s="7">
-        <v>770</v>
+        <v>329</v>
       </c>
       <c t="s" r="C252" s="7">
         <v>14</v>
       </c>
       <c r="D252" s="7"/>
       <c t="s" r="E252" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F252" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G252" s="8">
-        <v>222</v>
+        <v>25</v>
       </c>
       <c t="s" r="H252" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="I252" s="7">
-        <v>24</v>
+        <v>59</v>
       </c>
       <c t="s" r="J252" s="7">
-        <v>298</v>
+        <v>74</v>
       </c>
       <c r="K252" s="7"/>
       <c r="L252" s="7"/>
       <c r="M252" s="7"/>
     </row>
     <row r="253" ht="14.25" customHeight="1">
-      <c r="A253" s="6"/>
-      <c r="B253" s="7"/>
-      <c r="C253" s="7"/>
+      <c t="s" r="A253" s="6">
+        <v>13</v>
+      </c>
+      <c r="B253" s="7">
+        <v>844</v>
+      </c>
+      <c t="s" r="C253" s="7">
+        <v>14</v>
+      </c>
       <c r="D253" s="7"/>
-      <c r="E253" s="7"/>
-      <c r="F253" s="7"/>
-      <c r="G253" s="8"/>
-      <c r="H253" s="8"/>
-      <c r="I253" s="7"/>
-      <c r="J253" s="7"/>
+      <c t="s" r="E253" s="7">
+        <v>298</v>
+      </c>
+      <c r="F253" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G253" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H253" s="8">
+        <v>299</v>
+      </c>
+      <c t="s" r="I253" s="7">
+        <v>216</v>
+      </c>
+      <c t="s" r="J253" s="7">
+        <v>64</v>
+      </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c r="M253" s="7"/>
@@ -9252,29 +9274,29 @@
         <v>13</v>
       </c>
       <c r="B254" s="7">
-        <v>1502</v>
+        <v>845</v>
       </c>
       <c t="s" r="C254" s="7">
         <v>14</v>
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
+        <v>298</v>
+      </c>
+      <c r="F254" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G254" s="8">
         <v>299</v>
       </c>
-      <c r="F254" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G254" s="8">
-        <v>67</v>
-      </c>
       <c t="s" r="H254" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>163</v>
+        <v>92</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>196</v>
+        <v>81</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
@@ -9285,63 +9307,45 @@
         <v>13</v>
       </c>
       <c r="B255" s="7">
-        <v>501</v>
+        <v>440</v>
       </c>
       <c t="s" r="C255" s="7">
         <v>14</v>
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c t="s" r="H255" s="8">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>206</v>
+        <v>163</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
       <c r="M255" s="7"/>
     </row>
     <row r="256" ht="14.25" customHeight="1">
-      <c t="s" r="A256" s="6">
-        <v>13</v>
-      </c>
-      <c r="B256" s="7">
-        <v>510</v>
-      </c>
-      <c t="s" r="C256" s="7">
-        <v>14</v>
-      </c>
+      <c r="A256" s="6"/>
+      <c r="B256" s="7"/>
+      <c r="C256" s="7"/>
       <c r="D256" s="7"/>
-      <c t="s" r="E256" s="7">
-        <v>299</v>
-      </c>
-      <c r="F256" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G256" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H256" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I256" s="7">
-        <v>165</v>
-      </c>
-      <c t="s" r="J256" s="7">
-        <v>174</v>
-      </c>
+      <c r="E256" s="7"/>
+      <c r="F256" s="7"/>
+      <c r="G256" s="8"/>
+      <c r="H256" s="8"/>
+      <c r="I256" s="7"/>
+      <c r="J256" s="7"/>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
       <c r="M256" s="7"/>
@@ -9351,29 +9355,29 @@
         <v>13</v>
       </c>
       <c r="B257" s="7">
-        <v>509</v>
+        <v>774</v>
       </c>
       <c t="s" r="C257" s="7">
         <v>14</v>
       </c>
       <c r="D257" s="7"/>
       <c t="s" r="E257" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F257" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G257" s="8">
-        <v>40</v>
+        <v>229</v>
       </c>
       <c t="s" r="H257" s="8">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c t="s" r="I257" s="7">
-        <v>300</v>
+        <v>115</v>
       </c>
       <c t="s" r="J257" s="7">
-        <v>301</v>
+        <v>127</v>
       </c>
       <c r="K257" s="7"/>
       <c r="L257" s="7"/>
@@ -9384,29 +9388,29 @@
         <v>13</v>
       </c>
       <c r="B258" s="7">
-        <v>512</v>
+        <v>771</v>
       </c>
       <c t="s" r="C258" s="7">
         <v>14</v>
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c t="s" r="H258" s="8">
-        <v>40</v>
+        <v>229</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>302</v>
+        <v>66</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>303</v>
+        <v>172</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9417,78 +9421,78 @@
         <v>13</v>
       </c>
       <c r="B259" s="7">
-        <v>511</v>
+        <v>770</v>
       </c>
       <c t="s" r="C259" s="7">
         <v>14</v>
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G259" s="8">
-        <v>40</v>
+        <v>229</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>67</v>
+        <v>40</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>181</v>
+        <v>24</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>32</v>
+        <v>272</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
       <c r="M259" s="7"/>
     </row>
     <row r="260" ht="15" customHeight="1">
-      <c t="s" r="A260" s="6">
-        <v>13</v>
-      </c>
-      <c r="B260" s="7">
-        <v>878</v>
-      </c>
-      <c t="s" r="C260" s="7">
-        <v>14</v>
-      </c>
+      <c r="A260" s="6"/>
+      <c r="B260" s="7"/>
+      <c r="C260" s="7"/>
       <c r="D260" s="7"/>
-      <c t="s" r="E260" s="7">
-        <v>299</v>
-      </c>
-      <c r="F260" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G260" s="8">
-        <v>67</v>
-      </c>
-      <c t="s" r="H260" s="8">
-        <v>34</v>
-      </c>
-      <c t="s" r="I260" s="7">
-        <v>167</v>
-      </c>
-      <c t="s" r="J260" s="7">
-        <v>134</v>
-      </c>
+      <c r="E260" s="7"/>
+      <c r="F260" s="7"/>
+      <c r="G260" s="8"/>
+      <c r="H260" s="8"/>
+      <c r="I260" s="7"/>
+      <c r="J260" s="7"/>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
       <c r="M260" s="7"/>
     </row>
     <row r="261" ht="14.25" customHeight="1">
-      <c r="A261" s="6"/>
-      <c r="B261" s="7"/>
-      <c r="C261" s="7"/>
+      <c t="s" r="A261" s="6">
+        <v>13</v>
+      </c>
+      <c r="B261" s="7">
+        <v>1502</v>
+      </c>
+      <c t="s" r="C261" s="7">
+        <v>14</v>
+      </c>
       <c r="D261" s="7"/>
-      <c r="E261" s="7"/>
-      <c r="F261" s="7"/>
-      <c r="G261" s="8"/>
-      <c r="H261" s="8"/>
-      <c r="I261" s="7"/>
-      <c r="J261" s="7"/>
+      <c t="s" r="E261" s="7">
+        <v>301</v>
+      </c>
+      <c r="F261" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G261" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H261" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I261" s="7">
+        <v>165</v>
+      </c>
+      <c t="s" r="J261" s="7">
+        <v>206</v>
+      </c>
       <c r="K261" s="7"/>
       <c r="L261" s="7"/>
       <c r="M261" s="7"/>
@@ -9498,29 +9502,29 @@
         <v>13</v>
       </c>
       <c r="B262" s="7">
-        <v>825</v>
+        <v>501</v>
       </c>
       <c t="s" r="C262" s="7">
         <v>14</v>
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H262" s="8">
-        <v>305</v>
+        <v>68</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>137</v>
+        <v>195</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>306</v>
+        <v>216</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
@@ -9531,29 +9535,29 @@
         <v>13</v>
       </c>
       <c r="B263" s="7">
-        <v>826</v>
+        <v>510</v>
       </c>
       <c t="s" r="C263" s="7">
         <v>14</v>
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G263" s="8">
-        <v>305</v>
+        <v>68</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>240</v>
+        <v>177</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>140</v>
+        <v>185</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
@@ -9564,29 +9568,29 @@
         <v>13</v>
       </c>
       <c r="B264" s="7">
-        <v>820</v>
+        <v>509</v>
       </c>
       <c t="s" r="C264" s="7">
         <v>14</v>
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c t="s" r="H264" s="8">
-        <v>307</v>
+        <v>68</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>200</v>
+        <v>302</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>308</v>
+        <v>303</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
@@ -9594,48 +9598,66 @@
     </row>
     <row r="265" ht="15" customHeight="1">
       <c t="s" r="A265" s="6">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="B265" s="7">
-        <v>821</v>
+        <v>512</v>
       </c>
       <c t="s" r="C265" s="7">
         <v>14</v>
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
+        <v>301</v>
+      </c>
+      <c r="F265" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G265" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="H265" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="I265" s="7">
         <v>304</v>
       </c>
-      <c r="F265" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G265" s="8">
-        <v>307</v>
-      </c>
-      <c t="s" r="H265" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="I265" s="7">
-        <v>309</v>
-      </c>
       <c t="s" r="J265" s="7">
-        <v>266</v>
+        <v>305</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
       <c r="M265" s="7"/>
     </row>
     <row r="266" ht="14.25" customHeight="1">
-      <c r="A266" s="6"/>
-      <c r="B266" s="7"/>
-      <c r="C266" s="7"/>
+      <c t="s" r="A266" s="6">
+        <v>13</v>
+      </c>
+      <c r="B266" s="7">
+        <v>511</v>
+      </c>
+      <c t="s" r="C266" s="7">
+        <v>14</v>
+      </c>
       <c r="D266" s="7"/>
-      <c r="E266" s="7"/>
-      <c r="F266" s="7"/>
-      <c r="G266" s="8"/>
-      <c r="H266" s="8"/>
-      <c r="I266" s="7"/>
-      <c r="J266" s="7"/>
+      <c t="s" r="E266" s="7">
+        <v>301</v>
+      </c>
+      <c r="F266" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G266" s="8">
+        <v>40</v>
+      </c>
+      <c t="s" r="H266" s="8">
+        <v>68</v>
+      </c>
+      <c t="s" r="I266" s="7">
+        <v>191</v>
+      </c>
+      <c t="s" r="J266" s="7">
+        <v>32</v>
+      </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
       <c r="M266" s="7"/>
@@ -9645,63 +9667,45 @@
         <v>13</v>
       </c>
       <c r="B267" s="7">
-        <v>137</v>
+        <v>878</v>
       </c>
       <c t="s" r="C267" s="7">
         <v>14</v>
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="F267" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G267" s="8">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>25</v>
+        <v>34</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>311</v>
+        <v>179</v>
       </c>
       <c t="s" r="J267" s="7">
-        <v>171</v>
+        <v>134</v>
       </c>
       <c r="K267" s="7"/>
       <c r="L267" s="7"/>
       <c r="M267" s="7"/>
     </row>
     <row r="268" ht="14.25" customHeight="1">
-      <c t="s" r="A268" s="6">
-        <v>13</v>
-      </c>
-      <c r="B268" s="7">
-        <v>148</v>
-      </c>
-      <c t="s" r="C268" s="7">
-        <v>14</v>
-      </c>
+      <c r="A268" s="6"/>
+      <c r="B268" s="7"/>
+      <c r="C268" s="7"/>
       <c r="D268" s="7"/>
-      <c t="s" r="E268" s="7">
-        <v>310</v>
-      </c>
-      <c r="F268" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G268" s="8">
-        <v>25</v>
-      </c>
-      <c t="s" r="H268" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="I268" s="7">
-        <v>42</v>
-      </c>
-      <c t="s" r="J268" s="7">
-        <v>146</v>
-      </c>
+      <c r="E268" s="7"/>
+      <c r="F268" s="7"/>
+      <c r="G268" s="8"/>
+      <c r="H268" s="8"/>
+      <c r="I268" s="7"/>
+      <c r="J268" s="7"/>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
       <c r="M268" s="7"/>
@@ -9711,29 +9715,29 @@
         <v>13</v>
       </c>
       <c r="B269" s="7">
-        <v>441</v>
+        <v>825</v>
       </c>
       <c t="s" r="C269" s="7">
         <v>14</v>
       </c>
       <c r="D269" s="7"/>
       <c t="s" r="E269" s="7">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F269" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G269" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="H269" s="8">
-        <v>17</v>
+        <v>307</v>
       </c>
       <c t="s" r="I269" s="7">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c t="s" r="J269" s="7">
-        <v>140</v>
+        <v>308</v>
       </c>
       <c r="K269" s="7"/>
       <c r="L269" s="7"/>
@@ -9744,29 +9748,29 @@
         <v>13</v>
       </c>
       <c r="B270" s="7">
-        <v>442</v>
+        <v>826</v>
       </c>
       <c t="s" r="C270" s="7">
         <v>14</v>
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F270" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G270" s="8">
-        <v>17</v>
+        <v>307</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>181</v>
+        <v>246</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>253</v>
+        <v>140</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
@@ -9777,29 +9781,29 @@
         <v>13</v>
       </c>
       <c r="B271" s="7">
-        <v>1409</v>
+        <v>820</v>
       </c>
       <c t="s" r="C271" s="7">
         <v>14</v>
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
+        <v>306</v>
+      </c>
+      <c r="F271" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G271" s="8">
+        <v>25</v>
+      </c>
+      <c t="s" r="H271" s="8">
+        <v>309</v>
+      </c>
+      <c t="s" r="I271" s="7">
+        <v>210</v>
+      </c>
+      <c t="s" r="J271" s="7">
         <v>310</v>
-      </c>
-      <c r="F271" s="7">
-        <v>320</v>
-      </c>
-      <c t="s" r="G271" s="8">
-        <v>40</v>
-      </c>
-      <c t="s" r="H271" s="8">
-        <v>46</v>
-      </c>
-      <c t="s" r="I271" s="7">
-        <v>24</v>
-      </c>
-      <c t="s" r="J271" s="7">
-        <v>298</v>
       </c>
       <c r="K271" s="7"/>
       <c r="L271" s="7"/>
@@ -9807,32 +9811,32 @@
     </row>
     <row r="272" ht="14.25" customHeight="1">
       <c t="s" r="A272" s="6">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="B272" s="7">
-        <v>1410</v>
+        <v>821</v>
       </c>
       <c t="s" r="C272" s="7">
         <v>14</v>
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="F272" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c t="s" r="G272" s="8">
-        <v>46</v>
+        <v>309</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>40</v>
+        <v>25</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>144</v>
+        <v>311</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -9874,13 +9878,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H274" s="8">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="I274" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J274" s="7">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K274" s="7"/>
       <c r="L274" s="7"/>
@@ -9904,16 +9908,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G275" s="8">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c t="s" r="H275" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I275" s="7">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
@@ -9940,10 +9944,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H276" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>117</v>
@@ -9991,10 +9995,10 @@
         <v>125</v>
       </c>
       <c t="s" r="I278" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c t="s" r="J278" s="7">
-        <v>60</v>
+        <v>137</v>
       </c>
       <c r="K278" s="7"/>
       <c r="L278" s="7"/>
@@ -10027,7 +10031,7 @@
         <v>30</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>207</v>
+        <v>148</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10057,7 +10061,7 @@
         <v>314</v>
       </c>
       <c t="s" r="I280" s="7">
-        <v>158</v>
+        <v>66</v>
       </c>
       <c t="s" r="J280" s="7">
         <v>315</v>
@@ -10090,7 +10094,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>316</v>
@@ -10168,7 +10172,7 @@
         <v>40</v>
       </c>
       <c t="s" r="H284" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I284" s="7">
         <v>19</v>
@@ -10198,7 +10202,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G285" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H285" s="8">
         <v>320</v>
@@ -10234,10 +10238,10 @@
         <v>320</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c t="s" r="J286" s="7">
         <v>130</v>
@@ -10264,16 +10268,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H287" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10321,7 +10325,7 @@
         <v>111</v>
       </c>
       <c t="s" r="J289" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K289" s="7"/>
       <c r="L289" s="7"/>
@@ -10354,7 +10358,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
@@ -10381,10 +10385,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H291" s="8">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c t="s" r="I291" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J291" s="7">
         <v>322</v>
@@ -10411,16 +10415,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G292" s="8">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c t="s" r="H292" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>201</v>
+        <v>211</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10447,13 +10451,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H293" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c t="s" r="K293" s="7">
         <v>325</v>
@@ -10502,10 +10506,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I295" s="7">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c t="s" r="J295" s="7">
-        <v>59</v>
+        <v>156</v>
       </c>
       <c r="K295" s="7"/>
       <c r="L295" s="7"/>
@@ -10532,13 +10536,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H296" s="8">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>206</v>
+        <v>216</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
@@ -10562,16 +10566,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G297" s="8">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="H297" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10604,7 +10608,7 @@
         <v>102</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -10664,13 +10668,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H300" s="8">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="I300" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="K300" s="7"/>
       <c r="L300" s="7"/>
@@ -10694,16 +10698,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G301" s="8">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="H301" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -10730,10 +10734,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H302" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J302" s="7">
         <v>329</v>
@@ -10760,13 +10764,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G303" s="8">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c t="s" r="H303" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I303" s="7">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c t="s" r="J303" s="7">
         <v>330</v>
@@ -10814,10 +10818,10 @@
         <v>332</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J305" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K305" s="7"/>
       <c r="L305" s="7"/>
@@ -10847,7 +10851,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>44</v>
@@ -10877,10 +10881,10 @@
         <v>40</v>
       </c>
       <c t="s" r="H307" s="8">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>233</v>
+        <v>240</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>95</v>
@@ -10907,16 +10911,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G308" s="8">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c t="s" r="H308" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>178</v>
+        <v>188</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -10946,7 +10950,7 @@
         <v>333</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c t="s" r="J309" s="7">
         <v>334</v>
@@ -11027,10 +11031,10 @@
         <v>338</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>311</v>
+        <v>271</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>266</v>
+        <v>167</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
@@ -11060,10 +11064,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>197</v>
+        <v>207</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11090,13 +11094,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H314" s="8">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>230</v>
+        <v>237</v>
       </c>
       <c t="s" r="J314" s="7">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="K314" s="7"/>
       <c r="L314" s="7"/>
@@ -11120,13 +11124,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G315" s="8">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c t="s" r="H315" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>44</v>
@@ -11159,7 +11163,7 @@
         <v>338</v>
       </c>
       <c t="s" r="I316" s="7">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c t="s" r="J316" s="7">
         <v>104</v>
@@ -11195,7 +11199,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11309,11 +11313,15 @@
         <v>53</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>244</v>
-      </c>
-      <c r="K321" s="7"/>
+        <v>250</v>
+      </c>
+      <c t="s" r="K321" s="7">
+        <v>77</v>
+      </c>
       <c r="L321" s="7"/>
-      <c r="M321" s="7"/>
+      <c t="s" r="M321" s="7">
+        <v>21</v>
+      </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
       <c t="s" r="A322" s="6">
@@ -11336,10 +11344,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H322" s="8">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c t="s" r="J322" s="7">
         <v>93</v>
@@ -11366,13 +11374,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G323" s="8">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c t="s" r="H323" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>118</v>
@@ -11405,10 +11413,10 @@
         <v>333</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11438,10 +11446,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I325" s="7">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c t="s" r="J325" s="7">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="K325" s="7"/>
       <c r="L325" s="7"/>
@@ -11486,7 +11494,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c t="s" r="J327" s="7">
         <v>116</v>
@@ -11519,10 +11527,10 @@
         <v>344</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>298</v>
+        <v>272</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11552,10 +11560,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I329" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="J329" s="7">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="K329" s="7"/>
       <c r="L329" s="7"/>
@@ -11699,7 +11707,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>49</v>
@@ -11729,10 +11737,10 @@
         <v>25</v>
       </c>
       <c t="s" r="H335" s="8">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c t="s" r="J335" s="7">
         <v>347</v>
@@ -11759,7 +11767,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G336" s="8">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c t="s" r="H336" s="8">
         <v>25</v>
@@ -11843,13 +11851,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H339" s="8">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c t="s" r="I339" s="7">
         <v>351</v>
       </c>
       <c t="s" r="J339" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K339" s="7"/>
       <c r="L339" s="7"/>
@@ -11873,13 +11881,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G340" s="8">
-        <v>153</v>
+        <v>58</v>
       </c>
       <c t="s" r="H340" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>78</v>
+        <v>65</v>
       </c>
       <c t="s" r="J340" s="7">
         <v>33</v>
@@ -11945,7 +11953,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I342" s="7">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c t="s" r="J342" s="7">
         <v>353</v>
@@ -11996,7 +12004,7 @@
         <v>134</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
@@ -12023,13 +12031,13 @@
         <v>46</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c t="s" r="I345" s="7">
         <v>108</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
@@ -12053,7 +12061,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>58</v>
+        <v>79</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>46</v>
@@ -12092,7 +12100,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c t="s" r="J347" s="7">
         <v>147</v>
@@ -12122,13 +12130,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H348" s="8">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12152,7 +12160,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G349" s="8">
-        <v>238</v>
+        <v>245</v>
       </c>
       <c t="s" r="H349" s="8">
         <v>40</v>
@@ -12161,7 +12169,7 @@
         <v>47</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12188,13 +12196,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H350" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12218,13 +12226,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G351" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H351" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I351" s="7">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c t="s" r="J351" s="7">
         <v>356</v>
@@ -12275,7 +12283,7 @@
         <v>351</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12371,7 +12379,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I356" s="7">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c t="s" r="J356" s="7">
         <v>361</v>
@@ -12413,13 +12421,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G358" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H358" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>175</v>
+        <v>186</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>92</v>
@@ -12449,13 +12457,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H359" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>252</v>
+        <v>149</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -12479,13 +12487,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G360" s="8">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="H360" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I360" s="7">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c t="s" r="J360" s="7">
         <v>121</v>
@@ -12533,10 +12541,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I362" s="7">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>139</v>
+        <v>62</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12569,7 +12577,7 @@
         <v>31</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -12599,10 +12607,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12632,10 +12640,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I365" s="7">
-        <v>192</v>
+        <v>202</v>
       </c>
       <c t="s" r="J365" s="7">
-        <v>170</v>
+        <v>182</v>
       </c>
       <c r="K365" s="7"/>
       <c r="L365" s="7"/>
@@ -12677,13 +12685,13 @@
         <v>34</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>367</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -12707,16 +12715,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -12740,16 +12748,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>231</v>
+        <v>238</v>
       </c>
       <c t="s" r="H369" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -12773,7 +12781,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G370" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H370" s="8">
         <v>34</v>
@@ -12824,13 +12832,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H372" s="8">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="I372" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -12854,16 +12862,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G373" s="8">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c t="s" r="H373" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>187</v>
+        <v>197</v>
       </c>
       <c t="s" r="J373" s="7">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="K373" s="7"/>
       <c r="L373" s="7"/>
@@ -12893,7 +12901,7 @@
         <v>133</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>176</v>
+        <v>187</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>32</v>
@@ -12926,7 +12934,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c t="s" r="J375" s="7">
         <v>45</v>
@@ -12956,13 +12964,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H376" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I376" s="7">
         <v>97</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -12986,16 +12994,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G377" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H377" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>228</v>
+        <v>235</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13028,7 +13036,7 @@
         <v>370</v>
       </c>
       <c t="s" r="J378" s="7">
-        <v>221</v>
+        <v>228</v>
       </c>
       <c r="K378" s="7"/>
       <c r="L378" s="7"/>
@@ -13073,10 +13081,10 @@
         <v>55</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c t="s" r="J380" s="7">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="K380" s="7"/>
       <c r="L380" s="7"/>
@@ -13139,10 +13147,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13172,10 +13180,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I383" s="7">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="J383" s="7">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="K383" s="7"/>
       <c r="L383" s="7"/>
@@ -13217,13 +13225,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H385" s="8">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>171</v>
+        <v>183</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
@@ -13247,16 +13255,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G386" s="8">
-        <v>61</v>
+        <v>150</v>
       </c>
       <c t="s" r="H386" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>186</v>
+        <v>196</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13283,13 +13291,13 @@
         <v>40</v>
       </c>
       <c t="s" r="H387" s="8">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>232</v>
+        <v>239</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>267</v>
+        <v>171</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13313,16 +13321,16 @@
         <v>320</v>
       </c>
       <c t="s" r="G388" s="8">
-        <v>87</v>
+        <v>63</v>
       </c>
       <c t="s" r="H388" s="8">
         <v>40</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>181</v>
+        <v>191</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -13352,10 +13360,10 @@
         <v>314</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13388,7 +13396,7 @@
         <v>326</v>
       </c>
       <c t="s" r="J390" s="7">
-        <v>183</v>
+        <v>193</v>
       </c>
       <c r="K390" s="7"/>
       <c r="L390" s="7"/>
@@ -13430,13 +13438,13 @@
         <v>25</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>346</v>
       </c>
       <c t="s" r="J392" s="7">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
@@ -13460,16 +13468,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>62</v>
+        <v>157</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13532,7 +13540,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>375</v>
@@ -13568,7 +13576,7 @@
         <v>37</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>213</v>
+        <v>220</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13646,7 +13654,7 @@
         <v>40</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>31</v>
@@ -13688,16 +13696,16 @@
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H401" s="8">
         <v>378</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>157</v>
+        <v>64</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
@@ -13724,13 +13732,13 @@
         <v>378</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I402" s="7">
         <v>379</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>266</v>
+        <v>167</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -13808,10 +13816,10 @@
         <v>381</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>239</v>
+        <v>169</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -13850,13 +13858,13 @@
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>25</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>196</v>
+        <v>206</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>53</v>
@@ -13892,7 +13900,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>202</v>
+        <v>212</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -13925,7 +13933,7 @@
         <v>329</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>215</v>
+        <v>222</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -13964,7 +13972,7 @@
         <v>330</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="H411" s="8">
         <v>386</v>
@@ -13973,7 +13981,7 @@
         <v>387</v>
       </c>
       <c t="s" r="J411" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14000,13 +14008,13 @@
         <v>386</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>222</v>
+        <v>229</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>168</v>
+        <v>180</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14051,10 +14059,10 @@
         <v>389</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>174</v>
+        <v>185</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
@@ -14084,7 +14092,7 @@
         <v>25</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c t="s" r="J415" s="7">
         <v>390</v>
@@ -14116,7 +14124,7 @@
         <v>6853</v>
       </c>
       <c t="s" r="C417" s="7">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
@@ -14149,7 +14157,7 @@
         <v>6854</v>
       </c>
       <c t="s" r="C418" s="7">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
@@ -14165,10 +14173,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14213,10 +14221,10 @@
         <v>40</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14246,10 +14254,10 @@
         <v>25</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>189</v>
+        <v>199</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>

--- a/Data/FlightPlan/FPL_29OCT26.xlsx
+++ b/Data/FlightPlan/FPL_29OCT26.xlsx
@@ -212,7 +212,7 @@
     <t>12:25</t>
   </si>
   <si>
-    <t>12:13</t>
+    <t>12:16</t>
   </si>
   <si>
     <t>BKK</t>
@@ -416,903 +416,915 @@
     <t>08:25</t>
   </si>
   <si>
+    <t>12:05</t>
+  </si>
+  <si>
+    <t>21:15</t>
+  </si>
+  <si>
+    <t>00:45</t>
+  </si>
+  <si>
+    <t>09:50</t>
+  </si>
+  <si>
+    <t>VN-A530</t>
+  </si>
+  <si>
+    <t>HUI</t>
+  </si>
+  <si>
+    <t>06:00</t>
+  </si>
+  <si>
+    <t>07:15</t>
+  </si>
+  <si>
+    <t>07:07</t>
+  </si>
+  <si>
+    <t>07:45</t>
+  </si>
+  <si>
+    <t>09:00</t>
+  </si>
+  <si>
+    <t>09:02</t>
+  </si>
+  <si>
+    <t>09:40</t>
+  </si>
+  <si>
+    <t>11:50</t>
+  </si>
+  <si>
+    <t>11:41</t>
+  </si>
+  <si>
+    <t>16:00</t>
+  </si>
+  <si>
+    <t>18:05</t>
+  </si>
+  <si>
+    <t>18:40</t>
+  </si>
+  <si>
+    <t>20:45</t>
+  </si>
+  <si>
+    <t>23:10</t>
+  </si>
+  <si>
+    <t>VN-A532</t>
+  </si>
+  <si>
+    <t>10:50</t>
+  </si>
+  <si>
+    <t>14:20</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>14:44</t>
+  </si>
+  <si>
+    <t>BMV</t>
+  </si>
+  <si>
+    <t>17:00</t>
+  </si>
+  <si>
+    <t>17:30</t>
+  </si>
+  <si>
+    <t>HYD</t>
+  </si>
+  <si>
+    <t>19:40</t>
+  </si>
+  <si>
+    <t>22:35</t>
+  </si>
+  <si>
+    <t>23:45</t>
+  </si>
+  <si>
+    <t>05:40</t>
+  </si>
+  <si>
+    <t>VN-A535</t>
+  </si>
+  <si>
+    <t>CXR</t>
+  </si>
+  <si>
+    <t>08:10</t>
+  </si>
+  <si>
+    <t>09:20</t>
+  </si>
+  <si>
+    <t>09:31</t>
+  </si>
+  <si>
+    <t>10:55</t>
+  </si>
+  <si>
+    <t>11:14</t>
+  </si>
+  <si>
     <t>HPH</t>
   </si>
   <si>
     <t>11:00</t>
   </si>
   <si>
+    <t>12:10</t>
+  </si>
+  <si>
+    <t>14:10</t>
+  </si>
+  <si>
     <t>15:30</t>
   </si>
   <si>
+    <t>21:25</t>
+  </si>
+  <si>
+    <t>00:05</t>
+  </si>
+  <si>
+    <t>VN-A536</t>
+  </si>
+  <si>
+    <t>07:20</t>
+  </si>
+  <si>
+    <t>08:45</t>
+  </si>
+  <si>
+    <t>10:00</t>
+  </si>
+  <si>
+    <t>11:25</t>
+  </si>
+  <si>
+    <t>11:36</t>
+  </si>
+  <si>
+    <t>13:20</t>
+  </si>
+  <si>
+    <t>14:05</t>
+  </si>
+  <si>
+    <t>17:55</t>
+  </si>
+  <si>
+    <t>20:30</t>
+  </si>
+  <si>
+    <t>22:30</t>
+  </si>
+  <si>
+    <t>23:25</t>
+  </si>
+  <si>
+    <t>VN-A542</t>
+  </si>
+  <si>
+    <t>13:05</t>
+  </si>
+  <si>
+    <t>12:30</t>
+  </si>
+  <si>
+    <t>23:40</t>
+  </si>
+  <si>
+    <t>06:30</t>
+  </si>
+  <si>
+    <t>VN-A543</t>
+  </si>
+  <si>
+    <t>06:55</t>
+  </si>
+  <si>
+    <t>08:15</t>
+  </si>
+  <si>
+    <t>08:06</t>
+  </si>
+  <si>
+    <t>10:10</t>
+  </si>
+  <si>
+    <t>09:55</t>
+  </si>
+  <si>
+    <t>10:40</t>
+  </si>
+  <si>
+    <t>12:40</t>
+  </si>
+  <si>
+    <t>12:57</t>
+  </si>
+  <si>
+    <t>15:10</t>
+  </si>
+  <si>
+    <t>20:25</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>VN-A549</t>
+  </si>
+  <si>
+    <t>10:29</t>
+  </si>
+  <si>
+    <t>15:05</t>
+  </si>
+  <si>
+    <t>BAX</t>
+  </si>
+  <si>
+    <t>02:05</t>
+  </si>
+  <si>
+    <t>VN-A551</t>
+  </si>
+  <si>
+    <t>07:30</t>
+  </si>
+  <si>
+    <t>08:59</t>
+  </si>
+  <si>
+    <t>10:30</t>
+  </si>
+  <si>
+    <t>10:35</t>
+  </si>
+  <si>
+    <t>15:35</t>
+  </si>
+  <si>
+    <t>20:05</t>
+  </si>
+  <si>
+    <t>20:35</t>
+  </si>
+  <si>
+    <t>VN-A552</t>
+  </si>
+  <si>
+    <t>00:55</t>
+  </si>
+  <si>
+    <t>VN-A553</t>
+  </si>
+  <si>
+    <t>20:10</t>
+  </si>
+  <si>
+    <t>VN-A554</t>
+  </si>
+  <si>
+    <t>07:00</t>
+  </si>
+  <si>
+    <t>09:10</t>
+  </si>
+  <si>
+    <t>09:08</t>
+  </si>
+  <si>
+    <t>12:17</t>
+  </si>
+  <si>
+    <t>14:40</t>
+  </si>
+  <si>
+    <t>16:50</t>
+  </si>
+  <si>
+    <t>17:20</t>
+  </si>
+  <si>
+    <t>19:30</t>
+  </si>
+  <si>
+    <t>23:35</t>
+  </si>
+  <si>
+    <t>VN-A575</t>
+  </si>
+  <si>
+    <t>VCA</t>
+  </si>
+  <si>
+    <t>06:40</t>
+  </si>
+  <si>
+    <t>08:50</t>
+  </si>
+  <si>
+    <t>08:53</t>
+  </si>
+  <si>
+    <t>11:29</t>
+  </si>
+  <si>
+    <t>UIH</t>
+  </si>
+  <si>
+    <t>16:20</t>
+  </si>
+  <si>
+    <t>18:00</t>
+  </si>
+  <si>
+    <t>20:00</t>
+  </si>
+  <si>
+    <t>KHV</t>
+  </si>
+  <si>
+    <t>01:10</t>
+  </si>
+  <si>
+    <t>VN-A578</t>
+  </si>
+  <si>
+    <t>05:55</t>
+  </si>
+  <si>
+    <t>08:05</t>
+  </si>
+  <si>
+    <t>07:56</t>
+  </si>
+  <si>
+    <t>11:11</t>
+  </si>
+  <si>
+    <t>13:50</t>
+  </si>
+  <si>
+    <t>VN-A580</t>
+  </si>
+  <si>
+    <t>VVO</t>
+  </si>
+  <si>
+    <t>04:55</t>
+  </si>
+  <si>
+    <t>07:55</t>
+  </si>
+  <si>
+    <t>10:25</t>
+  </si>
+  <si>
+    <t>21:35</t>
+  </si>
+  <si>
+    <t>BQS</t>
+  </si>
+  <si>
+    <t>23:55</t>
+  </si>
+  <si>
+    <t>VN-A607</t>
+  </si>
+  <si>
+    <t>PER</t>
+  </si>
+  <si>
+    <t>16:37</t>
+  </si>
+  <si>
+    <t>23:05</t>
+  </si>
+  <si>
+    <t>VN-A629</t>
+  </si>
+  <si>
+    <t>09:07</t>
+  </si>
+  <si>
+    <t>09:45</t>
+  </si>
+  <si>
+    <t>11:10</t>
+  </si>
+  <si>
+    <t>MFM</t>
+  </si>
+  <si>
+    <t>12:15</t>
+  </si>
+  <si>
+    <t>15:50</t>
+  </si>
+  <si>
+    <t>MNL</t>
+  </si>
+  <si>
+    <t>01:05</t>
+  </si>
+  <si>
+    <t>03:25</t>
+  </si>
+  <si>
+    <t>VN-A632</t>
+  </si>
+  <si>
+    <t>09:54</t>
+  </si>
+  <si>
+    <t>12:02</t>
+  </si>
+  <si>
+    <t>13:35</t>
+  </si>
+  <si>
+    <t>15:25</t>
+  </si>
+  <si>
+    <t>22:10</t>
+  </si>
+  <si>
+    <t>VN-A633</t>
+  </si>
+  <si>
+    <t>09:39</t>
+  </si>
+  <si>
+    <t>11:40</t>
+  </si>
+  <si>
+    <t>18:35</t>
+  </si>
+  <si>
+    <t>20:40</t>
+  </si>
+  <si>
+    <t>VN-A634</t>
+  </si>
+  <si>
+    <t>07:25</t>
+  </si>
+  <si>
+    <t>07:40</t>
+  </si>
+  <si>
+    <t>11:20</t>
+  </si>
+  <si>
+    <t>15:00</t>
+  </si>
+  <si>
+    <t>17:10</t>
+  </si>
+  <si>
+    <t>VN-A636</t>
+  </si>
+  <si>
+    <t>05:00</t>
+  </si>
+  <si>
+    <t>07:10</t>
+  </si>
+  <si>
+    <t>07:05</t>
+  </si>
+  <si>
+    <t>11:46</t>
+  </si>
+  <si>
+    <t>12:20</t>
+  </si>
+  <si>
+    <t>13:45</t>
+  </si>
+  <si>
+    <t>VDH</t>
+  </si>
+  <si>
+    <t>14:45</t>
+  </si>
+  <si>
+    <t>16:55</t>
+  </si>
+  <si>
+    <t>VN-A637</t>
+  </si>
+  <si>
+    <t>12:03</t>
+  </si>
+  <si>
+    <t>VN-A639</t>
+  </si>
+  <si>
+    <t>06:05</t>
+  </si>
+  <si>
+    <t>08:20</t>
+  </si>
+  <si>
+    <t>11:17</t>
+  </si>
+  <si>
+    <t>20:15</t>
+  </si>
+  <si>
+    <t>VN-A640</t>
+  </si>
+  <si>
+    <t>10:37</t>
+  </si>
+  <si>
+    <t>11:35</t>
+  </si>
+  <si>
+    <t>VN-A642</t>
+  </si>
+  <si>
+    <t>08:34</t>
+  </si>
+  <si>
+    <t>15:20</t>
+  </si>
+  <si>
+    <t>17:45</t>
+  </si>
+  <si>
+    <t>19:20</t>
+  </si>
+  <si>
+    <t>21:10</t>
+  </si>
+  <si>
+    <t>21:40</t>
+  </si>
+  <si>
+    <t>23:30</t>
+  </si>
+  <si>
+    <t>VN-A643</t>
+  </si>
+  <si>
+    <t>12:50</t>
+  </si>
+  <si>
+    <t>12:48</t>
+  </si>
+  <si>
+    <t>SAI</t>
+  </si>
+  <si>
+    <t>20:50</t>
+  </si>
+  <si>
+    <t>CAN</t>
+  </si>
+  <si>
+    <t>02:15</t>
+  </si>
+  <si>
+    <t>03:15</t>
+  </si>
+  <si>
+    <t>04:20</t>
+  </si>
+  <si>
+    <t>VN-A644</t>
+  </si>
+  <si>
+    <t>10:54</t>
+  </si>
+  <si>
+    <t>18:10</t>
+  </si>
+  <si>
+    <t>00:30</t>
+  </si>
+  <si>
+    <t>VN-A645</t>
+  </si>
+  <si>
+    <t>13:34</t>
+  </si>
+  <si>
+    <t>22:40</t>
+  </si>
+  <si>
+    <t>VN-A646</t>
+  </si>
+  <si>
+    <t>HKT</t>
+  </si>
+  <si>
+    <t>23:00</t>
+  </si>
+  <si>
+    <t>VN-A647</t>
+  </si>
+  <si>
+    <t>07:46</t>
+  </si>
+  <si>
+    <t>TPE</t>
+  </si>
+  <si>
+    <t>VN-A648</t>
+  </si>
+  <si>
+    <t>VN-A649</t>
+  </si>
+  <si>
+    <t>06:51</t>
+  </si>
+  <si>
+    <t>10:33</t>
+  </si>
+  <si>
+    <t>13:15</t>
+  </si>
+  <si>
+    <t>14:35</t>
+  </si>
+  <si>
+    <t>VN-A653</t>
+  </si>
+  <si>
+    <t>KUL</t>
+  </si>
+  <si>
+    <t>12:35</t>
+  </si>
+  <si>
+    <t>12:43</t>
+  </si>
+  <si>
+    <t>HND</t>
+  </si>
+  <si>
+    <t>01:00</t>
+  </si>
+  <si>
+    <t>02:30</t>
+  </si>
+  <si>
+    <t>VN-A657</t>
+  </si>
+  <si>
+    <t>10:42</t>
+  </si>
+  <si>
+    <t>VN-A658</t>
+  </si>
+  <si>
+    <t>09:17</t>
+  </si>
+  <si>
+    <t>PKX</t>
+  </si>
+  <si>
+    <t>22:00</t>
+  </si>
+  <si>
+    <t>03:05</t>
+  </si>
+  <si>
+    <t>VN-A661</t>
+  </si>
+  <si>
+    <t>06:25</t>
+  </si>
+  <si>
+    <t>08:46</t>
+  </si>
+  <si>
+    <t>12:55</t>
+  </si>
+  <si>
+    <t>WUX</t>
+  </si>
+  <si>
+    <t>14:15</t>
+  </si>
+  <si>
+    <t>19:00</t>
+  </si>
+  <si>
+    <t>VN-A663</t>
+  </si>
+  <si>
+    <t>HIJ</t>
+  </si>
+  <si>
+    <t>12:54</t>
+  </si>
+  <si>
+    <t>21:50</t>
+  </si>
+  <si>
+    <t>23:15</t>
+  </si>
+  <si>
+    <t>VN-A667</t>
+  </si>
+  <si>
+    <t>11:52</t>
+  </si>
+  <si>
+    <t>01:30</t>
+  </si>
+  <si>
+    <t>04:10</t>
+  </si>
+  <si>
+    <t>VN-A668</t>
+  </si>
+  <si>
+    <t>TNN</t>
+  </si>
+  <si>
+    <t>11:33</t>
+  </si>
+  <si>
+    <t>PVG</t>
+  </si>
+  <si>
+    <t>01:15</t>
+  </si>
+  <si>
+    <t>02:20</t>
+  </si>
+  <si>
+    <t>05:15</t>
+  </si>
+  <si>
+    <t>VN-A669</t>
+  </si>
+  <si>
+    <t>VCL</t>
+  </si>
+  <si>
+    <t>07:24</t>
+  </si>
+  <si>
+    <t>11:44</t>
+  </si>
+  <si>
+    <t>19:35</t>
+  </si>
+  <si>
+    <t>22:55</t>
+  </si>
+  <si>
+    <t>VN-A670</t>
+  </si>
+  <si>
+    <t>VN-A672</t>
+  </si>
+  <si>
+    <t>FSZ</t>
+  </si>
+  <si>
+    <t>14:21</t>
+  </si>
+  <si>
+    <t>ENH</t>
+  </si>
+  <si>
+    <t>VN-A673</t>
+  </si>
+  <si>
+    <t>10:23</t>
+  </si>
+  <si>
+    <t>02:50</t>
+  </si>
+  <si>
+    <t>03:45</t>
+  </si>
+  <si>
+    <t>05:30</t>
+  </si>
+  <si>
+    <t>VN-A674</t>
+  </si>
+  <si>
+    <t>08:13</t>
+  </si>
+  <si>
+    <t>09:35</t>
+  </si>
+  <si>
+    <t>13:41</t>
+  </si>
+  <si>
+    <t>DEL</t>
+  </si>
+  <si>
+    <t>05:35</t>
+  </si>
+  <si>
+    <t>VN-A675</t>
+  </si>
+  <si>
+    <t>07:51</t>
+  </si>
+  <si>
+    <t>10:01</t>
+  </si>
+  <si>
+    <t>00:50</t>
+  </si>
+  <si>
+    <t>VN-A676</t>
+  </si>
+  <si>
+    <t>16:35</t>
+  </si>
+  <si>
+    <t>CMB</t>
+  </si>
+  <si>
+    <t>22:05</t>
+  </si>
+  <si>
+    <t>05:50</t>
+  </si>
+  <si>
+    <t>VN-A677</t>
+  </si>
+  <si>
+    <t>VN-A683</t>
+  </si>
+  <si>
+    <t>FUK</t>
+  </si>
+  <si>
+    <t>RMQ</t>
+  </si>
+  <si>
+    <t>VN-A684</t>
+  </si>
+  <si>
+    <t>06:45</t>
+  </si>
+  <si>
+    <t>09:21</t>
+  </si>
+  <si>
+    <t>22:45</t>
+  </si>
+  <si>
+    <t>VN-A685</t>
+  </si>
+  <si>
+    <t>01:45</t>
+  </si>
+  <si>
+    <t>VN-A687</t>
+  </si>
+  <si>
+    <t>VN-A689</t>
+  </si>
+  <si>
+    <t>08:04</t>
+  </si>
+  <si>
+    <t>VN-A697</t>
+  </si>
+  <si>
+    <t>10:49</t>
+  </si>
+  <si>
+    <t>15:15</t>
+  </si>
+  <si>
     <t>BOM</t>
   </si>
   <si>
     <t>18:55</t>
   </si>
   <si>
-    <t>23:10</t>
-  </si>
-  <si>
     <t>00:10</t>
   </si>
   <si>
-    <t>VN-A530</t>
-  </si>
-  <si>
-    <t>HUI</t>
-  </si>
-  <si>
-    <t>06:00</t>
-  </si>
-  <si>
-    <t>07:15</t>
-  </si>
-  <si>
-    <t>07:07</t>
-  </si>
-  <si>
-    <t>07:45</t>
-  </si>
-  <si>
-    <t>09:00</t>
-  </si>
-  <si>
-    <t>09:02</t>
-  </si>
-  <si>
-    <t>09:40</t>
-  </si>
-  <si>
-    <t>11:50</t>
-  </si>
-  <si>
-    <t>11:41</t>
-  </si>
-  <si>
-    <t>16:00</t>
-  </si>
-  <si>
-    <t>18:05</t>
-  </si>
-  <si>
-    <t>18:40</t>
-  </si>
-  <si>
-    <t>20:45</t>
-  </si>
-  <si>
-    <t>VN-A532</t>
-  </si>
-  <si>
-    <t>10:50</t>
-  </si>
-  <si>
-    <t>14:20</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>14:44</t>
-  </si>
-  <si>
-    <t>BMV</t>
-  </si>
-  <si>
-    <t>17:00</t>
-  </si>
-  <si>
-    <t>17:30</t>
-  </si>
-  <si>
-    <t>21:25</t>
-  </si>
-  <si>
-    <t>00:05</t>
-  </si>
-  <si>
-    <t>VN-A535</t>
-  </si>
-  <si>
-    <t>CXR</t>
-  </si>
-  <si>
-    <t>08:10</t>
-  </si>
-  <si>
-    <t>09:20</t>
-  </si>
-  <si>
-    <t>09:31</t>
-  </si>
-  <si>
-    <t>09:50</t>
-  </si>
-  <si>
-    <t>10:55</t>
-  </si>
-  <si>
-    <t>12:05</t>
-  </si>
-  <si>
-    <t>21:15</t>
-  </si>
-  <si>
-    <t>00:45</t>
-  </si>
-  <si>
-    <t>VN-A536</t>
-  </si>
-  <si>
-    <t>07:20</t>
-  </si>
-  <si>
-    <t>08:45</t>
-  </si>
-  <si>
-    <t>10:00</t>
-  </si>
-  <si>
-    <t>11:25</t>
-  </si>
-  <si>
-    <t>11:26</t>
-  </si>
-  <si>
-    <t>13:20</t>
-  </si>
-  <si>
-    <t>14:05</t>
-  </si>
-  <si>
-    <t>17:55</t>
-  </si>
-  <si>
-    <t>20:30</t>
-  </si>
-  <si>
-    <t>22:30</t>
-  </si>
-  <si>
-    <t>23:25</t>
-  </si>
-  <si>
-    <t>VN-A542</t>
-  </si>
-  <si>
-    <t>13:05</t>
-  </si>
-  <si>
-    <t>12:30</t>
-  </si>
-  <si>
-    <t>23:40</t>
-  </si>
-  <si>
-    <t>06:30</t>
-  </si>
-  <si>
-    <t>VN-A543</t>
-  </si>
-  <si>
-    <t>06:55</t>
-  </si>
-  <si>
-    <t>08:15</t>
-  </si>
-  <si>
-    <t>08:06</t>
-  </si>
-  <si>
-    <t>10:10</t>
-  </si>
-  <si>
-    <t>09:55</t>
-  </si>
-  <si>
-    <t>10:40</t>
-  </si>
-  <si>
-    <t>12:40</t>
-  </si>
-  <si>
-    <t>15:10</t>
-  </si>
-  <si>
-    <t>20:25</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>VN-A549</t>
-  </si>
-  <si>
-    <t>10:29</t>
-  </si>
-  <si>
-    <t>15:05</t>
-  </si>
-  <si>
-    <t>BAX</t>
-  </si>
-  <si>
-    <t>22:35</t>
-  </si>
-  <si>
-    <t>02:05</t>
-  </si>
-  <si>
-    <t>VN-A551</t>
-  </si>
-  <si>
-    <t>07:30</t>
-  </si>
-  <si>
-    <t>08:59</t>
-  </si>
-  <si>
-    <t>10:30</t>
-  </si>
-  <si>
-    <t>10:35</t>
-  </si>
-  <si>
-    <t>12:10</t>
-  </si>
-  <si>
-    <t>15:35</t>
-  </si>
-  <si>
-    <t>20:05</t>
-  </si>
-  <si>
-    <t>20:35</t>
-  </si>
-  <si>
-    <t>VN-A552</t>
-  </si>
-  <si>
-    <t>00:55</t>
-  </si>
-  <si>
-    <t>VN-A553</t>
-  </si>
-  <si>
-    <t>19:40</t>
-  </si>
-  <si>
-    <t>20:10</t>
-  </si>
-  <si>
-    <t>VN-A554</t>
-  </si>
-  <si>
-    <t>07:00</t>
-  </si>
-  <si>
-    <t>09:10</t>
-  </si>
-  <si>
-    <t>09:08</t>
-  </si>
-  <si>
-    <t>14:40</t>
-  </si>
-  <si>
-    <t>16:50</t>
-  </si>
-  <si>
-    <t>17:20</t>
-  </si>
-  <si>
-    <t>19:30</t>
-  </si>
-  <si>
-    <t>23:35</t>
-  </si>
-  <si>
-    <t>VN-A575</t>
-  </si>
-  <si>
-    <t>VCA</t>
-  </si>
-  <si>
-    <t>06:40</t>
-  </si>
-  <si>
-    <t>08:50</t>
-  </si>
-  <si>
-    <t>08:53</t>
-  </si>
-  <si>
-    <t>11:29</t>
-  </si>
-  <si>
-    <t>UIH</t>
-  </si>
-  <si>
-    <t>16:20</t>
-  </si>
-  <si>
-    <t>18:00</t>
-  </si>
-  <si>
-    <t>20:00</t>
-  </si>
-  <si>
-    <t>KHV</t>
-  </si>
-  <si>
-    <t>01:10</t>
-  </si>
-  <si>
-    <t>VN-A578</t>
-  </si>
-  <si>
-    <t>05:55</t>
-  </si>
-  <si>
-    <t>08:05</t>
-  </si>
-  <si>
-    <t>07:56</t>
-  </si>
-  <si>
-    <t>11:11</t>
-  </si>
-  <si>
-    <t>13:50</t>
-  </si>
-  <si>
-    <t>VN-A580</t>
-  </si>
-  <si>
-    <t>VVO</t>
-  </si>
-  <si>
-    <t>04:55</t>
-  </si>
-  <si>
-    <t>07:55</t>
-  </si>
-  <si>
-    <t>10:25</t>
-  </si>
-  <si>
-    <t>21:35</t>
-  </si>
-  <si>
-    <t>BQS</t>
-  </si>
-  <si>
-    <t>23:55</t>
-  </si>
-  <si>
-    <t>VN-A607</t>
-  </si>
-  <si>
-    <t>PER</t>
-  </si>
-  <si>
-    <t>16:37</t>
-  </si>
-  <si>
-    <t>23:05</t>
-  </si>
-  <si>
-    <t>VN-A629</t>
-  </si>
-  <si>
-    <t>09:07</t>
-  </si>
-  <si>
-    <t>09:45</t>
-  </si>
-  <si>
-    <t>11:10</t>
-  </si>
-  <si>
-    <t>MFM</t>
-  </si>
-  <si>
-    <t>12:15</t>
-  </si>
-  <si>
-    <t>15:50</t>
-  </si>
-  <si>
-    <t>MNL</t>
-  </si>
-  <si>
-    <t>01:05</t>
-  </si>
-  <si>
-    <t>03:25</t>
-  </si>
-  <si>
-    <t>VN-A632</t>
-  </si>
-  <si>
-    <t>09:54</t>
-  </si>
-  <si>
-    <t>13:35</t>
-  </si>
-  <si>
-    <t>15:25</t>
-  </si>
-  <si>
-    <t>22:10</t>
-  </si>
-  <si>
-    <t>VN-A633</t>
-  </si>
-  <si>
-    <t>09:39</t>
-  </si>
-  <si>
-    <t>11:40</t>
-  </si>
-  <si>
-    <t>18:35</t>
-  </si>
-  <si>
-    <t>20:40</t>
-  </si>
-  <si>
-    <t>VN-A634</t>
-  </si>
-  <si>
-    <t>07:25</t>
-  </si>
-  <si>
-    <t>07:40</t>
-  </si>
-  <si>
-    <t>11:20</t>
-  </si>
-  <si>
-    <t>14:10</t>
-  </si>
-  <si>
-    <t>15:00</t>
-  </si>
-  <si>
-    <t>17:10</t>
-  </si>
-  <si>
-    <t>VN-A636</t>
-  </si>
-  <si>
-    <t>05:00</t>
-  </si>
-  <si>
-    <t>07:10</t>
-  </si>
-  <si>
-    <t>07:05</t>
-  </si>
-  <si>
-    <t>12:20</t>
-  </si>
-  <si>
-    <t>13:45</t>
-  </si>
-  <si>
-    <t>VDH</t>
-  </si>
-  <si>
-    <t>14:45</t>
-  </si>
-  <si>
-    <t>16:55</t>
-  </si>
-  <si>
-    <t>VN-A637</t>
-  </si>
-  <si>
-    <t>23:45</t>
-  </si>
-  <si>
-    <t>VN-A639</t>
-  </si>
-  <si>
-    <t>06:05</t>
-  </si>
-  <si>
-    <t>08:20</t>
-  </si>
-  <si>
-    <t>11:17</t>
-  </si>
-  <si>
-    <t>20:15</t>
-  </si>
-  <si>
-    <t>VN-A640</t>
-  </si>
-  <si>
-    <t>10:37</t>
-  </si>
-  <si>
-    <t>11:35</t>
-  </si>
-  <si>
-    <t>VN-A642</t>
-  </si>
-  <si>
-    <t>08:34</t>
-  </si>
-  <si>
-    <t>15:20</t>
-  </si>
-  <si>
-    <t>17:45</t>
-  </si>
-  <si>
-    <t>19:20</t>
-  </si>
-  <si>
-    <t>21:10</t>
-  </si>
-  <si>
-    <t>21:40</t>
-  </si>
-  <si>
-    <t>23:30</t>
-  </si>
-  <si>
-    <t>VN-A643</t>
-  </si>
-  <si>
-    <t>12:50</t>
-  </si>
-  <si>
-    <t>SAI</t>
-  </si>
-  <si>
-    <t>20:50</t>
-  </si>
-  <si>
-    <t>CAN</t>
-  </si>
-  <si>
-    <t>02:15</t>
-  </si>
-  <si>
-    <t>03:15</t>
-  </si>
-  <si>
-    <t>04:20</t>
-  </si>
-  <si>
-    <t>VN-A644</t>
-  </si>
-  <si>
-    <t>10:54</t>
-  </si>
-  <si>
-    <t>18:10</t>
-  </si>
-  <si>
-    <t>00:30</t>
-  </si>
-  <si>
-    <t>VN-A645</t>
-  </si>
-  <si>
-    <t>13:34</t>
-  </si>
-  <si>
-    <t>22:40</t>
-  </si>
-  <si>
-    <t>VN-A646</t>
-  </si>
-  <si>
-    <t>HKT</t>
-  </si>
-  <si>
-    <t>23:00</t>
-  </si>
-  <si>
-    <t>VN-A647</t>
-  </si>
-  <si>
-    <t>07:46</t>
-  </si>
-  <si>
-    <t>TPE</t>
-  </si>
-  <si>
-    <t>VN-A648</t>
-  </si>
-  <si>
-    <t>VN-A649</t>
-  </si>
-  <si>
-    <t>05:40</t>
-  </si>
-  <si>
-    <t>06:51</t>
-  </si>
-  <si>
-    <t>10:33</t>
-  </si>
-  <si>
-    <t>13:15</t>
-  </si>
-  <si>
-    <t>14:35</t>
-  </si>
-  <si>
-    <t>VN-A653</t>
-  </si>
-  <si>
-    <t>KUL</t>
-  </si>
-  <si>
-    <t>12:35</t>
-  </si>
-  <si>
-    <t>12:43</t>
-  </si>
-  <si>
-    <t>HND</t>
-  </si>
-  <si>
-    <t>01:00</t>
-  </si>
-  <si>
-    <t>02:30</t>
-  </si>
-  <si>
-    <t>VN-A657</t>
-  </si>
-  <si>
-    <t>10:42</t>
-  </si>
-  <si>
-    <t>VN-A658</t>
-  </si>
-  <si>
-    <t>09:17</t>
-  </si>
-  <si>
-    <t>12:02</t>
-  </si>
-  <si>
-    <t>PKX</t>
-  </si>
-  <si>
-    <t>22:00</t>
-  </si>
-  <si>
-    <t>03:05</t>
-  </si>
-  <si>
-    <t>VN-A661</t>
-  </si>
-  <si>
-    <t>06:25</t>
-  </si>
-  <si>
-    <t>08:46</t>
-  </si>
-  <si>
-    <t>12:55</t>
-  </si>
-  <si>
-    <t>WUX</t>
-  </si>
-  <si>
-    <t>14:15</t>
-  </si>
-  <si>
-    <t>19:00</t>
-  </si>
-  <si>
-    <t>VN-A663</t>
-  </si>
-  <si>
-    <t>HIJ</t>
-  </si>
-  <si>
-    <t>12:54</t>
-  </si>
-  <si>
-    <t>21:50</t>
-  </si>
-  <si>
-    <t>23:15</t>
-  </si>
-  <si>
-    <t>VN-A667</t>
-  </si>
-  <si>
-    <t>01:30</t>
-  </si>
-  <si>
-    <t>04:10</t>
-  </si>
-  <si>
-    <t>VN-A668</t>
-  </si>
-  <si>
-    <t>TNN</t>
-  </si>
-  <si>
-    <t>11:33</t>
-  </si>
-  <si>
-    <t>PVG</t>
-  </si>
-  <si>
-    <t>01:15</t>
-  </si>
-  <si>
-    <t>02:20</t>
-  </si>
-  <si>
-    <t>05:15</t>
-  </si>
-  <si>
-    <t>VN-A669</t>
-  </si>
-  <si>
-    <t>VCL</t>
-  </si>
-  <si>
-    <t>07:24</t>
-  </si>
-  <si>
-    <t>11:44</t>
-  </si>
-  <si>
-    <t>19:35</t>
-  </si>
-  <si>
-    <t>22:55</t>
-  </si>
-  <si>
-    <t>VN-A670</t>
-  </si>
-  <si>
-    <t>12:03</t>
-  </si>
-  <si>
-    <t>VN-A672</t>
-  </si>
-  <si>
-    <t>FSZ</t>
-  </si>
-  <si>
-    <t>14:21</t>
-  </si>
-  <si>
-    <t>ENH</t>
-  </si>
-  <si>
-    <t>VN-A673</t>
-  </si>
-  <si>
-    <t>10:23</t>
-  </si>
-  <si>
-    <t>02:50</t>
-  </si>
-  <si>
-    <t>03:45</t>
-  </si>
-  <si>
-    <t>05:30</t>
-  </si>
-  <si>
-    <t>VN-A674</t>
-  </si>
-  <si>
-    <t>08:13</t>
-  </si>
-  <si>
-    <t>09:35</t>
-  </si>
-  <si>
-    <t>13:41</t>
-  </si>
-  <si>
-    <t>DEL</t>
-  </si>
-  <si>
-    <t>05:35</t>
-  </si>
-  <si>
-    <t>VN-A675</t>
-  </si>
-  <si>
-    <t>07:51</t>
-  </si>
-  <si>
-    <t>10:01</t>
-  </si>
-  <si>
-    <t>11:42</t>
-  </si>
-  <si>
-    <t>00:50</t>
-  </si>
-  <si>
-    <t>VN-A676</t>
-  </si>
-  <si>
-    <t>16:35</t>
-  </si>
-  <si>
-    <t>CMB</t>
-  </si>
-  <si>
-    <t>22:05</t>
-  </si>
-  <si>
-    <t>05:50</t>
-  </si>
-  <si>
-    <t>VN-A677</t>
-  </si>
-  <si>
-    <t>VN-A683</t>
-  </si>
-  <si>
-    <t>FUK</t>
-  </si>
-  <si>
-    <t>RMQ</t>
-  </si>
-  <si>
-    <t>VN-A684</t>
-  </si>
-  <si>
-    <t>06:45</t>
-  </si>
-  <si>
-    <t>09:21</t>
-  </si>
-  <si>
-    <t>22:45</t>
-  </si>
-  <si>
-    <t>VN-A685</t>
-  </si>
-  <si>
-    <t>11:14</t>
-  </si>
-  <si>
-    <t>01:45</t>
-  </si>
-  <si>
-    <t>VN-A687</t>
-  </si>
-  <si>
-    <t>VN-A689</t>
-  </si>
-  <si>
-    <t>08:04</t>
-  </si>
-  <si>
-    <t>VN-A697</t>
-  </si>
-  <si>
-    <t>10:49</t>
-  </si>
-  <si>
-    <t>15:15</t>
-  </si>
-  <si>
-    <t>HYD</t>
-  </si>
-  <si>
     <t>VN-A810</t>
   </si>
   <si>
@@ -1331,6 +1343,9 @@
     <t>SYD</t>
   </si>
   <si>
+    <t>18:02</t>
+  </si>
+  <si>
     <t>P</t>
   </si>
   <si>
@@ -1358,6 +1373,9 @@
     <t>BNE</t>
   </si>
   <si>
+    <t>22:07</t>
+  </si>
+  <si>
     <t>05:05</t>
   </si>
   <si>
@@ -1385,7 +1403,7 @@
     <t>Total Record(s): 348</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 29, 2026 10:13</t>
+    <t xml:space="preserve">Generated on  Oct 29, 2026 10:56</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -3695,7 +3713,7 @@
         <v>13</v>
       </c>
       <c r="B64" s="7">
-        <v>278</v>
+        <v>860</v>
       </c>
       <c t="s" r="C64" s="7">
         <v>14</v>
@@ -3711,13 +3729,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H64" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I64" s="7">
         <v>135</v>
       </c>
-      <c t="s" r="I64" s="7">
-        <v>136</v>
-      </c>
       <c t="s" r="J64" s="7">
-        <v>45</v>
+        <v>129</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
@@ -3728,7 +3746,7 @@
         <v>13</v>
       </c>
       <c r="B65" s="7">
-        <v>279</v>
+        <v>861</v>
       </c>
       <c t="s" r="C65" s="7">
         <v>14</v>
@@ -3741,13 +3759,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G65" s="8">
-        <v>135</v>
+        <v>36</v>
       </c>
       <c t="s" r="H65" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>32</v>
+        <v>136</v>
       </c>
       <c t="s" r="J65" s="7">
         <v>137</v>
@@ -3758,10 +3776,10 @@
     </row>
     <row r="66" ht="14.25" customHeight="1">
       <c t="s" r="A66" s="6">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B66" s="7">
-        <v>883</v>
+        <v>862</v>
       </c>
       <c t="s" r="C66" s="7">
         <v>14</v>
@@ -3777,88 +3795,90 @@
         <v>26</v>
       </c>
       <c t="s" r="H66" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="I66" s="7">
+        <v>39</v>
+      </c>
+      <c t="s" r="J66" s="7">
         <v>138</v>
-      </c>
-      <c t="s" r="I66" s="7">
-        <v>139</v>
-      </c>
-      <c t="s" r="J66" s="7">
-        <v>140</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
       <c r="M66" s="7"/>
     </row>
     <row r="67" ht="14.25" customHeight="1">
-      <c t="s" r="A67" s="6">
-        <v>38</v>
-      </c>
-      <c r="B67" s="7">
-        <v>884</v>
-      </c>
-      <c t="s" r="C67" s="7">
-        <v>14</v>
-      </c>
+      <c r="A67" s="6"/>
+      <c r="B67" s="7"/>
+      <c r="C67" s="7"/>
       <c r="D67" s="7"/>
-      <c t="s" r="E67" s="7">
-        <v>131</v>
-      </c>
-      <c r="F67" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G67" s="8">
-        <v>138</v>
-      </c>
-      <c t="s" r="H67" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I67" s="7">
-        <v>141</v>
-      </c>
-      <c t="s" r="J67" s="7">
-        <v>119</v>
-      </c>
+      <c r="E67" s="7"/>
+      <c r="F67" s="7"/>
+      <c r="G67" s="8"/>
+      <c r="H67" s="8"/>
+      <c r="I67" s="7"/>
+      <c r="J67" s="7"/>
       <c r="K67" s="7"/>
       <c r="L67" s="7"/>
       <c r="M67" s="7"/>
     </row>
     <row r="68" ht="14.25" customHeight="1">
-      <c r="A68" s="6"/>
-      <c r="B68" s="7"/>
-      <c r="C68" s="7"/>
+      <c t="s" r="A68" s="6">
+        <v>13</v>
+      </c>
+      <c r="B68" s="7">
+        <v>567</v>
+      </c>
+      <c t="s" r="C68" s="7">
+        <v>14</v>
+      </c>
       <c r="D68" s="7"/>
-      <c r="E68" s="7"/>
-      <c r="F68" s="7"/>
-      <c r="G68" s="8"/>
-      <c r="H68" s="8"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7"/>
+      <c t="s" r="E68" s="7">
+        <v>139</v>
+      </c>
+      <c r="F68" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G68" s="8">
+        <v>42</v>
+      </c>
+      <c t="s" r="H68" s="8">
+        <v>140</v>
+      </c>
+      <c t="s" r="I68" s="7">
+        <v>141</v>
+      </c>
+      <c t="s" r="J68" s="7">
+        <v>142</v>
+      </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
-      <c r="M68" s="7"/>
+      <c t="s" r="M68" s="7">
+        <v>143</v>
+      </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
       <c t="s" r="A69" s="6">
         <v>13</v>
       </c>
       <c r="B69" s="7">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c t="s" r="C69" s="7">
         <v>14</v>
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
+        <v>140</v>
+      </c>
+      <c t="s" r="H69" s="8">
         <v>42</v>
-      </c>
-      <c t="s" r="H69" s="8">
-        <v>143</v>
       </c>
       <c t="s" r="I69" s="7">
         <v>144</v>
@@ -3877,23 +3897,23 @@
         <v>13</v>
       </c>
       <c r="B70" s="7">
-        <v>566</v>
+        <v>447</v>
       </c>
       <c t="s" r="C70" s="7">
         <v>14</v>
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G70" s="8">
-        <v>143</v>
+        <v>42</v>
       </c>
       <c t="s" r="H70" s="8">
-        <v>42</v>
+        <v>17</v>
       </c>
       <c t="s" r="I70" s="7">
         <v>147</v>
@@ -3912,64 +3932,62 @@
         <v>13</v>
       </c>
       <c r="B71" s="7">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c t="s" r="C71" s="7">
         <v>14</v>
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G71" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H71" s="8">
         <v>42</v>
       </c>
-      <c t="s" r="H71" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I71" s="7">
-        <v>150</v>
+        <v>66</v>
       </c>
       <c t="s" r="J71" s="7">
-        <v>151</v>
+        <v>33</v>
       </c>
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
-      <c t="s" r="M71" s="7">
-        <v>152</v>
-      </c>
+      <c r="M71" s="7"/>
     </row>
     <row r="72" ht="14.25" customHeight="1">
       <c t="s" r="A72" s="6">
         <v>13</v>
       </c>
       <c r="B72" s="7">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c t="s" r="C72" s="7">
         <v>14</v>
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G72" s="8">
+        <v>42</v>
+      </c>
+      <c t="s" r="H72" s="8">
         <v>17</v>
       </c>
-      <c t="s" r="H72" s="8">
-        <v>42</v>
-      </c>
       <c t="s" r="I72" s="7">
-        <v>66</v>
+        <v>150</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>33</v>
+        <v>151</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -3980,29 +3998,29 @@
         <v>13</v>
       </c>
       <c r="B73" s="7">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c t="s" r="C73" s="7">
         <v>14</v>
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G73" s="8">
+        <v>17</v>
+      </c>
+      <c t="s" r="H73" s="8">
         <v>42</v>
       </c>
-      <c t="s" r="H73" s="8">
-        <v>17</v>
-      </c>
       <c t="s" r="I73" s="7">
+        <v>152</v>
+      </c>
+      <c t="s" r="J73" s="7">
         <v>153</v>
-      </c>
-      <c t="s" r="J73" s="7">
-        <v>154</v>
       </c>
       <c r="K73" s="7"/>
       <c r="L73" s="7"/>
@@ -4013,147 +4031,147 @@
         <v>13</v>
       </c>
       <c r="B74" s="7">
-        <v>446</v>
+        <v>1169</v>
       </c>
       <c t="s" r="C74" s="7">
         <v>14</v>
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G74" s="8">
-        <v>17</v>
+        <v>42</v>
       </c>
       <c t="s" r="H74" s="8">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c t="s" r="I74" s="7">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>156</v>
+        <v>115</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
       <c r="M74" s="7"/>
     </row>
     <row r="75" ht="15" customHeight="1">
-      <c t="s" r="A75" s="6">
-        <v>13</v>
-      </c>
-      <c r="B75" s="7">
-        <v>1169</v>
-      </c>
-      <c t="s" r="C75" s="7">
-        <v>14</v>
-      </c>
+      <c r="A75" s="6"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
       <c r="D75" s="7"/>
-      <c t="s" r="E75" s="7">
-        <v>142</v>
-      </c>
-      <c r="F75" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G75" s="8">
-        <v>42</v>
-      </c>
-      <c t="s" r="H75" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I75" s="7">
-        <v>140</v>
-      </c>
-      <c t="s" r="J75" s="7">
-        <v>115</v>
-      </c>
+      <c r="E75" s="7"/>
+      <c r="F75" s="7"/>
+      <c r="G75" s="8"/>
+      <c r="H75" s="8"/>
+      <c r="I75" s="7"/>
+      <c r="J75" s="7"/>
       <c r="K75" s="7"/>
       <c r="L75" s="7"/>
       <c r="M75" s="7"/>
     </row>
     <row r="76" ht="14.25" customHeight="1">
-      <c r="A76" s="6"/>
-      <c r="B76" s="7"/>
-      <c r="C76" s="7"/>
+      <c t="s" r="A76" s="6">
+        <v>13</v>
+      </c>
+      <c r="B76" s="7">
+        <v>863</v>
+      </c>
+      <c t="s" r="C76" s="7">
+        <v>14</v>
+      </c>
       <c r="D76" s="7"/>
-      <c r="E76" s="7"/>
-      <c r="F76" s="7"/>
-      <c r="G76" s="8"/>
-      <c r="H76" s="8"/>
-      <c r="I76" s="7"/>
-      <c r="J76" s="7"/>
-      <c r="K76" s="7"/>
+      <c t="s" r="E76" s="7">
+        <v>155</v>
+      </c>
+      <c r="F76" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G76" s="8">
+        <v>36</v>
+      </c>
+      <c t="s" r="H76" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I76" s="7">
+        <v>156</v>
+      </c>
+      <c t="s" r="J76" s="7">
+        <v>157</v>
+      </c>
+      <c t="s" r="K76" s="7">
+        <v>158</v>
+      </c>
       <c r="L76" s="7"/>
-      <c r="M76" s="7"/>
+      <c t="s" r="M76" s="7">
+        <v>159</v>
+      </c>
     </row>
     <row r="77" ht="14.25" customHeight="1">
       <c t="s" r="A77" s="6">
         <v>13</v>
       </c>
       <c r="B77" s="7">
-        <v>863</v>
+        <v>358</v>
       </c>
       <c t="s" r="C77" s="7">
         <v>14</v>
       </c>
       <c r="D77" s="7"/>
       <c t="s" r="E77" s="7">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F77" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G77" s="8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c t="s" r="H77" s="8">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c t="s" r="J77" s="7">
-        <v>159</v>
-      </c>
-      <c t="s" r="K77" s="7">
-        <v>160</v>
-      </c>
+        <v>161</v>
+      </c>
+      <c r="K77" s="7"/>
       <c r="L77" s="7"/>
-      <c t="s" r="M77" s="7">
-        <v>161</v>
-      </c>
+      <c r="M77" s="7"/>
     </row>
     <row r="78" ht="14.25" customHeight="1">
       <c t="s" r="A78" s="6">
         <v>13</v>
       </c>
       <c r="B78" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c t="s" r="C78" s="7">
         <v>14</v>
       </c>
       <c r="D78" s="7"/>
       <c t="s" r="E78" s="7">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F78" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G78" s="8">
-        <v>26</v>
+        <v>160</v>
       </c>
       <c t="s" r="H78" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="I78" s="7">
         <v>162</v>
       </c>
-      <c t="s" r="I78" s="7">
-        <v>153</v>
-      </c>
       <c t="s" r="J78" s="7">
-        <v>163</v>
+        <v>74</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4164,29 +4182,29 @@
         <v>13</v>
       </c>
       <c r="B79" s="7">
-        <v>359</v>
+        <v>1803</v>
       </c>
       <c t="s" r="C79" s="7">
         <v>14</v>
       </c>
       <c r="D79" s="7"/>
       <c t="s" r="E79" s="7">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F79" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G79" s="8">
-        <v>162</v>
+        <v>26</v>
       </c>
       <c t="s" r="H79" s="8">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c t="s" r="I79" s="7">
         <v>164</v>
       </c>
       <c t="s" r="J79" s="7">
-        <v>74</v>
+        <v>165</v>
       </c>
       <c r="K79" s="7"/>
       <c r="L79" s="7"/>
@@ -4197,115 +4215,117 @@
         <v>13</v>
       </c>
       <c r="B80" s="7">
-        <v>168</v>
+        <v>1804</v>
       </c>
       <c t="s" r="C80" s="7">
         <v>14</v>
       </c>
       <c r="D80" s="7"/>
       <c t="s" r="E80" s="7">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F80" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G80" s="8">
-        <v>26</v>
+        <v>163</v>
       </c>
       <c t="s" r="H80" s="8">
-        <v>42</v>
+        <v>26</v>
       </c>
       <c t="s" r="I80" s="7">
-        <v>27</v>
+        <v>166</v>
       </c>
       <c t="s" r="J80" s="7">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="K80" s="7"/>
       <c r="L80" s="7"/>
       <c r="M80" s="7"/>
     </row>
     <row r="81" ht="14.25" customHeight="1">
-      <c t="s" r="A81" s="6">
-        <v>13</v>
-      </c>
-      <c r="B81" s="7">
-        <v>123</v>
-      </c>
-      <c t="s" r="C81" s="7">
-        <v>14</v>
-      </c>
+      <c r="A81" s="6"/>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
       <c r="D81" s="7"/>
-      <c t="s" r="E81" s="7">
-        <v>157</v>
-      </c>
-      <c r="F81" s="7">
-        <v>321</v>
-      </c>
-      <c t="s" r="G81" s="8">
-        <v>42</v>
-      </c>
-      <c t="s" r="H81" s="8">
-        <v>26</v>
-      </c>
-      <c t="s" r="I81" s="7">
-        <v>90</v>
-      </c>
-      <c t="s" r="J81" s="7">
-        <v>166</v>
-      </c>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="8"/>
+      <c r="I81" s="7"/>
+      <c r="J81" s="7"/>
       <c r="K81" s="7"/>
       <c r="L81" s="7"/>
       <c r="M81" s="7"/>
     </row>
     <row r="82" ht="14.25" customHeight="1">
-      <c r="A82" s="6"/>
-      <c r="B82" s="7"/>
-      <c r="C82" s="7"/>
+      <c t="s" r="A82" s="6">
+        <v>13</v>
+      </c>
+      <c r="B82" s="7">
+        <v>602</v>
+      </c>
+      <c t="s" r="C82" s="7">
+        <v>14</v>
+      </c>
       <c r="D82" s="7"/>
-      <c r="E82" s="7"/>
-      <c r="F82" s="7"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="8"/>
-      <c r="I82" s="7"/>
-      <c r="J82" s="7"/>
+      <c t="s" r="E82" s="7">
+        <v>168</v>
+      </c>
+      <c r="F82" s="7">
+        <v>321</v>
+      </c>
+      <c t="s" r="G82" s="8">
+        <v>26</v>
+      </c>
+      <c t="s" r="H82" s="8">
+        <v>169</v>
+      </c>
+      <c t="s" r="I82" s="7">
+        <v>170</v>
+      </c>
+      <c t="s" r="J82" s="7">
+        <v>171</v>
+      </c>
       <c r="K82" s="7"/>
       <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
+      <c t="s" r="M82" s="7">
+        <v>172</v>
+      </c>
     </row>
     <row r="83" ht="14.25" customHeight="1">
       <c t="s" r="A83" s="6">
         <v>13</v>
       </c>
       <c r="B83" s="7">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c t="s" r="C83" s="7">
         <v>14</v>
       </c>
       <c r="D83" s="7"/>
       <c t="s" r="E83" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F83" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G83" s="8">
-        <v>26</v>
+        <v>169</v>
       </c>
       <c t="s" r="H83" s="8">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>169</v>
+        <v>138</v>
       </c>
       <c t="s" r="J83" s="7">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="K83" s="7"/>
       <c r="L83" s="7"/>
       <c t="s" r="M83" s="7">
-        <v>171</v>
+        <v>174</v>
       </c>
     </row>
     <row r="84" ht="14.25" customHeight="1">
@@ -4313,95 +4333,103 @@
         <v>13</v>
       </c>
       <c r="B84" s="7">
-        <v>603</v>
+        <v>278</v>
       </c>
       <c t="s" r="C84" s="7">
         <v>14</v>
       </c>
       <c r="D84" s="7"/>
       <c t="s" r="E84" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F84" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G84" s="8">
-        <v>168</v>
+        <v>26</v>
       </c>
       <c t="s" r="H84" s="8">
-        <v>26</v>
+        <v>175</v>
       </c>
       <c t="s" r="I84" s="7">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c t="s" r="J84" s="7">
-        <v>173</v>
-      </c>
-      <c r="K84" s="7"/>
+        <v>45</v>
+      </c>
+      <c t="s" r="K84" s="7">
+        <v>177</v>
+      </c>
       <c r="L84" s="7"/>
-      <c r="M84" s="7"/>
+      <c t="s" r="M84" s="7">
+        <v>178</v>
+      </c>
     </row>
     <row r="85" ht="15" customHeight="1">
       <c t="s" r="A85" s="6">
         <v>13</v>
       </c>
       <c r="B85" s="7">
-        <v>860</v>
+        <v>279</v>
       </c>
       <c t="s" r="C85" s="7">
         <v>14</v>
       </c>
       <c r="D85" s="7"/>
       <c t="s" r="E85" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F85" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G85" s="8">
-        <v>26</v>
+        <v>175</v>
       </c>
       <c t="s" r="H85" s="8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c t="s" r="I85" s="7">
-        <v>174</v>
+        <v>32</v>
       </c>
       <c t="s" r="J85" s="7">
-        <v>129</v>
-      </c>
-      <c r="K85" s="7"/>
+        <v>179</v>
+      </c>
+      <c t="s" r="K85" s="7">
+        <v>125</v>
+      </c>
       <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
+      <c t="s" r="M85" s="7">
+        <v>86</v>
+      </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
       <c t="s" r="A86" s="6">
         <v>13</v>
       </c>
       <c r="B86" s="7">
-        <v>861</v>
+        <v>168</v>
       </c>
       <c t="s" r="C86" s="7">
         <v>14</v>
       </c>
       <c r="D86" s="7"/>
       <c t="s" r="E86" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F86" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G86" s="8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c t="s" r="I86" s="7">
-        <v>175</v>
+        <v>27</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4409,32 +4437,32 @@
     </row>
     <row r="87" ht="14.25" customHeight="1">
       <c t="s" r="A87" s="6">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="B87" s="7">
-        <v>862</v>
+        <v>123</v>
       </c>
       <c t="s" r="C87" s="7">
         <v>14</v>
       </c>
       <c r="D87" s="7"/>
       <c t="s" r="E87" s="7">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F87" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>26</v>
+        <v>42</v>
       </c>
       <c t="s" r="H87" s="8">
-        <v>36</v>
+        <v>26</v>
       </c>
       <c t="s" r="I87" s="7">
-        <v>39</v>
+        <v>90</v>
       </c>
       <c t="s" r="J87" s="7">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="K87" s="7"/>
       <c r="L87" s="7"/>
@@ -4467,7 +4495,7 @@
       </c>
       <c r="D89" s="7"/>
       <c t="s" r="E89" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F89" s="7">
         <v>321</v>
@@ -4479,10 +4507,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I89" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c t="s" r="J89" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="K89" s="7"/>
       <c r="L89" s="7"/>
@@ -4502,7 +4530,7 @@
       </c>
       <c r="D90" s="7"/>
       <c t="s" r="E90" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F90" s="7">
         <v>321</v>
@@ -4511,18 +4539,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H90" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="I90" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c t="s" r="J90" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>182</v>
+        <v>187</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4537,13 +4565,13 @@
       </c>
       <c r="D91" s="7"/>
       <c t="s" r="E91" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F91" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G91" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="H91" s="8">
         <v>26</v>
@@ -4552,7 +4580,7 @@
         <v>22</v>
       </c>
       <c t="s" r="J91" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K91" s="7"/>
       <c r="L91" s="7"/>
@@ -4570,7 +4598,7 @@
       </c>
       <c r="D92" s="7"/>
       <c t="s" r="E92" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F92" s="7">
         <v>321</v>
@@ -4579,13 +4607,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H92" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="I92" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c t="s" r="J92" s="7">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="K92" s="7"/>
       <c r="L92" s="7"/>
@@ -4603,19 +4631,19 @@
       </c>
       <c r="D93" s="7"/>
       <c t="s" r="E93" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F93" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G93" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="H93" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I93" s="7">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c t="s" r="J93" s="7">
         <v>35</v>
@@ -4636,7 +4664,7 @@
       </c>
       <c r="D94" s="7"/>
       <c t="s" r="E94" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F94" s="7">
         <v>321</v>
@@ -4648,7 +4676,7 @@
         <v>118</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>130</v>
@@ -4669,7 +4697,7 @@
       </c>
       <c r="D95" s="7"/>
       <c t="s" r="E95" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F95" s="7">
         <v>321</v>
@@ -4681,10 +4709,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I95" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="J95" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c r="K95" s="7"/>
       <c r="L95" s="7"/>
@@ -4702,7 +4730,7 @@
       </c>
       <c r="D96" s="7"/>
       <c t="s" r="E96" s="7">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="F96" s="7">
         <v>321</v>
@@ -4714,7 +4742,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>55</v>
@@ -4750,7 +4778,7 @@
       </c>
       <c r="D98" s="7"/>
       <c t="s" r="E98" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F98" s="7">
         <v>321</v>
@@ -4762,15 +4790,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I98" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J98" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="K98" s="7"/>
       <c r="L98" s="7"/>
       <c t="s" r="M98" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
     </row>
     <row r="99" ht="14.25" customHeight="1">
@@ -4785,7 +4813,7 @@
       </c>
       <c r="D99" s="7"/>
       <c t="s" r="E99" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F99" s="7">
         <v>321</v>
@@ -4818,7 +4846,7 @@
       </c>
       <c r="D100" s="7"/>
       <c t="s" r="E100" s="7">
-        <v>189</v>
+        <v>194</v>
       </c>
       <c r="F100" s="7">
         <v>321</v>
@@ -4830,10 +4858,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I100" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J100" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K100" s="7"/>
       <c r="L100" s="7"/>
@@ -4866,7 +4894,7 @@
       </c>
       <c r="D102" s="7"/>
       <c t="s" r="E102" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F102" s="7">
         <v>321</v>
@@ -4878,15 +4906,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I102" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c t="s" r="J102" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K102" s="7"/>
       <c r="L102" s="7"/>
       <c t="s" r="M102" s="7">
-        <v>197</v>
+        <v>202</v>
       </c>
     </row>
     <row r="103" ht="14.25" customHeight="1">
@@ -4901,7 +4929,7 @@
       </c>
       <c r="D103" s="7"/>
       <c t="s" r="E103" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F103" s="7">
         <v>321</v>
@@ -4913,15 +4941,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I103" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c t="s" r="J103" s="7">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="K103" s="7"/>
       <c r="L103" s="7"/>
       <c t="s" r="M103" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="104" ht="14.25" customHeight="1">
@@ -4936,7 +4964,7 @@
       </c>
       <c r="D104" s="7"/>
       <c t="s" r="E104" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F104" s="7">
         <v>321</v>
@@ -4948,14 +4976,16 @@
         <v>118</v>
       </c>
       <c t="s" r="I104" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="J104" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="K104" s="7"/>
       <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
+      <c t="s" r="M104" s="7">
+        <v>207</v>
+      </c>
     </row>
     <row r="105" ht="15" customHeight="1">
       <c t="s" r="A105" s="6">
@@ -4969,7 +4999,7 @@
       </c>
       <c r="D105" s="7"/>
       <c t="s" r="E105" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F105" s="7">
         <v>321</v>
@@ -4984,7 +5014,7 @@
         <v>98</v>
       </c>
       <c t="s" r="J105" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="K105" s="7"/>
       <c r="L105" s="7"/>
@@ -5002,7 +5032,7 @@
       </c>
       <c r="D106" s="7"/>
       <c t="s" r="E106" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F106" s="7">
         <v>321</v>
@@ -5017,7 +5047,7 @@
         <v>112</v>
       </c>
       <c t="s" r="J106" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K106" s="7"/>
       <c r="L106" s="7"/>
@@ -5035,7 +5065,7 @@
       </c>
       <c r="D107" s="7"/>
       <c t="s" r="E107" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F107" s="7">
         <v>321</v>
@@ -5050,7 +5080,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J107" s="7">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K107" s="7"/>
       <c r="L107" s="7"/>
@@ -5068,7 +5098,7 @@
       </c>
       <c r="D108" s="7"/>
       <c t="s" r="E108" s="7">
-        <v>194</v>
+        <v>199</v>
       </c>
       <c r="F108" s="7">
         <v>321</v>
@@ -5083,7 +5113,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J108" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c r="K108" s="7"/>
       <c r="L108" s="7"/>
@@ -5112,11 +5142,11 @@
         <v>6847</v>
       </c>
       <c t="s" r="C110" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D110" s="7"/>
       <c t="s" r="E110" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F110" s="7">
         <v>321</v>
@@ -5128,7 +5158,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I110" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c t="s" r="J110" s="7">
         <v>95</v>
@@ -5136,7 +5166,7 @@
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
       <c t="s" r="M110" s="7">
-        <v>206</v>
+        <v>212</v>
       </c>
     </row>
     <row r="111" ht="14.25" customHeight="1">
@@ -5147,11 +5177,11 @@
         <v>6848</v>
       </c>
       <c t="s" r="C111" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D111" s="7"/>
       <c t="s" r="E111" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F111" s="7">
         <v>321</v>
@@ -5166,7 +5196,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J111" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K111" s="7"/>
       <c r="L111" s="7"/>
@@ -5180,11 +5210,11 @@
         <v>6848</v>
       </c>
       <c t="s" r="C112" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D112" s="7"/>
       <c t="s" r="E112" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F112" s="7">
         <v>321</v>
@@ -5193,13 +5223,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H112" s="8">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c t="s" r="I112" s="7">
         <v>23</v>
       </c>
       <c t="s" r="J112" s="7">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="K112" s="7"/>
       <c r="L112" s="7"/>
@@ -5213,23 +5243,23 @@
         <v>6849</v>
       </c>
       <c t="s" r="C113" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D113" s="7"/>
       <c t="s" r="E113" s="7">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F113" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G113" s="8">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c t="s" r="H113" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I113" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c t="s" r="J113" s="7">
         <v>116</v>
@@ -5265,7 +5295,7 @@
       </c>
       <c r="D115" s="7"/>
       <c t="s" r="E115" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F115" s="7">
         <v>321</v>
@@ -5274,18 +5304,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H115" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="I115" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J115" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5300,13 +5330,13 @@
       </c>
       <c r="D116" s="7"/>
       <c t="s" r="E116" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F116" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G116" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="H116" s="8">
         <v>26</v>
@@ -5315,12 +5345,12 @@
         <v>56</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
       <c t="s" r="M116" s="7">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="117" ht="14.25" customHeight="1">
@@ -5335,7 +5365,7 @@
       </c>
       <c r="D117" s="7"/>
       <c t="s" r="E117" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F117" s="7">
         <v>321</v>
@@ -5350,12 +5380,12 @@
         <v>31</v>
       </c>
       <c t="s" r="J117" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K117" s="7"/>
       <c r="L117" s="7"/>
       <c t="s" r="M117" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="118" ht="14.25" customHeight="1">
@@ -5370,7 +5400,7 @@
       </c>
       <c r="D118" s="7"/>
       <c t="s" r="E118" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F118" s="7">
         <v>321</v>
@@ -5385,7 +5415,7 @@
         <v>19</v>
       </c>
       <c t="s" r="J118" s="7">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="K118" s="7"/>
       <c r="L118" s="7"/>
@@ -5403,7 +5433,7 @@
       </c>
       <c r="D119" s="7"/>
       <c t="s" r="E119" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F119" s="7">
         <v>321</v>
@@ -5412,13 +5442,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H119" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I119" s="7">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c t="s" r="J119" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="K119" s="7"/>
       <c r="L119" s="7"/>
@@ -5436,19 +5466,19 @@
       </c>
       <c r="D120" s="7"/>
       <c t="s" r="E120" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F120" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G120" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H120" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I120" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c t="s" r="J120" s="7">
         <v>72</v>
@@ -5469,7 +5499,7 @@
       </c>
       <c r="D121" s="7"/>
       <c t="s" r="E121" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F121" s="7">
         <v>321</v>
@@ -5478,13 +5508,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H121" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5502,22 +5532,22 @@
       </c>
       <c r="D122" s="7"/>
       <c t="s" r="E122" s="7">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="F122" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G122" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H122" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J122" s="7">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="K122" s="7"/>
       <c r="L122" s="7"/>
@@ -5550,7 +5580,7 @@
       </c>
       <c r="D124" s="7"/>
       <c t="s" r="E124" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F124" s="7">
         <v>321</v>
@@ -5585,7 +5615,7 @@
       </c>
       <c r="D125" s="7"/>
       <c t="s" r="E125" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F125" s="7">
         <v>321</v>
@@ -5618,7 +5648,7 @@
       </c>
       <c r="D126" s="7"/>
       <c t="s" r="E126" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F126" s="7">
         <v>321</v>
@@ -5651,7 +5681,7 @@
       </c>
       <c r="D127" s="7"/>
       <c t="s" r="E127" s="7">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F127" s="7">
         <v>321</v>
@@ -5663,7 +5693,7 @@
         <v>81</v>
       </c>
       <c t="s" r="I127" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="J127" s="7">
         <v>56</v>
@@ -5699,7 +5729,7 @@
       </c>
       <c r="D129" s="7"/>
       <c t="s" r="E129" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F129" s="7">
         <v>321</v>
@@ -5708,10 +5738,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H129" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I129" s="7">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c t="s" r="J129" s="7">
         <v>23</v>
@@ -5732,13 +5762,13 @@
       </c>
       <c r="D130" s="7"/>
       <c t="s" r="E130" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F130" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G130" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H130" s="8">
         <v>73</v>
@@ -5747,7 +5777,7 @@
         <v>101</v>
       </c>
       <c t="s" r="J130" s="7">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K130" s="7"/>
       <c r="L130" s="7"/>
@@ -5765,7 +5795,7 @@
       </c>
       <c r="D131" s="7"/>
       <c t="s" r="E131" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F131" s="7">
         <v>321</v>
@@ -5780,7 +5810,7 @@
         <v>48</v>
       </c>
       <c t="s" r="J131" s="7">
-        <v>223</v>
+        <v>164</v>
       </c>
       <c r="K131" s="7"/>
       <c r="L131" s="7"/>
@@ -5798,7 +5828,7 @@
       </c>
       <c r="D132" s="7"/>
       <c t="s" r="E132" s="7">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="F132" s="7">
         <v>321</v>
@@ -5810,7 +5840,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I132" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c t="s" r="J132" s="7">
         <v>52</v>
@@ -5846,7 +5876,7 @@
       </c>
       <c r="D134" s="7"/>
       <c t="s" r="E134" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F134" s="7">
         <v>321</v>
@@ -5858,15 +5888,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I134" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J134" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K134" s="7"/>
       <c r="L134" s="7"/>
       <c t="s" r="M134" s="7">
-        <v>228</v>
+        <v>231</v>
       </c>
     </row>
     <row r="135" ht="15" customHeight="1">
@@ -5881,7 +5911,7 @@
       </c>
       <c r="D135" s="7"/>
       <c t="s" r="E135" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F135" s="7">
         <v>321</v>
@@ -5893,15 +5923,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
       <c t="s" r="M135" s="7">
-        <v>123</v>
+        <v>232</v>
       </c>
     </row>
     <row r="136" ht="14.25" customHeight="1">
@@ -5916,7 +5946,7 @@
       </c>
       <c r="D136" s="7"/>
       <c t="s" r="E136" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F136" s="7">
         <v>321</v>
@@ -5928,10 +5958,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I136" s="7">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c t="s" r="J136" s="7">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="K136" s="7"/>
       <c r="L136" s="7"/>
@@ -5949,7 +5979,7 @@
       </c>
       <c r="D137" s="7"/>
       <c t="s" r="E137" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F137" s="7">
         <v>321</v>
@@ -5961,10 +5991,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I137" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="J137" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K137" s="7"/>
       <c r="L137" s="7"/>
@@ -5982,7 +6012,7 @@
       </c>
       <c r="D138" s="7"/>
       <c t="s" r="E138" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F138" s="7">
         <v>321</v>
@@ -5994,7 +6024,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I138" s="7">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c t="s" r="J138" s="7">
         <v>76</v>
@@ -6015,7 +6045,7 @@
       </c>
       <c r="D139" s="7"/>
       <c t="s" r="E139" s="7">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="F139" s="7">
         <v>321</v>
@@ -6030,7 +6060,7 @@
         <v>77</v>
       </c>
       <c t="s" r="J139" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K139" s="7"/>
       <c r="L139" s="7"/>
@@ -6063,7 +6093,7 @@
       </c>
       <c r="D141" s="7"/>
       <c t="s" r="E141" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F141" s="7">
         <v>321</v>
@@ -6072,18 +6102,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H141" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="I141" s="7">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c t="s" r="J141" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K141" s="7"/>
       <c r="L141" s="7"/>
       <c t="s" r="M141" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="142" ht="14.25" customHeight="1">
@@ -6098,27 +6128,27 @@
       </c>
       <c r="D142" s="7"/>
       <c t="s" r="E142" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F142" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G142" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="H142" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I142" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J142" s="7">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K142" s="7"/>
       <c r="L142" s="7"/>
       <c t="s" r="M142" s="7">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="143" ht="14.25" customHeight="1">
@@ -6133,7 +6163,7 @@
       </c>
       <c r="D143" s="7"/>
       <c t="s" r="E143" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F143" s="7">
         <v>321</v>
@@ -6145,10 +6175,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I143" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c t="s" r="J143" s="7">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="K143" s="7"/>
       <c r="L143" s="7"/>
@@ -6166,7 +6196,7 @@
       </c>
       <c r="D144" s="7"/>
       <c t="s" r="E144" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F144" s="7">
         <v>321</v>
@@ -6175,13 +6205,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H144" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="I144" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J144" s="7">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="K144" s="7"/>
       <c r="L144" s="7"/>
@@ -6199,19 +6229,19 @@
       </c>
       <c r="D145" s="7"/>
       <c t="s" r="E145" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F145" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G145" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="H145" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I145" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J145" s="7">
         <v>88</v>
@@ -6232,7 +6262,7 @@
       </c>
       <c r="D146" s="7"/>
       <c t="s" r="E146" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F146" s="7">
         <v>321</v>
@@ -6244,7 +6274,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I146" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J146" s="7">
         <v>51</v>
@@ -6261,11 +6291,11 @@
         <v>6842</v>
       </c>
       <c t="s" r="C147" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D147" s="7"/>
       <c t="s" r="E147" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F147" s="7">
         <v>321</v>
@@ -6277,7 +6307,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I147" s="7">
-        <v>187</v>
+        <v>192</v>
       </c>
       <c t="s" r="J147" s="7">
         <v>92</v>
@@ -6294,11 +6324,11 @@
         <v>6842</v>
       </c>
       <c t="s" r="C148" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D148" s="7"/>
       <c t="s" r="E148" s="7">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F148" s="7">
         <v>321</v>
@@ -6307,13 +6337,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H148" s="8">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c t="s" r="I148" s="7">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6346,7 +6376,7 @@
       </c>
       <c r="D150" s="7"/>
       <c t="s" r="E150" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F150" s="7">
         <v>321</v>
@@ -6358,15 +6388,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I150" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c t="s" r="J150" s="7">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="K150" s="7"/>
       <c r="L150" s="7"/>
       <c t="s" r="M150" s="7">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="151" ht="14.25" customHeight="1">
@@ -6381,7 +6411,7 @@
       </c>
       <c r="D151" s="7"/>
       <c t="s" r="E151" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F151" s="7">
         <v>321</v>
@@ -6401,7 +6431,7 @@
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
       <c t="s" r="M151" s="7">
-        <v>250</v>
+        <v>254</v>
       </c>
     </row>
     <row r="152" ht="14.25" customHeight="1">
@@ -6416,7 +6446,7 @@
       </c>
       <c r="D152" s="7"/>
       <c t="s" r="E152" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F152" s="7">
         <v>321</v>
@@ -6428,10 +6458,10 @@
         <v>49</v>
       </c>
       <c t="s" r="I152" s="7">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c t="s" r="J152" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K152" s="7"/>
       <c r="L152" s="7"/>
@@ -6449,7 +6479,7 @@
       </c>
       <c r="D153" s="7"/>
       <c t="s" r="E153" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F153" s="7">
         <v>321</v>
@@ -6461,7 +6491,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I153" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J153" s="7">
         <v>23</v>
@@ -6482,7 +6512,7 @@
       </c>
       <c r="D154" s="7"/>
       <c t="s" r="E154" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F154" s="7">
         <v>321</v>
@@ -6515,7 +6545,7 @@
       </c>
       <c r="D155" s="7"/>
       <c t="s" r="E155" s="7">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F155" s="7">
         <v>321</v>
@@ -6563,29 +6593,29 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="K157" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6600,7 +6630,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6609,7 +6639,7 @@
         <v>42</v>
       </c>
       <c t="s" r="H158" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I158" s="7">
         <v>116</v>
@@ -6622,7 +6652,7 @@
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6633,23 +6663,23 @@
         <v>6862</v>
       </c>
       <c t="s" r="C159" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G159" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H159" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c t="s" r="J159" s="7">
         <v>53</v>
@@ -6666,11 +6696,11 @@
         <v>6862</v>
       </c>
       <c t="s" r="C160" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6679,13 +6709,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c t="s" r="I160" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6718,7 +6748,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6727,7 +6757,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="I162" s="7">
         <v>116</v>
@@ -6738,7 +6768,7 @@
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>262</v>
+        <v>266</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6753,22 +6783,22 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I163" s="7">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6786,7 +6816,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -6798,7 +6828,7 @@
         <v>81</v>
       </c>
       <c t="s" r="I164" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c t="s" r="J164" s="7">
         <v>18</v>
@@ -6834,7 +6864,7 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
@@ -6846,7 +6876,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c t="s" r="J166" s="7">
         <v>94</v>
@@ -6854,7 +6884,7 @@
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -6869,7 +6899,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -6881,7 +6911,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>19</v>
@@ -6889,7 +6919,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -6904,7 +6934,7 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
@@ -6913,10 +6943,10 @@
         <v>73</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J168" s="7">
         <v>125</v>
@@ -6937,19 +6967,19 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="H169" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>24</v>
@@ -6966,11 +6996,11 @@
         <v>5840</v>
       </c>
       <c t="s" r="C170" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
@@ -6979,13 +7009,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="I170" s="7">
         <v>52</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -6999,26 +7029,26 @@
         <v>5841</v>
       </c>
       <c t="s" r="C171" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="H171" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I171" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7051,7 +7081,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7060,18 +7090,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H173" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="I173" s="7">
         <v>134</v>
       </c>
       <c t="s" r="J173" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7086,27 +7116,27 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G174" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="H174" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I174" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c t="s" r="J174" s="7">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>109</v>
+        <v>280</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7121,7 +7151,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7133,7 +7163,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I175" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J175" s="7">
         <v>70</v>
@@ -7154,7 +7184,7 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
@@ -7166,7 +7196,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J176" s="7">
         <v>86</v>
@@ -7187,7 +7217,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7196,13 +7226,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H177" s="8">
+        <v>239</v>
+      </c>
+      <c t="s" r="I177" s="7">
         <v>235</v>
       </c>
-      <c t="s" r="I177" s="7">
-        <v>231</v>
-      </c>
       <c t="s" r="J177" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="K177" s="7"/>
       <c r="L177" s="7"/>
@@ -7220,22 +7250,22 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G178" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="H178" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I178" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7268,7 +7298,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7277,18 +7307,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H180" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c t="s" r="J180" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>280</v>
+        <v>285</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7303,22 +7333,22 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G181" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H181" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J181" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
@@ -7336,22 +7366,22 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G182" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="H182" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I182" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="J182" s="7">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
@@ -7369,22 +7399,22 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G183" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H183" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7402,22 +7432,22 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G184" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="H184" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7450,7 +7480,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7462,17 +7492,17 @@
         <v>111</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c t="s" r="K186" s="7">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="187" ht="14.25" customHeight="1">
@@ -7487,7 +7517,7 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
@@ -7505,11 +7535,11 @@
         <v>19</v>
       </c>
       <c t="s" r="K187" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7524,7 +7554,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7536,17 +7566,17 @@
         <v>26</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="J188" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c t="s" r="K188" s="7">
         <v>123</v>
       </c>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>288</v>
+        <v>178</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7561,7 +7591,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7573,10 +7603,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7594,7 +7624,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7606,10 +7636,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I190" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J190" s="7">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="K190" s="7"/>
       <c r="L190" s="7"/>
@@ -7642,7 +7672,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7654,15 +7684,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7677,7 +7707,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7689,15 +7719,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c t="s" r="J193" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K193" s="7"/>
       <c r="L193" s="7"/>
       <c t="s" r="M193" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
     </row>
     <row r="194" ht="14.25" customHeight="1">
@@ -7712,7 +7742,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7724,14 +7754,16 @@
         <v>73</v>
       </c>
       <c t="s" r="I194" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
-      <c r="M194" s="7"/>
+      <c t="s" r="M194" s="7">
+        <v>299</v>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c t="s" r="A195" s="6">
@@ -7745,7 +7777,7 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
@@ -7757,10 +7789,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
@@ -7778,7 +7810,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -7787,13 +7819,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c t="s" r="J196" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K196" s="7"/>
       <c r="L196" s="7"/>
@@ -7811,19 +7843,19 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="J197" s="7">
         <v>74</v>
@@ -7844,7 +7876,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -7859,7 +7891,7 @@
         <v>129</v>
       </c>
       <c t="s" r="J198" s="7">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="K198" s="7"/>
       <c r="L198" s="7"/>
@@ -7877,7 +7909,7 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
@@ -7892,7 +7924,7 @@
         <v>90</v>
       </c>
       <c t="s" r="J199" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K199" s="7"/>
       <c r="L199" s="7"/>
@@ -7925,7 +7957,7 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
@@ -7934,17 +7966,19 @@
         <v>73</v>
       </c>
       <c t="s" r="H201" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="I201" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="J201" s="7">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
-      <c r="M201" s="7"/>
+      <c t="s" r="M201" s="7">
+        <v>306</v>
+      </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
       <c t="s" r="A202" s="6">
@@ -7958,22 +7992,22 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G202" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="H202" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I202" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>288</v>
+        <v>178</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
@@ -7991,7 +8025,7 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
@@ -8003,7 +8037,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>48</v>
@@ -8024,7 +8058,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8039,7 +8073,7 @@
         <v>114</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8057,7 +8091,7 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
@@ -8069,7 +8103,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c t="s" r="J205" s="7">
         <v>90</v>
@@ -8090,7 +8124,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8105,7 +8139,7 @@
         <v>91</v>
       </c>
       <c t="s" r="J206" s="7">
-        <v>301</v>
+        <v>166</v>
       </c>
       <c r="K206" s="7"/>
       <c r="L206" s="7"/>
@@ -8138,7 +8172,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8150,15 +8184,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c t="s" r="J208" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>304</v>
+        <v>309</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8173,7 +8207,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8188,12 +8222,12 @@
         <v>44</v>
       </c>
       <c t="s" r="J209" s="7">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>305</v>
+        <v>310</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8208,7 +8242,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8241,7 +8275,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8253,10 +8287,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I211" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8274,7 +8308,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8289,7 +8323,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8307,7 +8341,7 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
@@ -8319,10 +8353,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I213" s="7">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c t="s" r="J213" s="7">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="K213" s="7"/>
       <c r="L213" s="7"/>
@@ -8355,7 +8389,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8364,18 +8398,18 @@
         <v>16</v>
       </c>
       <c t="s" r="H215" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I215" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J215" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>308</v>
+        <v>313</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8390,29 +8424,29 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G216" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H216" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I216" s="7">
         <v>173</v>
       </c>
       <c t="s" r="J216" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8427,16 +8461,16 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G217" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H217" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I217" s="7">
         <v>98</v>
@@ -8445,11 +8479,11 @@
         <v>70</v>
       </c>
       <c t="s" r="K217" s="7">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>217</v>
+        <v>221</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8464,13 +8498,13 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G218" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H218" s="8">
         <v>26</v>
@@ -8497,7 +8531,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8506,13 +8540,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H219" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I219" s="7">
         <v>27</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8530,13 +8564,13 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G220" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H220" s="8">
         <v>26</v>
@@ -8545,7 +8579,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J220" s="7">
-        <v>301</v>
+        <v>166</v>
       </c>
       <c r="K220" s="7"/>
       <c r="L220" s="7"/>
@@ -8578,7 +8612,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8587,10 +8621,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="J222" s="7">
         <v>120</v>
@@ -8598,7 +8632,7 @@
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>311</v>
+        <v>316</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8613,13 +8647,13 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>26</v>
@@ -8628,14 +8662,14 @@
         <v>122</v>
       </c>
       <c t="s" r="J223" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c t="s" r="K223" s="7">
         <v>95</v>
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>123</v>
+        <v>280</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8650,7 +8684,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8665,7 +8699,7 @@
         <v>110</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
@@ -8683,7 +8717,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8695,10 +8729,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I225" s="7">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8716,7 +8750,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8728,7 +8762,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I226" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J226" s="7">
         <v>87</v>
@@ -8749,7 +8783,7 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
@@ -8761,10 +8795,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I227" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c t="s" r="J227" s="7">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="K227" s="7"/>
       <c r="L227" s="7"/>
@@ -8782,7 +8816,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -8794,10 +8828,10 @@
         <v>85</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -8815,7 +8849,7 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
@@ -8827,10 +8861,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -8863,7 +8897,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -8875,14 +8909,16 @@
         <v>26</v>
       </c>
       <c t="s" r="I231" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
-      <c r="M231" s="7"/>
+      <c t="s" r="M231" s="7">
+        <v>325</v>
+      </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
       <c t="s" r="A232" s="6">
@@ -8896,7 +8932,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -8908,10 +8944,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I232" s="7">
-        <v>183</v>
+        <v>188</v>
       </c>
       <c t="s" r="J232" s="7">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
@@ -8929,7 +8965,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -8938,13 +8974,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c t="s" r="I233" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -8962,13 +8998,13 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>42</v>
@@ -8977,7 +9013,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -8995,7 +9031,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9004,13 +9040,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c t="s" r="I235" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9028,22 +9064,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9076,7 +9112,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9091,12 +9127,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J238" s="7">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>327</v>
+        <v>333</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9111,7 +9147,7 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
@@ -9120,13 +9156,13 @@
         <v>73</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="I239" s="7">
         <v>47</v>
       </c>
       <c t="s" r="J239" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
@@ -9144,22 +9180,22 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="H240" s="8">
         <v>73</v>
       </c>
       <c t="s" r="I240" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9177,7 +9213,7 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
@@ -9189,7 +9225,7 @@
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c t="s" r="J241" s="7">
         <v>62</v>
@@ -9225,7 +9261,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9240,12 +9276,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>288</v>
+        <v>178</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>331</v>
+        <v>337</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9260,7 +9296,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9269,13 +9305,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H244" s="8">
+        <v>239</v>
+      </c>
+      <c t="s" r="I244" s="7">
+        <v>208</v>
+      </c>
+      <c t="s" r="J244" s="7">
         <v>235</v>
-      </c>
-      <c t="s" r="I244" s="7">
-        <v>202</v>
-      </c>
-      <c t="s" r="J244" s="7">
-        <v>231</v>
       </c>
       <c r="K244" s="7"/>
       <c r="L244" s="7"/>
@@ -9293,13 +9329,13 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G245" s="8">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c t="s" r="H245" s="8">
         <v>42</v>
@@ -9308,7 +9344,7 @@
         <v>127</v>
       </c>
       <c t="s" r="J245" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="K245" s="7"/>
       <c r="L245" s="7"/>
@@ -9326,7 +9362,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9338,10 +9374,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I246" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9374,7 +9410,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9383,7 +9419,7 @@
         <v>26</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="I248" s="7">
         <v>65</v>
@@ -9407,19 +9443,19 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>288</v>
+        <v>178</v>
       </c>
       <c t="s" r="J249" s="7">
         <v>71</v>
@@ -9440,7 +9476,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9452,7 +9488,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>28</v>
@@ -9473,7 +9509,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9485,10 +9521,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c t="s" r="J251" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="K251" s="7"/>
       <c r="L251" s="7"/>
@@ -9521,7 +9557,7 @@
       </c>
       <c r="D253" s="7"/>
       <c t="s" r="E253" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F253" s="7">
         <v>321</v>
@@ -9541,7 +9577,7 @@
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
       <c t="s" r="M253" s="7">
-        <v>337</v>
+        <v>343</v>
       </c>
     </row>
     <row r="254" ht="14.25" customHeight="1">
@@ -9556,7 +9592,7 @@
       </c>
       <c r="D254" s="7"/>
       <c t="s" r="E254" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F254" s="7">
         <v>321</v>
@@ -9565,10 +9601,10 @@
         <v>17</v>
       </c>
       <c t="s" r="H254" s="8">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="I254" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J254" s="7">
         <v>69</v>
@@ -9591,13 +9627,13 @@
       </c>
       <c r="D255" s="7"/>
       <c t="s" r="E255" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F255" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G255" s="8">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="H255" s="8">
         <v>17</v>
@@ -9624,7 +9660,7 @@
       </c>
       <c r="D256" s="7"/>
       <c t="s" r="E256" s="7">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="F256" s="7">
         <v>321</v>
@@ -9636,10 +9672,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I256" s="7">
-        <v>186</v>
+        <v>191</v>
       </c>
       <c t="s" r="J256" s="7">
-        <v>209</v>
+        <v>165</v>
       </c>
       <c r="K256" s="7"/>
       <c r="L256" s="7"/>
@@ -9672,13 +9708,13 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G258" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H258" s="8">
         <v>42</v>
@@ -9687,7 +9723,7 @@
         <v>124</v>
       </c>
       <c t="s" r="J258" s="7">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
@@ -9705,7 +9741,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9714,13 +9750,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H259" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I259" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J259" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K259" s="7"/>
       <c r="L259" s="7"/>
@@ -9738,13 +9774,13 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G260" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H260" s="8">
         <v>42</v>
@@ -9753,7 +9789,7 @@
         <v>25</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K260" s="7"/>
       <c r="L260" s="7"/>
@@ -9786,7 +9822,7 @@
       </c>
       <c r="D262" s="7"/>
       <c t="s" r="E262" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F262" s="7">
         <v>321</v>
@@ -9798,15 +9834,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I262" s="7">
-        <v>341</v>
+        <v>167</v>
       </c>
       <c t="s" r="J262" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="K262" s="7"/>
       <c r="L262" s="7"/>
       <c t="s" r="M262" s="7">
-        <v>342</v>
+        <v>347</v>
       </c>
     </row>
     <row r="263" ht="14.25" customHeight="1">
@@ -9821,7 +9857,7 @@
       </c>
       <c r="D263" s="7"/>
       <c t="s" r="E263" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F263" s="7">
         <v>321</v>
@@ -9833,15 +9869,15 @@
         <v>73</v>
       </c>
       <c t="s" r="I263" s="7">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c t="s" r="J263" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="K263" s="7"/>
       <c r="L263" s="7"/>
       <c t="s" r="M263" s="7">
-        <v>238</v>
+        <v>242</v>
       </c>
     </row>
     <row r="264" ht="14.25" customHeight="1">
@@ -9856,7 +9892,7 @@
       </c>
       <c r="D264" s="7"/>
       <c t="s" r="E264" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F264" s="7">
         <v>321</v>
@@ -9868,15 +9904,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I264" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c t="s" r="J264" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="K264" s="7"/>
       <c r="L264" s="7"/>
       <c t="s" r="M264" s="7">
-        <v>343</v>
+        <v>348</v>
       </c>
     </row>
     <row r="265" ht="15" customHeight="1">
@@ -9891,7 +9927,7 @@
       </c>
       <c r="D265" s="7"/>
       <c t="s" r="E265" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F265" s="7">
         <v>321</v>
@@ -9903,10 +9939,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c t="s" r="J265" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K265" s="7"/>
       <c r="L265" s="7"/>
@@ -9924,7 +9960,7 @@
       </c>
       <c r="D266" s="7"/>
       <c t="s" r="E266" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F266" s="7">
         <v>321</v>
@@ -9936,10 +9972,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I266" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c t="s" r="J266" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="K266" s="7"/>
       <c r="L266" s="7"/>
@@ -9957,7 +9993,7 @@
       </c>
       <c r="D267" s="7"/>
       <c t="s" r="E267" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F267" s="7">
         <v>321</v>
@@ -9969,7 +10005,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I267" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c t="s" r="J267" s="7">
         <v>34</v>
@@ -9990,7 +10026,7 @@
       </c>
       <c r="D268" s="7"/>
       <c t="s" r="E268" s="7">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="F268" s="7">
         <v>321</v>
@@ -10002,10 +10038,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I268" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10038,7 +10074,7 @@
       </c>
       <c r="D270" s="7"/>
       <c t="s" r="E270" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F270" s="7">
         <v>321</v>
@@ -10047,18 +10083,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H270" s="8">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c t="s" r="J270" s="7">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K270" s="7"/>
       <c r="L270" s="7"/>
       <c t="s" r="M270" s="7">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
     <row r="271" ht="14.25" customHeight="1">
@@ -10073,19 +10109,19 @@
       </c>
       <c r="D271" s="7"/>
       <c t="s" r="E271" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F271" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G271" s="8">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="H271" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I271" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c t="s" r="J271" s="7">
         <v>33</v>
@@ -10106,7 +10142,7 @@
       </c>
       <c r="D272" s="7"/>
       <c t="s" r="E272" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F272" s="7">
         <v>321</v>
@@ -10115,13 +10151,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H272" s="8">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c t="s" r="I272" s="7">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c t="s" r="J272" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K272" s="7"/>
       <c r="L272" s="7"/>
@@ -10139,22 +10175,22 @@
       </c>
       <c r="D273" s="7"/>
       <c t="s" r="E273" s="7">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F273" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G273" s="8">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c t="s" r="H273" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I273" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="J273" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K273" s="7"/>
       <c r="L273" s="7"/>
@@ -10187,7 +10223,7 @@
       </c>
       <c r="D275" s="7"/>
       <c t="s" r="E275" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F275" s="7">
         <v>321</v>
@@ -10196,18 +10232,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H275" s="8">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="I275" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J275" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K275" s="7"/>
       <c r="L275" s="7"/>
       <c t="s" r="M275" s="7">
-        <v>354</v>
+        <v>359</v>
       </c>
     </row>
     <row r="276" ht="14.25" customHeight="1">
@@ -10222,19 +10258,19 @@
       </c>
       <c r="D276" s="7"/>
       <c t="s" r="E276" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F276" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G276" s="8">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c t="s" r="H276" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I276" s="7">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c t="s" r="J276" s="7">
         <v>66</v>
@@ -10257,7 +10293,7 @@
       </c>
       <c r="D277" s="7"/>
       <c t="s" r="E277" s="7">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="F277" s="7">
         <v>321</v>
@@ -10266,10 +10302,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H277" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c t="s" r="J277" s="7">
         <v>126</v>
@@ -10305,7 +10341,7 @@
       </c>
       <c r="D279" s="7"/>
       <c t="s" r="E279" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F279" s="7">
         <v>320</v>
@@ -10314,18 +10350,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H279" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="I279" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
       <c t="s" r="M279" s="7">
-        <v>356</v>
+        <v>361</v>
       </c>
     </row>
     <row r="280" ht="15" customHeight="1">
@@ -10340,13 +10376,13 @@
       </c>
       <c r="D280" s="7"/>
       <c t="s" r="E280" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F280" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G280" s="8">
-        <v>135</v>
+        <v>175</v>
       </c>
       <c t="s" r="H280" s="8">
         <v>26</v>
@@ -10355,12 +10391,12 @@
         <v>31</v>
       </c>
       <c t="s" r="J280" s="7">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>357</v>
+        <v>280</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10375,7 +10411,7 @@
       </c>
       <c r="D281" s="7"/>
       <c t="s" r="E281" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F281" s="7">
         <v>320</v>
@@ -10384,13 +10420,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H281" s="8">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="I281" s="7">
         <v>71</v>
       </c>
       <c t="s" r="J281" s="7">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="K281" s="7"/>
       <c r="L281" s="7"/>
@@ -10408,22 +10444,22 @@
       </c>
       <c r="D282" s="7"/>
       <c t="s" r="E282" s="7">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="F282" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G282" s="8">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="H282" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I282" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c t="s" r="J282" s="7">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="K282" s="7"/>
       <c r="L282" s="7"/>
@@ -10456,7 +10492,7 @@
       </c>
       <c r="D284" s="7"/>
       <c t="s" r="E284" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F284" s="7">
         <v>321</v>
@@ -10468,7 +10504,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I284" s="7">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c t="s" r="J284" s="7">
         <v>31</v>
@@ -10476,7 +10512,7 @@
       <c r="K284" s="7"/>
       <c r="L284" s="7"/>
       <c t="s" r="M284" s="7">
-        <v>363</v>
+        <v>367</v>
       </c>
     </row>
     <row r="285" ht="15" customHeight="1">
@@ -10491,7 +10527,7 @@
       </c>
       <c r="D285" s="7"/>
       <c t="s" r="E285" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F285" s="7">
         <v>321</v>
@@ -10500,13 +10536,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H285" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I285" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J285" s="7">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="K285" s="7"/>
       <c r="L285" s="7"/>
@@ -10524,22 +10560,22 @@
       </c>
       <c r="D286" s="7"/>
       <c t="s" r="E286" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F286" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G286" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H286" s="8">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="I286" s="7">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c t="s" r="J286" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K286" s="7"/>
       <c r="L286" s="7"/>
@@ -10557,22 +10593,22 @@
       </c>
       <c r="D287" s="7"/>
       <c t="s" r="E287" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F287" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G287" s="8">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c t="s" r="H287" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I287" s="7">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c t="s" r="J287" s="7">
-        <v>140</v>
+        <v>154</v>
       </c>
       <c r="K287" s="7"/>
       <c r="L287" s="7"/>
@@ -10590,22 +10626,22 @@
       </c>
       <c r="D288" s="7"/>
       <c t="s" r="E288" s="7">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="F288" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G288" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H288" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I288" s="7">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c t="s" r="J288" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K288" s="7"/>
       <c r="L288" s="7"/>
@@ -10638,7 +10674,7 @@
       </c>
       <c r="D290" s="7"/>
       <c t="s" r="E290" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F290" s="7">
         <v>320</v>
@@ -10647,18 +10683,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H290" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="I290" s="7">
         <v>119</v>
       </c>
       <c t="s" r="J290" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K290" s="7"/>
       <c r="L290" s="7"/>
       <c t="s" r="M290" s="7">
-        <v>370</v>
+        <v>374</v>
       </c>
     </row>
     <row r="291" ht="14.25" customHeight="1">
@@ -10673,13 +10709,13 @@
       </c>
       <c r="D291" s="7"/>
       <c t="s" r="E291" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F291" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G291" s="8">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c t="s" r="H291" s="8">
         <v>42</v>
@@ -10688,7 +10724,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J291" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="K291" s="7"/>
       <c r="L291" s="7"/>
@@ -10706,7 +10742,7 @@
       </c>
       <c r="D292" s="7"/>
       <c t="s" r="E292" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F292" s="7">
         <v>320</v>
@@ -10715,13 +10751,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H292" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="I292" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J292" s="7">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="K292" s="7"/>
       <c r="L292" s="7"/>
@@ -10739,22 +10775,22 @@
       </c>
       <c r="D293" s="7"/>
       <c t="s" r="E293" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F293" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G293" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="H293" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I293" s="7">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -10772,7 +10808,7 @@
       </c>
       <c r="D294" s="7"/>
       <c t="s" r="E294" s="7">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="F294" s="7">
         <v>320</v>
@@ -10784,17 +10820,17 @@
         <v>73</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c t="s" r="K294" s="7">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="L294" s="7"/>
       <c t="s" r="M294" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
     </row>
     <row r="295" ht="15" customHeight="1">
@@ -10824,7 +10860,7 @@
       </c>
       <c r="D296" s="7"/>
       <c t="s" r="E296" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F296" s="7">
         <v>321</v>
@@ -10836,15 +10872,15 @@
         <v>26</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -10859,7 +10895,7 @@
       </c>
       <c r="D297" s="7"/>
       <c t="s" r="E297" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F297" s="7">
         <v>321</v>
@@ -10868,13 +10904,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H297" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="I297" s="7">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c t="s" r="J297" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
@@ -10894,26 +10930,28 @@
       </c>
       <c r="D298" s="7"/>
       <c t="s" r="E298" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F298" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G298" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="H298" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I298" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
-      <c r="M298" s="7"/>
+      <c t="s" r="M298" s="7">
+        <v>378</v>
+      </c>
     </row>
     <row r="299" ht="14.25" customHeight="1">
       <c t="s" r="A299" s="6">
@@ -10927,7 +10965,7 @@
       </c>
       <c r="D299" s="7"/>
       <c t="s" r="E299" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F299" s="7">
         <v>321</v>
@@ -10939,7 +10977,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I299" s="7">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c t="s" r="J299" s="7">
         <v>45</v>
@@ -10964,7 +11002,7 @@
       </c>
       <c r="D300" s="7"/>
       <c t="s" r="E300" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F300" s="7">
         <v>321</v>
@@ -10979,14 +11017,14 @@
         <v>47</v>
       </c>
       <c t="s" r="J300" s="7">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c t="s" r="K300" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11001,7 +11039,7 @@
       </c>
       <c r="D301" s="7"/>
       <c t="s" r="E301" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F301" s="7">
         <v>321</v>
@@ -11010,13 +11048,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c t="s" r="I301" s="7">
         <v>76</v>
       </c>
       <c t="s" r="J301" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c r="K301" s="7"/>
       <c r="L301" s="7"/>
@@ -11034,22 +11072,22 @@
       </c>
       <c r="D302" s="7"/>
       <c t="s" r="E302" s="7">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F302" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I302" s="7">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c t="s" r="J302" s="7">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="K302" s="7"/>
       <c r="L302" s="7"/>
@@ -11082,7 +11120,7 @@
       </c>
       <c r="D304" s="7"/>
       <c t="s" r="E304" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F304" s="7">
         <v>320</v>
@@ -11091,18 +11129,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H304" s="8">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c t="s" r="I304" s="7">
         <v>79</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
       <c t="s" r="M304" s="7">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="305" ht="15" customHeight="1">
@@ -11117,19 +11155,19 @@
       </c>
       <c r="D305" s="7"/>
       <c t="s" r="E305" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F305" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G305" s="8">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c t="s" r="H305" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I305" s="7">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c t="s" r="J305" s="7">
         <v>47</v>
@@ -11150,7 +11188,7 @@
       </c>
       <c r="D306" s="7"/>
       <c t="s" r="E306" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F306" s="7">
         <v>320</v>
@@ -11162,7 +11200,7 @@
         <v>68</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c t="s" r="J306" s="7">
         <v>102</v>
@@ -11183,7 +11221,7 @@
       </c>
       <c r="D307" s="7"/>
       <c t="s" r="E307" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F307" s="7">
         <v>320</v>
@@ -11195,10 +11233,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c t="s" r="J307" s="7">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="K307" s="7"/>
       <c r="L307" s="7"/>
@@ -11216,7 +11254,7 @@
       </c>
       <c r="D308" s="7"/>
       <c t="s" r="E308" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F308" s="7">
         <v>320</v>
@@ -11225,13 +11263,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H308" s="8">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c t="s" r="I308" s="7">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c t="s" r="J308" s="7">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="K308" s="7"/>
       <c r="L308" s="7"/>
@@ -11249,22 +11287,22 @@
       </c>
       <c r="D309" s="7"/>
       <c t="s" r="E309" s="7">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="F309" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G309" s="8">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c t="s" r="H309" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I309" s="7">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c t="s" r="J309" s="7">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="K309" s="7"/>
       <c r="L309" s="7"/>
@@ -11297,7 +11335,7 @@
       </c>
       <c r="D311" s="7"/>
       <c t="s" r="E311" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F311" s="7">
         <v>320</v>
@@ -11306,18 +11344,18 @@
         <v>26</v>
       </c>
       <c t="s" r="H311" s="8">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c t="s" r="J311" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K311" s="7"/>
       <c r="L311" s="7"/>
       <c t="s" r="M311" s="7">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="312" ht="14.25" customHeight="1">
@@ -11332,13 +11370,13 @@
       </c>
       <c r="D312" s="7"/>
       <c t="s" r="E312" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F312" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G312" s="8">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c t="s" r="H312" s="8">
         <v>26</v>
@@ -11347,12 +11385,12 @@
         <v>79</v>
       </c>
       <c t="s" r="J312" s="7">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="K312" s="7"/>
       <c r="L312" s="7"/>
       <c t="s" r="M312" s="7">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="313" ht="14.25" customHeight="1">
@@ -11367,7 +11405,7 @@
       </c>
       <c r="D313" s="7"/>
       <c t="s" r="E313" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F313" s="7">
         <v>320</v>
@@ -11379,15 +11417,15 @@
         <v>85</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
       <c t="s" r="M313" s="7">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="314" ht="14.25" customHeight="1">
@@ -11402,7 +11440,7 @@
       </c>
       <c r="D314" s="7"/>
       <c t="s" r="E314" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F314" s="7">
         <v>320</v>
@@ -11414,7 +11452,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I314" s="7">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c t="s" r="J314" s="7">
         <v>47</v>
@@ -11435,7 +11473,7 @@
       </c>
       <c r="D315" s="7"/>
       <c t="s" r="E315" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F315" s="7">
         <v>320</v>
@@ -11444,10 +11482,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H315" s="8">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c t="s" r="I315" s="7">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c t="s" r="J315" s="7">
         <v>112</v>
@@ -11468,13 +11506,13 @@
       </c>
       <c r="D316" s="7"/>
       <c t="s" r="E316" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F316" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G316" s="8">
-        <v>384</v>
+        <v>389</v>
       </c>
       <c t="s" r="H316" s="8">
         <v>26</v>
@@ -11483,7 +11521,7 @@
         <v>34</v>
       </c>
       <c t="s" r="J316" s="7">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="K316" s="7"/>
       <c r="L316" s="7"/>
@@ -11501,7 +11539,7 @@
       </c>
       <c r="D317" s="7"/>
       <c t="s" r="E317" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F317" s="7">
         <v>320</v>
@@ -11510,10 +11548,10 @@
         <v>26</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="I317" s="7">
-        <v>387</v>
+        <v>392</v>
       </c>
       <c t="s" r="J317" s="7">
         <v>51</v>
@@ -11534,13 +11572,13 @@
       </c>
       <c r="D318" s="7"/>
       <c t="s" r="E318" s="7">
-        <v>383</v>
+        <v>388</v>
       </c>
       <c r="F318" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>26</v>
@@ -11549,7 +11587,7 @@
         <v>52</v>
       </c>
       <c t="s" r="J318" s="7">
-        <v>388</v>
+        <v>393</v>
       </c>
       <c r="K318" s="7"/>
       <c r="L318" s="7"/>
@@ -11582,7 +11620,7 @@
       </c>
       <c r="D320" s="7"/>
       <c t="s" r="E320" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F320" s="7">
         <v>321</v>
@@ -11597,14 +11635,14 @@
         <v>56</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c t="s" r="K320" s="7">
         <v>82</v>
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>390</v>
+        <v>306</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11619,7 +11657,7 @@
       </c>
       <c r="D321" s="7"/>
       <c t="s" r="E321" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F321" s="7">
         <v>321</v>
@@ -11631,7 +11669,7 @@
         <v>61</v>
       </c>
       <c t="s" r="I321" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="J321" s="7">
         <v>100</v>
@@ -11652,7 +11690,7 @@
       </c>
       <c r="D322" s="7"/>
       <c t="s" r="E322" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F322" s="7">
         <v>321</v>
@@ -11685,7 +11723,7 @@
       </c>
       <c r="D323" s="7"/>
       <c t="s" r="E323" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F323" s="7">
         <v>321</v>
@@ -11694,13 +11732,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H323" s="8">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c t="s" r="J323" s="7">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="K323" s="7"/>
       <c r="L323" s="7"/>
@@ -11718,22 +11756,22 @@
       </c>
       <c r="D324" s="7"/>
       <c t="s" r="E324" s="7">
-        <v>389</v>
+        <v>394</v>
       </c>
       <c r="F324" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G324" s="8">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c t="s" r="H324" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c t="s" r="J324" s="7">
-        <v>341</v>
+        <v>167</v>
       </c>
       <c r="K324" s="7"/>
       <c r="L324" s="7"/>
@@ -11766,19 +11804,19 @@
       </c>
       <c r="D326" s="7"/>
       <c t="s" r="E326" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F326" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G326" s="8">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c t="s" r="H326" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I326" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c t="s" r="J326" s="7">
         <v>125</v>
@@ -11786,7 +11824,7 @@
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
       <c t="s" r="M326" s="7">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="327" ht="14.25" customHeight="1">
@@ -11801,7 +11839,7 @@
       </c>
       <c r="D327" s="7"/>
       <c t="s" r="E327" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F327" s="7">
         <v>320</v>
@@ -11810,13 +11848,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H327" s="8">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c t="s" r="I327" s="7">
         <v>87</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -11834,22 +11872,22 @@
       </c>
       <c r="D328" s="7"/>
       <c t="s" r="E328" s="7">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="F328" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G328" s="8">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c t="s" r="H328" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -11882,7 +11920,7 @@
       </c>
       <c r="D330" s="7"/>
       <c t="s" r="E330" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F330" s="7">
         <v>321</v>
@@ -11894,15 +11932,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I330" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c t="s" r="J330" s="7">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="K330" s="7"/>
       <c r="L330" s="7"/>
       <c t="s" r="M330" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="331" ht="14.25" customHeight="1">
@@ -11917,7 +11955,7 @@
       </c>
       <c r="D331" s="7"/>
       <c t="s" r="E331" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F331" s="7">
         <v>321</v>
@@ -11932,7 +11970,7 @@
         <v>123</v>
       </c>
       <c t="s" r="J331" s="7">
-        <v>137</v>
+        <v>179</v>
       </c>
       <c r="K331" s="7"/>
       <c r="L331" s="7"/>
@@ -11950,7 +11988,7 @@
       </c>
       <c r="D332" s="7"/>
       <c t="s" r="E332" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F332" s="7">
         <v>321</v>
@@ -11983,7 +12021,7 @@
       </c>
       <c r="D333" s="7"/>
       <c t="s" r="E333" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F333" s="7">
         <v>321</v>
@@ -11995,7 +12033,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c t="s" r="J333" s="7">
         <v>52</v>
@@ -12016,7 +12054,7 @@
       </c>
       <c r="D334" s="7"/>
       <c t="s" r="E334" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F334" s="7">
         <v>321</v>
@@ -12025,13 +12063,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J334" s="7">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="K334" s="7"/>
       <c r="L334" s="7"/>
@@ -12049,22 +12087,22 @@
       </c>
       <c r="D335" s="7"/>
       <c t="s" r="E335" s="7">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="F335" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I335" s="7">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c t="s" r="J335" s="7">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="K335" s="7"/>
       <c r="L335" s="7"/>
@@ -12097,7 +12135,7 @@
       </c>
       <c r="D337" s="7"/>
       <c t="s" r="E337" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F337" s="7">
         <v>321</v>
@@ -12109,15 +12147,15 @@
         <v>42</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c t="s" r="J337" s="7">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="K337" s="7"/>
       <c r="L337" s="7"/>
       <c t="s" r="M337" s="7">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="338" ht="14.25" customHeight="1">
@@ -12132,7 +12170,7 @@
       </c>
       <c r="D338" s="7"/>
       <c t="s" r="E338" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F338" s="7">
         <v>321</v>
@@ -12144,7 +12182,7 @@
         <v>61</v>
       </c>
       <c t="s" r="I338" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="J338" s="7">
         <v>83</v>
@@ -12152,7 +12190,7 @@
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
       <c t="s" r="M338" s="7">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="339" ht="14.25" customHeight="1">
@@ -12167,7 +12205,7 @@
       </c>
       <c r="D339" s="7"/>
       <c t="s" r="E339" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F339" s="7">
         <v>321</v>
@@ -12200,7 +12238,7 @@
       </c>
       <c r="D340" s="7"/>
       <c t="s" r="E340" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F340" s="7">
         <v>321</v>
@@ -12209,7 +12247,7 @@
         <v>42</v>
       </c>
       <c t="s" r="H340" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="I340" s="7">
         <v>50</v>
@@ -12233,22 +12271,22 @@
       </c>
       <c r="D341" s="7"/>
       <c t="s" r="E341" s="7">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="F341" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G341" s="8">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c t="s" r="H341" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I341" s="7">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c t="s" r="J341" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K341" s="7"/>
       <c r="L341" s="7"/>
@@ -12281,7 +12319,7 @@
       </c>
       <c r="D343" s="7"/>
       <c t="s" r="E343" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F343" s="7">
         <v>320</v>
@@ -12293,7 +12331,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c t="s" r="J343" s="7">
         <v>79</v>
@@ -12301,7 +12339,7 @@
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
       <c t="s" r="M343" s="7">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="344" ht="14.25" customHeight="1">
@@ -12316,7 +12354,7 @@
       </c>
       <c r="D344" s="7"/>
       <c t="s" r="E344" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F344" s="7">
         <v>320</v>
@@ -12331,12 +12369,12 @@
         <v>116</v>
       </c>
       <c t="s" r="J344" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K344" s="7"/>
       <c r="L344" s="7"/>
       <c t="s" r="M344" s="7">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="345" ht="15" customHeight="1">
@@ -12351,7 +12389,7 @@
       </c>
       <c r="D345" s="7"/>
       <c t="s" r="E345" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F345" s="7">
         <v>320</v>
@@ -12363,7 +12401,7 @@
         <v>49</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c t="s" r="J345" s="7">
         <v>123</v>
@@ -12371,7 +12409,7 @@
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>409</v>
+        <v>306</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12386,7 +12424,7 @@
       </c>
       <c r="D346" s="7"/>
       <c t="s" r="E346" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F346" s="7">
         <v>320</v>
@@ -12398,10 +12436,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I346" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c t="s" r="J346" s="7">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="K346" s="7"/>
       <c r="L346" s="7"/>
@@ -12419,7 +12457,7 @@
       </c>
       <c r="D347" s="7"/>
       <c t="s" r="E347" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F347" s="7">
         <v>320</v>
@@ -12428,13 +12466,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H347" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="I347" s="7">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c t="s" r="J347" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="K347" s="7"/>
       <c r="L347" s="7"/>
@@ -12452,13 +12490,13 @@
       </c>
       <c r="D348" s="7"/>
       <c t="s" r="E348" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F348" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G348" s="8">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c t="s" r="H348" s="8">
         <v>42</v>
@@ -12467,7 +12505,7 @@
         <v>50</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12485,7 +12523,7 @@
       </c>
       <c r="D349" s="7"/>
       <c t="s" r="E349" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F349" s="7">
         <v>320</v>
@@ -12497,10 +12535,10 @@
         <v>73</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c t="s" r="J349" s="7">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="K349" s="7"/>
       <c r="L349" s="7"/>
@@ -12518,7 +12556,7 @@
       </c>
       <c r="D350" s="7"/>
       <c t="s" r="E350" s="7">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="F350" s="7">
         <v>320</v>
@@ -12530,10 +12568,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c t="s" r="J350" s="7">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K350" s="7"/>
       <c r="L350" s="7"/>
@@ -12566,7 +12604,7 @@
       </c>
       <c r="D352" s="7"/>
       <c t="s" r="E352" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F352" s="7">
         <v>320</v>
@@ -12578,15 +12616,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I352" s="7">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c t="s" r="J352" s="7">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="K352" s="7"/>
       <c r="L352" s="7"/>
       <c t="s" r="M352" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
     </row>
     <row r="353" ht="14.25" customHeight="1">
@@ -12601,7 +12639,7 @@
       </c>
       <c r="D353" s="7"/>
       <c t="s" r="E353" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F353" s="7">
         <v>320</v>
@@ -12616,7 +12654,7 @@
         <v>32</v>
       </c>
       <c t="s" r="J353" s="7">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="K353" s="7"/>
       <c r="L353" s="7"/>
@@ -12634,7 +12672,7 @@
       </c>
       <c r="D354" s="7"/>
       <c t="s" r="E354" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F354" s="7">
         <v>320</v>
@@ -12643,13 +12681,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H354" s="8">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c t="s" r="I354" s="7">
         <v>128</v>
       </c>
       <c t="s" r="J354" s="7">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="K354" s="7"/>
       <c r="L354" s="7"/>
@@ -12667,22 +12705,22 @@
       </c>
       <c r="D355" s="7"/>
       <c t="s" r="E355" s="7">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="F355" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G355" s="8">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c t="s" r="H355" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c t="s" r="J355" s="7">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="K355" s="7"/>
       <c r="L355" s="7"/>
@@ -12715,7 +12753,7 @@
       </c>
       <c r="D357" s="7"/>
       <c t="s" r="E357" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F357" s="7">
         <v>321</v>
@@ -12727,7 +12765,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I357" s="7">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c t="s" r="J357" s="7">
         <v>99</v>
@@ -12748,7 +12786,7 @@
       </c>
       <c r="D358" s="7"/>
       <c t="s" r="E358" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F358" s="7">
         <v>321</v>
@@ -12760,7 +12798,7 @@
         <v>73</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c t="s" r="J358" s="7">
         <v>86</v>
@@ -12781,7 +12819,7 @@
       </c>
       <c r="D359" s="7"/>
       <c t="s" r="E359" s="7">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="F359" s="7">
         <v>321</v>
@@ -12793,7 +12831,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c t="s" r="J359" s="7">
         <v>130</v>
@@ -12829,13 +12867,13 @@
       </c>
       <c r="D361" s="7"/>
       <c t="s" r="E361" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F361" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G361" s="8">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c t="s" r="H361" s="8">
         <v>42</v>
@@ -12849,7 +12887,7 @@
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
       <c t="s" r="M361" s="7">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="362" ht="14.25" customHeight="1">
@@ -12864,7 +12902,7 @@
       </c>
       <c r="D362" s="7"/>
       <c t="s" r="E362" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F362" s="7">
         <v>321</v>
@@ -12873,13 +12911,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H362" s="8">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c t="s" r="I362" s="7">
         <v>32</v>
       </c>
       <c t="s" r="J362" s="7">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
@@ -12897,19 +12935,19 @@
       </c>
       <c r="D363" s="7"/>
       <c t="s" r="E363" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F363" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G363" s="8">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c t="s" r="H363" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I363" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J363" s="7">
         <v>75</v>
@@ -12930,7 +12968,7 @@
       </c>
       <c r="D364" s="7"/>
       <c t="s" r="E364" s="7">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="F364" s="7">
         <v>321</v>
@@ -12942,10 +12980,10 @@
         <v>16</v>
       </c>
       <c t="s" r="I364" s="7">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c t="s" r="J364" s="7">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="K364" s="7"/>
       <c r="L364" s="7"/>
@@ -12978,7 +13016,7 @@
       </c>
       <c r="D366" s="7"/>
       <c t="s" r="E366" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F366" s="7">
         <v>321</v>
@@ -12987,18 +13025,18 @@
         <v>36</v>
       </c>
       <c t="s" r="H366" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I366" s="7">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c t="s" r="J366" s="7">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="K366" s="7"/>
       <c r="L366" s="7"/>
       <c t="s" r="M366" s="7">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="367" ht="14.25" customHeight="1">
@@ -13013,22 +13051,22 @@
       </c>
       <c r="D367" s="7"/>
       <c t="s" r="E367" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F367" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G367" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="I367" s="7">
         <v>83</v>
       </c>
       <c t="s" r="J367" s="7">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K367" s="7"/>
       <c r="L367" s="7"/>
@@ -13046,19 +13084,19 @@
       </c>
       <c r="D368" s="7"/>
       <c t="s" r="E368" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F368" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c t="s" r="H368" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I368" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J368" s="7">
         <v>88</v>
@@ -13079,22 +13117,22 @@
       </c>
       <c r="D369" s="7"/>
       <c t="s" r="E369" s="7">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="F369" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G369" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H369" s="8">
         <v>36</v>
       </c>
       <c t="s" r="I369" s="7">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c t="s" r="J369" s="7">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="K369" s="7"/>
       <c r="L369" s="7"/>
@@ -13127,7 +13165,7 @@
       </c>
       <c r="D371" s="7"/>
       <c t="s" r="E371" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F371" s="7">
         <v>321</v>
@@ -13136,18 +13174,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H371" s="8">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="I371" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
       <c t="s" r="M371" s="7">
-        <v>425</v>
+        <v>174</v>
       </c>
     </row>
     <row r="372" ht="14.25" customHeight="1">
@@ -13162,22 +13200,22 @@
       </c>
       <c r="D372" s="7"/>
       <c t="s" r="E372" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F372" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G372" s="8">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c t="s" r="H372" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I372" s="7">
-        <v>216</v>
+        <v>177</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>288</v>
+        <v>178</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13195,7 +13233,7 @@
       </c>
       <c r="D373" s="7"/>
       <c t="s" r="E373" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F373" s="7">
         <v>321</v>
@@ -13204,10 +13242,10 @@
         <v>42</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="I373" s="7">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c t="s" r="J373" s="7">
         <v>34</v>
@@ -13228,19 +13266,19 @@
       </c>
       <c r="D374" s="7"/>
       <c t="s" r="E374" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F374" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>143</v>
+        <v>140</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I374" s="7">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c t="s" r="J374" s="7">
         <v>48</v>
@@ -13261,7 +13299,7 @@
       </c>
       <c r="D375" s="7"/>
       <c t="s" r="E375" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F375" s="7">
         <v>321</v>
@@ -13270,13 +13308,13 @@
         <v>42</v>
       </c>
       <c t="s" r="H375" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I375" s="7">
         <v>104</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13294,22 +13332,22 @@
       </c>
       <c r="D376" s="7"/>
       <c t="s" r="E376" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F376" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G376" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H376" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13327,7 +13365,7 @@
       </c>
       <c r="D377" s="7"/>
       <c t="s" r="E377" s="7">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="F377" s="7">
         <v>321</v>
@@ -13339,10 +13377,10 @@
         <v>36</v>
       </c>
       <c t="s" r="I377" s="7">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13375,7 +13413,7 @@
       </c>
       <c r="D379" s="7"/>
       <c t="s" r="E379" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F379" s="7">
         <v>321</v>
@@ -13387,10 +13425,10 @@
         <v>58</v>
       </c>
       <c t="s" r="I379" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c t="s" r="J379" s="7">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="K379" s="7"/>
       <c r="L379" s="7"/>
@@ -13410,7 +13448,7 @@
       </c>
       <c r="D380" s="7"/>
       <c t="s" r="E380" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F380" s="7">
         <v>321</v>
@@ -13422,7 +13460,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I380" s="7">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c t="s" r="J380" s="7">
         <v>35</v>
@@ -13443,7 +13481,7 @@
       </c>
       <c r="D381" s="7"/>
       <c t="s" r="E381" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F381" s="7">
         <v>321</v>
@@ -13458,7 +13496,7 @@
         <v>88</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>175</v>
+        <v>136</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13476,7 +13514,7 @@
       </c>
       <c r="D382" s="7"/>
       <c t="s" r="E382" s="7">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="F382" s="7">
         <v>321</v>
@@ -13491,7 +13529,7 @@
         <v>76</v>
       </c>
       <c t="s" r="J382" s="7">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="K382" s="7"/>
       <c r="L382" s="7"/>
@@ -13524,7 +13562,7 @@
       </c>
       <c r="D384" s="7"/>
       <c t="s" r="E384" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F384" s="7">
         <v>320</v>
@@ -13533,18 +13571,18 @@
         <v>42</v>
       </c>
       <c t="s" r="H384" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="I384" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c t="s" r="J384" s="7">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="K384" s="7"/>
       <c r="L384" s="7"/>
       <c t="s" r="M384" s="7">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="385" ht="15" customHeight="1">
@@ -13559,27 +13597,27 @@
       </c>
       <c r="D385" s="7"/>
       <c t="s" r="E385" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F385" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G385" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="H385" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I385" s="7">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c t="s" r="J385" s="7">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="K385" s="7"/>
       <c r="L385" s="7"/>
       <c t="s" r="M385" s="7">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="386" ht="14.25" customHeight="1">
@@ -13594,7 +13632,7 @@
       </c>
       <c r="D386" s="7"/>
       <c t="s" r="E386" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F386" s="7">
         <v>320</v>
@@ -13606,10 +13644,10 @@
         <v>68</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c t="s" r="J386" s="7">
-        <v>184</v>
+        <v>189</v>
       </c>
       <c r="K386" s="7"/>
       <c r="L386" s="7"/>
@@ -13627,7 +13665,7 @@
       </c>
       <c r="D387" s="7"/>
       <c t="s" r="E387" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F387" s="7">
         <v>320</v>
@@ -13639,10 +13677,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I387" s="7">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c t="s" r="J387" s="7">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="K387" s="7"/>
       <c r="L387" s="7"/>
@@ -13660,7 +13698,7 @@
       </c>
       <c r="D388" s="7"/>
       <c t="s" r="E388" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F388" s="7">
         <v>320</v>
@@ -13669,10 +13707,10 @@
         <v>42</v>
       </c>
       <c t="s" r="H388" s="8">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="I388" s="7">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c t="s" r="J388" s="7">
         <v>77</v>
@@ -13693,22 +13731,22 @@
       </c>
       <c r="D389" s="7"/>
       <c t="s" r="E389" s="7">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F389" s="7">
         <v>320</v>
       </c>
       <c t="s" r="G389" s="8">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c t="s" r="H389" s="8">
         <v>42</v>
       </c>
       <c t="s" r="I389" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c t="s" r="J389" s="7">
-        <v>210</v>
+        <v>215</v>
       </c>
       <c r="K389" s="7"/>
       <c r="L389" s="7"/>
@@ -13741,7 +13779,7 @@
       </c>
       <c r="D391" s="7"/>
       <c t="s" r="E391" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F391" s="7">
         <v>321</v>
@@ -13753,10 +13791,10 @@
         <v>85</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
@@ -13776,7 +13814,7 @@
       </c>
       <c r="D392" s="7"/>
       <c t="s" r="E392" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F392" s="7">
         <v>321</v>
@@ -13785,7 +13823,7 @@
         <v>85</v>
       </c>
       <c t="s" r="H392" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="I392" s="7">
         <v>31</v>
@@ -13796,7 +13834,7 @@
       <c r="K392" s="7"/>
       <c r="L392" s="7"/>
       <c t="s" r="M392" s="7">
-        <v>431</v>
+        <v>433</v>
       </c>
     </row>
     <row r="393" ht="14.25" customHeight="1">
@@ -13811,22 +13849,22 @@
       </c>
       <c r="D393" s="7"/>
       <c t="s" r="E393" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F393" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G393" s="8">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c t="s" r="H393" s="8">
         <v>85</v>
       </c>
       <c t="s" r="I393" s="7">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -13844,7 +13882,7 @@
       </c>
       <c r="D394" s="7"/>
       <c t="s" r="E394" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F394" s="7">
         <v>321</v>
@@ -13856,7 +13894,7 @@
         <v>26</v>
       </c>
       <c t="s" r="I394" s="7">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c t="s" r="J394" s="7">
         <v>113</v>
@@ -13870,14 +13908,14 @@
         <v>13</v>
       </c>
       <c r="B395" s="7">
-        <v>1803</v>
+        <v>883</v>
       </c>
       <c t="s" r="C395" s="7">
         <v>14</v>
       </c>
       <c r="D395" s="7"/>
       <c t="s" r="E395" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F395" s="7">
         <v>321</v>
@@ -13886,13 +13924,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H395" s="8">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>223</v>
+        <v>436</v>
       </c>
       <c t="s" r="J395" s="7">
-        <v>209</v>
+        <v>154</v>
       </c>
       <c r="K395" s="7"/>
       <c r="L395" s="7"/>
@@ -13900,32 +13938,32 @@
     </row>
     <row r="396" ht="14.25" customHeight="1">
       <c t="s" r="A396" s="6">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="B396" s="7">
-        <v>1804</v>
+        <v>884</v>
       </c>
       <c t="s" r="C396" s="7">
         <v>14</v>
       </c>
       <c r="D396" s="7"/>
       <c t="s" r="E396" s="7">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="F396" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G396" s="8">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c t="s" r="H396" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>301</v>
+        <v>437</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>341</v>
+        <v>119</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -13958,7 +13996,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -13978,7 +14016,7 @@
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
       <c t="s" r="M398" s="7">
-        <v>215</v>
+        <v>220</v>
       </c>
     </row>
     <row r="399" ht="14.25" customHeight="1">
@@ -13993,7 +14031,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -14005,7 +14043,7 @@
         <v>42</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>32</v>
@@ -14041,16 +14079,16 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G401" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c t="s" r="I401" s="7">
         <v>69</v>
@@ -14074,22 +14112,22 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c t="s" r="H402" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c t="s" r="J402" s="7">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="K402" s="7"/>
       <c r="L402" s="7"/>
@@ -14122,26 +14160,28 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>174</v>
+        <v>135</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>24</v>
       </c>
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
-      <c r="M404" s="7"/>
+      <c t="s" r="M404" s="7">
+        <v>444</v>
+      </c>
     </row>
     <row r="405" ht="15" customHeight="1">
       <c t="s" r="A405" s="6">
@@ -14155,7 +14195,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14164,13 +14204,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c t="s" r="I405" s="7">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c t="s" r="J405" s="7">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="K405" s="7"/>
       <c r="L405" s="7"/>
@@ -14199,23 +14239,23 @@
         <v>611</v>
       </c>
       <c t="s" r="C407" s="7">
-        <v>440</v>
+        <v>445</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G407" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H407" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I407" s="7">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c t="s" r="J407" s="7">
         <v>56</v>
@@ -14223,7 +14263,7 @@
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14238,7 +14278,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -14247,13 +14287,13 @@
         <v>26</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>19</v>
       </c>
       <c t="s" r="J408" s="7">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
@@ -14271,22 +14311,22 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I409" s="7">
-        <v>374</v>
+        <v>379</v>
       </c>
       <c t="s" r="J409" s="7">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="K409" s="7"/>
       <c r="L409" s="7"/>
@@ -14319,19 +14359,19 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G411" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="H411" s="8">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c t="s" r="I411" s="7">
-        <v>446</v>
+        <v>451</v>
       </c>
       <c t="s" r="J411" s="7">
         <v>83</v>
@@ -14339,7 +14379,7 @@
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
       <c t="s" r="M411" s="7">
-        <v>276</v>
+        <v>281</v>
       </c>
     </row>
     <row r="412" ht="14.25" customHeight="1">
@@ -14354,22 +14394,22 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>444</v>
+        <v>449</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>445</v>
+        <v>450</v>
       </c>
       <c t="s" r="H412" s="8">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c t="s" r="I412" s="7">
         <v>112</v>
       </c>
       <c t="s" r="J412" s="7">
-        <v>193</v>
+        <v>198</v>
       </c>
       <c r="K412" s="7"/>
       <c r="L412" s="7"/>
@@ -14402,7 +14442,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14411,17 +14451,19 @@
         <v>26</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c t="s" r="I414" s="7">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
-      <c r="M414" s="7"/>
+      <c t="s" r="M414" s="7">
+        <v>454</v>
+      </c>
     </row>
     <row r="415" ht="15" customHeight="1">
       <c t="s" r="A415" s="6">
@@ -14435,22 +14477,22 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>447</v>
+        <v>452</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>448</v>
+        <v>453</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>26</v>
       </c>
       <c t="s" r="I415" s="7">
-        <v>192</v>
+        <v>197</v>
       </c>
       <c t="s" r="J415" s="7">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="K415" s="7"/>
       <c r="L415" s="7"/>
@@ -14479,11 +14521,11 @@
         <v>6853</v>
       </c>
       <c t="s" r="C417" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D417" s="7"/>
       <c t="s" r="E417" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F417" s="7">
         <v>330</v>
@@ -14492,17 +14534,19 @@
         <v>17</v>
       </c>
       <c t="s" r="H417" s="8">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c t="s" r="I417" s="7">
-        <v>452</v>
+        <v>458</v>
       </c>
       <c t="s" r="J417" s="7">
         <v>126</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
-      <c r="M417" s="7"/>
+      <c t="s" r="M417" s="7">
+        <v>415</v>
+      </c>
     </row>
     <row r="418" ht="14.25" customHeight="1">
       <c t="s" r="A418" s="6">
@@ -14512,23 +14556,23 @@
         <v>6854</v>
       </c>
       <c t="s" r="C418" s="7">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="D418" s="7"/>
       <c t="s" r="E418" s="7">
-        <v>450</v>
+        <v>456</v>
       </c>
       <c r="F418" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G418" s="8">
-        <v>451</v>
+        <v>457</v>
       </c>
       <c t="s" r="H418" s="8">
         <v>17</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c t="s" r="J418" s="7">
         <v>79</v>
@@ -14564,7 +14608,7 @@
       </c>
       <c r="D420" s="7"/>
       <c t="s" r="E420" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F420" s="7">
         <v>330</v>
@@ -14576,10 +14620,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14597,7 +14641,7 @@
       </c>
       <c r="D421" s="7"/>
       <c t="s" r="E421" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F421" s="7">
         <v>330</v>
@@ -14609,10 +14653,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I421" s="7">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
@@ -14630,7 +14674,7 @@
       </c>
       <c r="D422" s="7"/>
       <c t="s" r="E422" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F422" s="7">
         <v>330</v>
@@ -14642,10 +14686,10 @@
         <v>42</v>
       </c>
       <c t="s" r="I422" s="7">
-        <v>454</v>
+        <v>460</v>
       </c>
       <c t="s" r="J422" s="7">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="K422" s="7"/>
       <c r="L422" s="7"/>
@@ -14663,7 +14707,7 @@
       </c>
       <c r="D423" s="7"/>
       <c t="s" r="E423" s="7">
-        <v>453</v>
+        <v>459</v>
       </c>
       <c r="F423" s="7">
         <v>330</v>
@@ -14675,10 +14719,10 @@
         <v>26</v>
       </c>
       <c t="s" r="I423" s="7">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c t="s" r="J423" s="7">
-        <v>456</v>
+        <v>462</v>
       </c>
       <c r="K423" s="7"/>
       <c r="L423" s="7"/>
@@ -14686,7 +14730,7 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c t="s" r="A424" s="9">
-        <v>457</v>
+        <v>463</v>
       </c>
       <c r="B424" s="9"/>
       <c r="C424" s="9"/>
@@ -14706,7 +14750,7 @@
     <row r="425" ht="66" customHeight="1"/>
     <row r="426" ht="16.5" customHeight="1">
       <c t="s" r="A426" s="10">
-        <v>458</v>
+        <v>464</v>
       </c>
       <c r="B426" s="10"/>
       <c r="C426" s="10"/>
@@ -14719,7 +14763,7 @@
       <c r="J426" s="10"/>
       <c r="K426" s="10"/>
       <c t="s" r="L426" s="11">
-        <v>459</v>
+        <v>465</v>
       </c>
       <c r="M426" s="11"/>
       <c r="N426" s="11"/>

--- a/Data/FlightPlan/FPL_29OCT26.xlsx
+++ b/Data/FlightPlan/FPL_29OCT26.xlsx
@@ -161,6 +161,9 @@
     <t>18:15</t>
   </si>
   <si>
+    <t>18:05</t>
+  </si>
+  <si>
     <t>DLI</t>
   </si>
   <si>
@@ -488,9 +491,6 @@
     <t>16:00</t>
   </si>
   <si>
-    <t>18:05</t>
-  </si>
-  <si>
     <t>18:40</t>
   </si>
   <si>
@@ -824,7 +824,10 @@
     <t>13:50</t>
   </si>
   <si>
-    <t>16:07</t>
+    <t>15:59</t>
+  </si>
+  <si>
+    <t>18:55</t>
   </si>
   <si>
     <t>VN-A580</t>
@@ -1118,9 +1121,6 @@
     <t>12:58</t>
   </si>
   <si>
-    <t>16:11</t>
-  </si>
-  <si>
     <t>23:00</t>
   </si>
   <si>
@@ -1133,12 +1133,12 @@
     <t>TPE</t>
   </si>
   <si>
+    <t>17:51</t>
+  </si>
+  <si>
     <t>VN-A648</t>
   </si>
   <si>
-    <t>15:59</t>
-  </si>
-  <si>
     <t>VN-A649</t>
   </si>
   <si>
@@ -1229,7 +1229,7 @@
     <t>19:00</t>
   </si>
   <si>
-    <t>18:56</t>
+    <t>18:57</t>
   </si>
   <si>
     <t>VN-A663</t>
@@ -1346,7 +1346,7 @@
     <t>13:41</t>
   </si>
   <si>
-    <t>17:34</t>
+    <t>17:17</t>
   </si>
   <si>
     <t>DEL</t>
@@ -1376,7 +1376,7 @@
     <t>16:35</t>
   </si>
   <si>
-    <t>16:57</t>
+    <t>17:06</t>
   </si>
   <si>
     <t>CMB</t>
@@ -1451,9 +1451,6 @@
     <t>BOM</t>
   </si>
   <si>
-    <t>18:55</t>
-  </si>
-  <si>
     <t>00:10</t>
   </si>
   <si>
@@ -1514,6 +1511,9 @@
     <t>BNE</t>
   </si>
   <si>
+    <t>21:47</t>
+  </si>
+  <si>
     <t>05:05</t>
   </si>
   <si>
@@ -1541,7 +1541,7 @@
     <t>Total Record(s): 348</t>
   </si>
   <si>
-    <t xml:space="preserve">Generated on  Oct 29, 2026 14:16</t>
+    <t xml:space="preserve">Generated on  Oct 29, 2026 14:37</t>
   </si>
   <si>
     <t>Page 1 of 1</t>
@@ -2469,7 +2469,9 @@
       </c>
       <c r="K18" s="7"/>
       <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
+      <c t="s" r="M18" s="7">
+        <v>50</v>
+      </c>
     </row>
     <row r="19" ht="14.25" customHeight="1">
       <c t="s" r="A19" s="6">
@@ -2492,13 +2494,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H19" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I19" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J19" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K19" s="7"/>
       <c r="L19" s="7"/>
@@ -2522,16 +2524,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G20" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H20" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I20" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J20" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K20" s="7"/>
       <c r="L20" s="7"/>
@@ -2558,13 +2560,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H21" s="8">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c t="s" r="I21" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c t="s" r="J21" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K21" s="7"/>
       <c r="L21" s="7"/>
@@ -2597,7 +2599,7 @@
       </c>
       <c r="D23" s="7"/>
       <c t="s" r="E23" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F23" s="7">
         <v>321</v>
@@ -2606,10 +2608,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H23" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="I23" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c t="s" r="J23" s="7">
         <v>35</v>
@@ -2617,7 +2619,7 @@
       <c r="K23" s="7"/>
       <c r="L23" s="7"/>
       <c t="s" r="M23" s="7">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" ht="14.25" customHeight="1">
@@ -2632,13 +2634,13 @@
       </c>
       <c r="D24" s="7"/>
       <c t="s" r="E24" s="7">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F24" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G24" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="H24" s="8">
         <v>43</v>
@@ -2647,7 +2649,7 @@
         <v>36</v>
       </c>
       <c t="s" r="J24" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K24" s="7"/>
       <c r="L24" s="7"/>
@@ -2680,7 +2682,7 @@
       </c>
       <c r="D26" s="7"/>
       <c t="s" r="E26" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F26" s="7">
         <v>321</v>
@@ -2689,18 +2691,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H26" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="I26" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J26" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K26" s="7"/>
       <c r="L26" s="7"/>
       <c t="s" r="M26" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="27" ht="14.25" customHeight="1">
@@ -2715,27 +2717,27 @@
       </c>
       <c r="D27" s="7"/>
       <c t="s" r="E27" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F27" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G27" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="H27" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I27" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J27" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K27" s="7"/>
       <c r="L27" s="7"/>
       <c t="s" r="M27" s="7">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" ht="14.25" customHeight="1">
@@ -2750,7 +2752,7 @@
       </c>
       <c r="D28" s="7"/>
       <c t="s" r="E28" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F28" s="7">
         <v>321</v>
@@ -2759,18 +2761,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H28" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="I28" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J28" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K28" s="7"/>
       <c r="L28" s="7"/>
       <c t="s" r="M28" s="7">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="29" ht="14.25" customHeight="1">
@@ -2785,22 +2787,22 @@
       </c>
       <c r="D29" s="7"/>
       <c t="s" r="E29" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F29" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G29" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="H29" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I29" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J29" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K29" s="7"/>
       <c r="L29" s="7"/>
@@ -2818,7 +2820,7 @@
       </c>
       <c r="D30" s="7"/>
       <c t="s" r="E30" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F30" s="7">
         <v>321</v>
@@ -2827,13 +2829,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H30" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I30" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c t="s" r="J30" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K30" s="7"/>
       <c r="L30" s="7"/>
@@ -2851,13 +2853,13 @@
       </c>
       <c r="D31" s="7"/>
       <c t="s" r="E31" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F31" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G31" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H31" s="8">
         <v>27</v>
@@ -2866,7 +2868,7 @@
         <v>29</v>
       </c>
       <c t="s" r="J31" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K31" s="7"/>
       <c r="L31" s="7"/>
@@ -2884,7 +2886,7 @@
       </c>
       <c r="D32" s="7"/>
       <c t="s" r="E32" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F32" s="7">
         <v>321</v>
@@ -2896,10 +2898,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I32" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J32" s="7">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="K32" s="7"/>
       <c r="L32" s="7"/>
@@ -2917,7 +2919,7 @@
       </c>
       <c r="D33" s="7"/>
       <c t="s" r="E33" s="7">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F33" s="7">
         <v>321</v>
@@ -2932,7 +2934,7 @@
         <v>38</v>
       </c>
       <c t="s" r="J33" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K33" s="7"/>
       <c r="L33" s="7"/>
@@ -2965,27 +2967,27 @@
       </c>
       <c r="D35" s="7"/>
       <c t="s" r="E35" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F35" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G35" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H35" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I35" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J35" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K35" s="7"/>
       <c r="L35" s="7"/>
       <c t="s" r="M35" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="36" ht="14.25" customHeight="1">
@@ -3000,7 +3002,7 @@
       </c>
       <c r="D36" s="7"/>
       <c t="s" r="E36" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F36" s="7">
         <v>321</v>
@@ -3009,13 +3011,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H36" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I36" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J36" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K36" s="7"/>
       <c r="L36" s="7"/>
@@ -3033,22 +3035,22 @@
       </c>
       <c r="D37" s="7"/>
       <c t="s" r="E37" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F37" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G37" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H37" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I37" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J37" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K37" s="7"/>
       <c r="L37" s="7"/>
@@ -3066,7 +3068,7 @@
       </c>
       <c r="D38" s="7"/>
       <c t="s" r="E38" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F38" s="7">
         <v>321</v>
@@ -3078,10 +3080,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I38" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c t="s" r="J38" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K38" s="7"/>
       <c r="L38" s="7"/>
@@ -3099,7 +3101,7 @@
       </c>
       <c r="D39" s="7"/>
       <c t="s" r="E39" s="7">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F39" s="7">
         <v>321</v>
@@ -3111,10 +3113,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I39" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J39" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K39" s="7"/>
       <c r="L39" s="7"/>
@@ -3147,7 +3149,7 @@
       </c>
       <c r="D41" s="7"/>
       <c t="s" r="E41" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F41" s="7">
         <v>321</v>
@@ -3156,18 +3158,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H41" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="I41" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J41" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K41" s="7"/>
       <c r="L41" s="7"/>
       <c t="s" r="M41" s="7">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" ht="14.25" customHeight="1">
@@ -3182,27 +3184,27 @@
       </c>
       <c r="D42" s="7"/>
       <c t="s" r="E42" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F42" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G42" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="H42" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I42" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c t="s" r="J42" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K42" s="7"/>
       <c r="L42" s="7"/>
       <c t="s" r="M42" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="43" ht="14.25" customHeight="1">
@@ -3217,7 +3219,7 @@
       </c>
       <c r="D43" s="7"/>
       <c t="s" r="E43" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F43" s="7">
         <v>321</v>
@@ -3226,13 +3228,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H43" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I43" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J43" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K43" s="7"/>
       <c r="L43" s="7"/>
@@ -3250,22 +3252,22 @@
       </c>
       <c r="D44" s="7"/>
       <c t="s" r="E44" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F44" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G44" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H44" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I44" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J44" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K44" s="7"/>
       <c r="L44" s="7"/>
@@ -3283,7 +3285,7 @@
       </c>
       <c r="D45" s="7"/>
       <c t="s" r="E45" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F45" s="7">
         <v>321</v>
@@ -3292,13 +3294,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H45" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="I45" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J45" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K45" s="7"/>
       <c r="L45" s="7"/>
@@ -3316,19 +3318,19 @@
       </c>
       <c r="D46" s="7"/>
       <c t="s" r="E46" s="7">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="F46" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G46" s="8">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c t="s" r="H46" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I46" s="7">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c t="s" r="J46" s="7">
         <v>41</v>
@@ -3364,7 +3366,7 @@
       </c>
       <c r="D48" s="7"/>
       <c t="s" r="E48" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F48" s="7">
         <v>321</v>
@@ -3373,18 +3375,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H48" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I48" s="7">
         <v>18</v>
       </c>
       <c t="s" r="J48" s="7">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K48" s="7"/>
       <c r="L48" s="7"/>
       <c t="s" r="M48" s="7">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="49" ht="14.25" customHeight="1">
@@ -3399,27 +3401,27 @@
       </c>
       <c r="D49" s="7"/>
       <c t="s" r="E49" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F49" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G49" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H49" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I49" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J49" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K49" s="7"/>
       <c r="L49" s="7"/>
       <c t="s" r="M49" s="7">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="50" ht="15" customHeight="1">
@@ -3434,7 +3436,7 @@
       </c>
       <c r="D50" s="7"/>
       <c t="s" r="E50" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F50" s="7">
         <v>321</v>
@@ -3443,13 +3445,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H50" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I50" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J50" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K50" s="7"/>
       <c r="L50" s="7"/>
@@ -3467,22 +3469,22 @@
       </c>
       <c r="D51" s="7"/>
       <c t="s" r="E51" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F51" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G51" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H51" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I51" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c t="s" r="J51" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="K51" s="7"/>
       <c r="L51" s="7"/>
@@ -3500,7 +3502,7 @@
       </c>
       <c r="D52" s="7"/>
       <c t="s" r="E52" s="7">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F52" s="7">
         <v>321</v>
@@ -3512,10 +3514,10 @@
         <v>31</v>
       </c>
       <c t="s" r="I52" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c t="s" r="J52" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K52" s="7"/>
       <c r="L52" s="7"/>
@@ -3548,7 +3550,7 @@
       </c>
       <c r="D54" s="7"/>
       <c t="s" r="E54" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F54" s="7">
         <v>321</v>
@@ -3557,18 +3559,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H54" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I54" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J54" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K54" s="7"/>
       <c r="L54" s="7"/>
       <c t="s" r="M54" s="7">
-        <v>126</v>
+        <v>127</v>
       </c>
     </row>
     <row r="55" ht="15" customHeight="1">
@@ -3583,19 +3585,19 @@
       </c>
       <c r="D55" s="7"/>
       <c t="s" r="E55" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F55" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G55" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H55" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I55" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J55" s="7">
         <v>19</v>
@@ -3618,7 +3620,7 @@
       </c>
       <c r="D56" s="7"/>
       <c t="s" r="E56" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F56" s="7">
         <v>321</v>
@@ -3627,18 +3629,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H56" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I56" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J56" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K56" s="7"/>
       <c r="L56" s="7"/>
       <c t="s" r="M56" s="7">
-        <v>129</v>
+        <v>130</v>
       </c>
     </row>
     <row r="57" ht="14.25" customHeight="1">
@@ -3653,27 +3655,27 @@
       </c>
       <c r="D57" s="7"/>
       <c t="s" r="E57" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F57" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G57" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H57" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I57" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J57" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K57" s="7"/>
       <c r="L57" s="7"/>
       <c t="s" r="M57" s="7">
-        <v>131</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" ht="14.25" customHeight="1">
@@ -3688,7 +3690,7 @@
       </c>
       <c r="D58" s="7"/>
       <c t="s" r="E58" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F58" s="7">
         <v>321</v>
@@ -3697,13 +3699,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H58" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I58" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J58" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K58" s="7"/>
       <c r="L58" s="7"/>
@@ -3721,22 +3723,22 @@
       </c>
       <c r="D59" s="7"/>
       <c t="s" r="E59" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F59" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G59" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H59" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I59" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J59" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K59" s="7"/>
       <c r="L59" s="7"/>
@@ -3754,22 +3756,22 @@
       </c>
       <c r="D60" s="7"/>
       <c t="s" r="E60" s="7">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F60" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G60" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H60" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I60" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c t="s" r="J60" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K60" s="7"/>
       <c r="L60" s="7"/>
@@ -3802,7 +3804,7 @@
       </c>
       <c r="D62" s="7"/>
       <c t="s" r="E62" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F62" s="7">
         <v>321</v>
@@ -3814,7 +3816,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I62" s="7">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c t="s" r="J62" s="7">
         <v>18</v>
@@ -3822,7 +3824,7 @@
       <c r="K62" s="7"/>
       <c r="L62" s="7"/>
       <c t="s" r="M62" s="7">
-        <v>139</v>
+        <v>140</v>
       </c>
     </row>
     <row r="63" ht="14.25" customHeight="1">
@@ -3837,7 +3839,7 @@
       </c>
       <c r="D63" s="7"/>
       <c t="s" r="E63" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F63" s="7">
         <v>321</v>
@@ -3849,7 +3851,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I63" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J63" s="7">
         <v>32</v>
@@ -3872,7 +3874,7 @@
       </c>
       <c r="D64" s="7"/>
       <c t="s" r="E64" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F64" s="7">
         <v>321</v>
@@ -3884,15 +3886,15 @@
         <v>37</v>
       </c>
       <c t="s" r="I64" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J64" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="K64" s="7"/>
       <c r="L64" s="7"/>
       <c t="s" r="M64" s="7">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="65" ht="15" customHeight="1">
@@ -3907,7 +3909,7 @@
       </c>
       <c r="D65" s="7"/>
       <c t="s" r="E65" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F65" s="7">
         <v>321</v>
@@ -3919,10 +3921,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I65" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J65" s="7">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="K65" s="7"/>
       <c r="L65" s="7"/>
@@ -3940,7 +3942,7 @@
       </c>
       <c r="D66" s="7"/>
       <c t="s" r="E66" s="7">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F66" s="7">
         <v>321</v>
@@ -3955,7 +3957,7 @@
         <v>40</v>
       </c>
       <c t="s" r="J66" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K66" s="7"/>
       <c r="L66" s="7"/>
@@ -3988,7 +3990,7 @@
       </c>
       <c r="D68" s="7"/>
       <c t="s" r="E68" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F68" s="7">
         <v>321</v>
@@ -3997,18 +3999,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H68" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="I68" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J68" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K68" s="7"/>
       <c r="L68" s="7"/>
       <c t="s" r="M68" s="7">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="69" ht="14.25" customHeight="1">
@@ -4023,27 +4025,27 @@
       </c>
       <c r="D69" s="7"/>
       <c t="s" r="E69" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F69" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G69" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="H69" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I69" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J69" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K69" s="7"/>
       <c r="L69" s="7"/>
       <c t="s" r="M69" s="7">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="70" ht="15" customHeight="1">
@@ -4058,7 +4060,7 @@
       </c>
       <c r="D70" s="7"/>
       <c t="s" r="E70" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F70" s="7">
         <v>321</v>
@@ -4070,15 +4072,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I70" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J70" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K70" s="7"/>
       <c r="L70" s="7"/>
       <c t="s" r="M70" s="7">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="71" ht="14.25" customHeight="1">
@@ -4093,7 +4095,7 @@
       </c>
       <c r="D71" s="7"/>
       <c t="s" r="E71" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F71" s="7">
         <v>321</v>
@@ -4105,7 +4107,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I71" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J71" s="7">
         <v>34</v>
@@ -4113,7 +4115,7 @@
       <c r="K71" s="7"/>
       <c r="L71" s="7"/>
       <c t="s" r="M71" s="7">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="72" ht="14.25" customHeight="1">
@@ -4128,7 +4130,7 @@
       </c>
       <c r="D72" s="7"/>
       <c t="s" r="E72" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F72" s="7">
         <v>321</v>
@@ -4140,10 +4142,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I72" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J72" s="7">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c r="K72" s="7"/>
       <c r="L72" s="7"/>
@@ -4161,7 +4163,7 @@
       </c>
       <c r="D73" s="7"/>
       <c t="s" r="E73" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F73" s="7">
         <v>321</v>
@@ -4194,7 +4196,7 @@
       </c>
       <c r="D74" s="7"/>
       <c t="s" r="E74" s="7">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F74" s="7">
         <v>321</v>
@@ -4209,7 +4211,7 @@
         <v>162</v>
       </c>
       <c t="s" r="J74" s="7">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="K74" s="7"/>
       <c r="L74" s="7"/>
@@ -4291,7 +4293,7 @@
         <v>168</v>
       </c>
       <c t="s" r="I77" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J77" s="7">
         <v>169</v>
@@ -4327,7 +4329,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J78" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K78" s="7"/>
       <c r="L78" s="7"/>
@@ -4473,7 +4475,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I83" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c t="s" r="J83" s="7">
         <v>181</v>
@@ -4551,11 +4553,11 @@
         <v>187</v>
       </c>
       <c t="s" r="K85" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="L85" s="7"/>
       <c t="s" r="M85" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="86" ht="14.25" customHeight="1">
@@ -4579,13 +4581,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H86" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I86" s="7">
         <v>188</v>
       </c>
       <c t="s" r="J86" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K86" s="7"/>
       <c r="L86" s="7"/>
@@ -4609,7 +4611,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G87" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H87" s="8">
         <v>27</v>
@@ -4651,7 +4653,7 @@
         <v>191</v>
       </c>
       <c t="s" r="J88" s="7">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K88" s="7"/>
       <c r="L88" s="7"/>
@@ -4690,7 +4692,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G90" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H90" s="8">
         <v>27</v>
@@ -4704,7 +4706,7 @@
       <c r="K90" s="7"/>
       <c r="L90" s="7"/>
       <c t="s" r="M90" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" ht="14.25" customHeight="1">
@@ -4728,7 +4730,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H91" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="I91" s="7">
         <v>195</v>
@@ -4760,7 +4762,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G92" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="H92" s="8">
         <v>27</v>
@@ -4798,7 +4800,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H93" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="I93" s="7">
         <v>200</v>
@@ -4811,7 +4813,7 @@
       </c>
       <c r="L93" s="7"/>
       <c t="s" r="M93" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="94" ht="14.25" customHeight="1">
@@ -4832,19 +4834,19 @@
         <v>321</v>
       </c>
       <c t="s" r="G94" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="H94" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I94" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J94" s="7">
         <v>36</v>
       </c>
       <c t="s" r="K94" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="L94" s="7"/>
       <c t="s" r="M94" s="7">
@@ -4908,7 +4910,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I96" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J96" s="7">
         <v>204</v>
@@ -4991,10 +4993,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I99" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c t="s" r="J99" s="7">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K99" s="7"/>
       <c r="L99" s="7"/>
@@ -5069,7 +5071,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H102" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I102" s="7">
         <v>211</v>
@@ -5101,7 +5103,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G103" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H103" s="8">
         <v>27</v>
@@ -5139,7 +5141,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H104" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I104" s="7">
         <v>216</v>
@@ -5171,13 +5173,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G105" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H105" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I105" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J105" s="7">
         <v>219</v>
@@ -5209,10 +5211,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H106" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I106" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J106" s="7">
         <v>188</v>
@@ -5239,7 +5241,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G107" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H107" s="8">
         <v>27</v>
@@ -5278,7 +5280,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I108" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J108" s="7">
         <v>208</v>
@@ -5329,7 +5331,7 @@
         <v>194</v>
       </c>
       <c t="s" r="J110" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K110" s="7"/>
       <c r="L110" s="7"/>
@@ -5432,7 +5434,7 @@
         <v>228</v>
       </c>
       <c t="s" r="J113" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="K113" s="7"/>
       <c r="L113" s="7"/>
@@ -5485,7 +5487,7 @@
       <c r="K115" s="7"/>
       <c r="L115" s="7"/>
       <c t="s" r="M115" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="116" ht="14.25" customHeight="1">
@@ -5512,10 +5514,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I116" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J116" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K116" s="7"/>
       <c r="L116" s="7"/>
@@ -5655,7 +5657,7 @@
         <v>236</v>
       </c>
       <c t="s" r="J120" s="7">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="K120" s="7"/>
       <c r="L120" s="7"/>
@@ -5685,10 +5687,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I121" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J121" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K121" s="7"/>
       <c r="L121" s="7"/>
@@ -5718,7 +5720,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I122" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J122" s="7">
         <v>237</v>
@@ -5760,7 +5762,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G124" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="H124" s="8">
         <v>43</v>
@@ -5774,7 +5776,7 @@
       <c r="K124" s="7"/>
       <c r="L124" s="7"/>
       <c t="s" r="M124" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
     </row>
     <row r="125" ht="15" customHeight="1">
@@ -5798,13 +5800,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H125" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I125" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J125" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K125" s="7"/>
       <c r="L125" s="7"/>
@@ -5828,16 +5830,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G126" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H126" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I126" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J126" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K126" s="7"/>
       <c r="L126" s="7"/>
@@ -5864,13 +5866,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H127" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I127" s="7">
         <v>239</v>
       </c>
       <c t="s" r="J127" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K127" s="7"/>
       <c r="L127" s="7"/>
@@ -5909,7 +5911,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G129" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H129" s="8">
         <v>183</v>
@@ -5945,10 +5947,10 @@
         <v>183</v>
       </c>
       <c t="s" r="H130" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I130" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J130" s="7">
         <v>170</v>
@@ -5975,7 +5977,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G131" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H131" s="8">
         <v>27</v>
@@ -6011,13 +6013,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H132" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I132" s="7">
         <v>241</v>
       </c>
       <c t="s" r="J132" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K132" s="7"/>
       <c r="L132" s="7"/>
@@ -6097,10 +6099,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I135" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J135" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K135" s="7"/>
       <c r="L135" s="7"/>
@@ -6195,13 +6197,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H138" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I138" s="7">
         <v>221</v>
       </c>
       <c t="s" r="J138" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K138" s="7"/>
       <c r="L138" s="7"/>
@@ -6225,13 +6227,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G139" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H139" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I139" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c t="s" r="J139" s="7">
         <v>250</v>
@@ -6420,7 +6422,7 @@
         <v>260</v>
       </c>
       <c t="s" r="J145" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K145" s="7"/>
       <c r="L145" s="7"/>
@@ -6453,7 +6455,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J146" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K146" s="7"/>
       <c r="L146" s="7"/>
@@ -6486,7 +6488,7 @@
         <v>190</v>
       </c>
       <c t="s" r="J147" s="7">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K147" s="7"/>
       <c r="L147" s="7"/>
@@ -6519,7 +6521,7 @@
         <v>263</v>
       </c>
       <c t="s" r="J148" s="7">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="K148" s="7"/>
       <c r="L148" s="7"/>
@@ -6602,7 +6604,7 @@
         <v>45</v>
       </c>
       <c t="s" r="J151" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="K151" s="7"/>
       <c r="L151" s="7"/>
@@ -6631,7 +6633,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H152" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I152" s="7">
         <v>166</v>
@@ -6663,7 +6665,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G153" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H153" s="8">
         <v>43</v>
@@ -6701,17 +6703,21 @@
         <v>43</v>
       </c>
       <c t="s" r="H154" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I154" s="7">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c t="s" r="J154" s="7">
-        <v>133</v>
-      </c>
-      <c r="K154" s="7"/>
+        <v>134</v>
+      </c>
+      <c t="s" r="K154" s="7">
+        <v>90</v>
+      </c>
       <c r="L154" s="7"/>
-      <c r="M154" s="7"/>
+      <c t="s" r="M154" s="7">
+        <v>135</v>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c t="s" r="A155" s="6">
@@ -6731,20 +6737,24 @@
         <v>321</v>
       </c>
       <c t="s" r="G155" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H155" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I155" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J155" s="7">
-        <v>136</v>
-      </c>
-      <c r="K155" s="7"/>
+        <v>137</v>
+      </c>
+      <c t="s" r="K155" s="7">
+        <v>272</v>
+      </c>
       <c r="L155" s="7"/>
-      <c r="M155" s="7"/>
+      <c t="s" r="M155" s="7">
+        <v>221</v>
+      </c>
     </row>
     <row r="156" ht="14.25" customHeight="1">
       <c r="A156" s="6"/>
@@ -6773,29 +6783,29 @@
       </c>
       <c r="D157" s="7"/>
       <c t="s" r="E157" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F157" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G157" s="8">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c t="s" r="H157" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I157" s="7">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c t="s" r="J157" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="K157" s="7">
         <v>230</v>
       </c>
       <c r="L157" s="7"/>
       <c t="s" r="M157" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="158" ht="14.25" customHeight="1">
@@ -6810,7 +6820,7 @@
       </c>
       <c r="D158" s="7"/>
       <c t="s" r="E158" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F158" s="7">
         <v>321</v>
@@ -6822,17 +6832,17 @@
         <v>177</v>
       </c>
       <c t="s" r="I158" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J158" s="7">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c t="s" r="K158" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L158" s="7"/>
       <c t="s" r="M158" s="7">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="159" ht="14.25" customHeight="1">
@@ -6847,7 +6857,7 @@
       </c>
       <c r="D159" s="7"/>
       <c t="s" r="E159" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F159" s="7">
         <v>321</v>
@@ -6859,10 +6869,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I159" s="7">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c t="s" r="J159" s="7">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K159" s="7"/>
       <c r="L159" s="7"/>
@@ -6880,7 +6890,7 @@
       </c>
       <c r="D160" s="7"/>
       <c t="s" r="E160" s="7">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="F160" s="7">
         <v>321</v>
@@ -6889,13 +6899,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H160" s="8">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c t="s" r="I160" s="7">
         <v>237</v>
       </c>
       <c t="s" r="J160" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="K160" s="7"/>
       <c r="L160" s="7"/>
@@ -6928,7 +6938,7 @@
       </c>
       <c r="D162" s="7"/>
       <c t="s" r="E162" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F162" s="7">
         <v>321</v>
@@ -6937,10 +6947,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H162" s="8">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="I162" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J162" s="7">
         <v>35</v>
@@ -6948,7 +6958,7 @@
       <c r="K162" s="7"/>
       <c r="L162" s="7"/>
       <c t="s" r="M162" s="7">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="163" ht="14.25" customHeight="1">
@@ -6963,13 +6973,13 @@
       </c>
       <c r="D163" s="7"/>
       <c t="s" r="E163" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F163" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G163" s="8">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c t="s" r="H163" s="8">
         <v>27</v>
@@ -6978,7 +6988,7 @@
         <v>170</v>
       </c>
       <c t="s" r="J163" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K163" s="7"/>
       <c r="L163" s="7"/>
@@ -6996,7 +7006,7 @@
       </c>
       <c r="D164" s="7"/>
       <c t="s" r="E164" s="7">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="F164" s="7">
         <v>321</v>
@@ -7005,7 +7015,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H164" s="8">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c t="s" r="I164" s="7">
         <v>237</v>
@@ -7044,27 +7054,27 @@
       </c>
       <c r="D166" s="7"/>
       <c t="s" r="E166" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F166" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G166" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H166" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I166" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c t="s" r="J166" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K166" s="7"/>
       <c r="L166" s="7"/>
       <c t="s" r="M166" s="7">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="167" ht="14.25" customHeight="1">
@@ -7079,7 +7089,7 @@
       </c>
       <c r="D167" s="7"/>
       <c t="s" r="E167" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F167" s="7">
         <v>321</v>
@@ -7088,10 +7098,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H167" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I167" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J167" s="7">
         <v>19</v>
@@ -7099,7 +7109,7 @@
       <c r="K167" s="7"/>
       <c r="L167" s="7"/>
       <c t="s" r="M167" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="168" ht="14.25" customHeight="1">
@@ -7114,27 +7124,27 @@
       </c>
       <c r="D168" s="7"/>
       <c t="s" r="E168" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F168" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G168" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H168" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I168" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J168" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K168" s="7"/>
       <c r="L168" s="7"/>
       <c t="s" r="M168" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
     </row>
     <row r="169" ht="14.25" customHeight="1">
@@ -7149,19 +7159,19 @@
       </c>
       <c r="D169" s="7"/>
       <c t="s" r="E169" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F169" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G169" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H169" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I169" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J169" s="7">
         <v>25</v>
@@ -7182,22 +7192,22 @@
       </c>
       <c r="D170" s="7"/>
       <c t="s" r="E170" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F170" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G170" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H170" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I170" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J170" s="7">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="K170" s="7"/>
       <c r="L170" s="7"/>
@@ -7215,22 +7225,22 @@
       </c>
       <c r="D171" s="7"/>
       <c t="s" r="E171" s="7">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="F171" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G171" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H171" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I171" s="7">
         <v>228</v>
       </c>
       <c t="s" r="J171" s="7">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="K171" s="7"/>
       <c r="L171" s="7"/>
@@ -7263,7 +7273,7 @@
       </c>
       <c r="D173" s="7"/>
       <c t="s" r="E173" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F173" s="7">
         <v>321</v>
@@ -7275,7 +7285,7 @@
         <v>258</v>
       </c>
       <c t="s" r="I173" s="7">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c t="s" r="J173" s="7">
         <v>195</v>
@@ -7283,7 +7293,7 @@
       <c r="K173" s="7"/>
       <c r="L173" s="7"/>
       <c t="s" r="M173" s="7">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="174" ht="14.25" customHeight="1">
@@ -7298,7 +7308,7 @@
       </c>
       <c r="D174" s="7"/>
       <c t="s" r="E174" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F174" s="7">
         <v>321</v>
@@ -7318,7 +7328,7 @@
       <c r="K174" s="7"/>
       <c r="L174" s="7"/>
       <c t="s" r="M174" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="175" ht="15" customHeight="1">
@@ -7333,7 +7343,7 @@
       </c>
       <c r="D175" s="7"/>
       <c t="s" r="E175" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F175" s="7">
         <v>321</v>
@@ -7342,18 +7352,18 @@
         <v>43</v>
       </c>
       <c t="s" r="H175" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I175" s="7">
         <v>269</v>
       </c>
       <c t="s" r="J175" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="K175" s="7"/>
       <c r="L175" s="7"/>
       <c t="s" r="M175" s="7">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="176" ht="14.25" customHeight="1">
@@ -7368,22 +7378,22 @@
       </c>
       <c r="D176" s="7"/>
       <c t="s" r="E176" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F176" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G176" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H176" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I176" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J176" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K176" s="7"/>
       <c r="L176" s="7"/>
@@ -7401,7 +7411,7 @@
       </c>
       <c r="D177" s="7"/>
       <c t="s" r="E177" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F177" s="7">
         <v>321</v>
@@ -7434,7 +7444,7 @@
       </c>
       <c r="D178" s="7"/>
       <c t="s" r="E178" s="7">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F178" s="7">
         <v>321</v>
@@ -7449,7 +7459,7 @@
         <v>261</v>
       </c>
       <c t="s" r="J178" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K178" s="7"/>
       <c r="L178" s="7"/>
@@ -7482,7 +7492,7 @@
       </c>
       <c r="D180" s="7"/>
       <c t="s" r="E180" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F180" s="7">
         <v>321</v>
@@ -7494,7 +7504,7 @@
         <v>183</v>
       </c>
       <c t="s" r="I180" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c t="s" r="J180" s="7">
         <v>216</v>
@@ -7502,7 +7512,7 @@
       <c r="K180" s="7"/>
       <c r="L180" s="7"/>
       <c t="s" r="M180" s="7">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="181" ht="14.25" customHeight="1">
@@ -7517,7 +7527,7 @@
       </c>
       <c r="D181" s="7"/>
       <c t="s" r="E181" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F181" s="7">
         <v>321</v>
@@ -7529,7 +7539,7 @@
         <v>168</v>
       </c>
       <c t="s" r="I181" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J181" s="7">
         <v>198</v>
@@ -7537,7 +7547,7 @@
       <c r="K181" s="7"/>
       <c r="L181" s="7"/>
       <c t="s" r="M181" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="182" ht="14.25" customHeight="1">
@@ -7552,7 +7562,7 @@
       </c>
       <c r="D182" s="7"/>
       <c t="s" r="E182" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F182" s="7">
         <v>321</v>
@@ -7572,7 +7582,7 @@
       <c r="K182" s="7"/>
       <c r="L182" s="7"/>
       <c t="s" r="M182" s="7">
-        <v>304</v>
+        <v>305</v>
       </c>
     </row>
     <row r="183" ht="14.25" customHeight="1">
@@ -7587,7 +7597,7 @@
       </c>
       <c r="D183" s="7"/>
       <c t="s" r="E183" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F183" s="7">
         <v>321</v>
@@ -7599,10 +7609,10 @@
         <v>252</v>
       </c>
       <c t="s" r="I183" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c t="s" r="J183" s="7">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c r="K183" s="7"/>
       <c r="L183" s="7"/>
@@ -7620,7 +7630,7 @@
       </c>
       <c r="D184" s="7"/>
       <c t="s" r="E184" s="7">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F184" s="7">
         <v>321</v>
@@ -7632,10 +7642,10 @@
         <v>183</v>
       </c>
       <c t="s" r="I184" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J184" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K184" s="7"/>
       <c r="L184" s="7"/>
@@ -7668,7 +7678,7 @@
       </c>
       <c r="D186" s="7"/>
       <c t="s" r="E186" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F186" s="7">
         <v>321</v>
@@ -7677,16 +7687,16 @@
         <v>43</v>
       </c>
       <c t="s" r="H186" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="I186" s="7">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c t="s" r="J186" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c t="s" r="K186" s="7">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="L186" s="7"/>
       <c t="s" r="M186" s="7">
@@ -7705,13 +7715,13 @@
       </c>
       <c r="D187" s="7"/>
       <c t="s" r="E187" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F187" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G187" s="8">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c t="s" r="H187" s="8">
         <v>43</v>
@@ -7723,11 +7733,11 @@
         <v>19</v>
       </c>
       <c t="s" r="K187" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="L187" s="7"/>
       <c t="s" r="M187" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
     </row>
     <row r="188" ht="14.25" customHeight="1">
@@ -7742,7 +7752,7 @@
       </c>
       <c r="D188" s="7"/>
       <c t="s" r="E188" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F188" s="7">
         <v>321</v>
@@ -7754,17 +7764,17 @@
         <v>27</v>
       </c>
       <c t="s" r="I188" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="J188" s="7">
         <v>270</v>
       </c>
       <c t="s" r="K188" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L188" s="7"/>
       <c t="s" r="M188" s="7">
-        <v>311</v>
+        <v>312</v>
       </c>
     </row>
     <row r="189" ht="14.25" customHeight="1">
@@ -7779,7 +7789,7 @@
       </c>
       <c r="D189" s="7"/>
       <c t="s" r="E189" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F189" s="7">
         <v>321</v>
@@ -7791,10 +7801,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I189" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J189" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K189" s="7"/>
       <c r="L189" s="7"/>
@@ -7812,7 +7822,7 @@
       </c>
       <c r="D190" s="7"/>
       <c t="s" r="E190" s="7">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="F190" s="7">
         <v>321</v>
@@ -7860,7 +7870,7 @@
       </c>
       <c r="D192" s="7"/>
       <c t="s" r="E192" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F192" s="7">
         <v>321</v>
@@ -7872,15 +7882,15 @@
         <v>43</v>
       </c>
       <c t="s" r="I192" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J192" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K192" s="7"/>
       <c r="L192" s="7"/>
       <c t="s" r="M192" s="7">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="193" ht="14.25" customHeight="1">
@@ -7895,7 +7905,7 @@
       </c>
       <c r="D193" s="7"/>
       <c t="s" r="E193" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F193" s="7">
         <v>321</v>
@@ -7907,7 +7917,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I193" s="7">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c t="s" r="J193" s="7">
         <v>215</v>
@@ -7930,7 +7940,7 @@
       </c>
       <c r="D194" s="7"/>
       <c t="s" r="E194" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F194" s="7">
         <v>321</v>
@@ -7939,18 +7949,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H194" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I194" s="7">
         <v>232</v>
       </c>
       <c t="s" r="J194" s="7">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="K194" s="7"/>
       <c r="L194" s="7"/>
       <c t="s" r="M194" s="7">
-        <v>318</v>
+        <v>319</v>
       </c>
     </row>
     <row r="195" ht="15" customHeight="1">
@@ -7965,27 +7975,27 @@
       </c>
       <c r="D195" s="7"/>
       <c t="s" r="E195" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F195" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G195" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H195" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I195" s="7">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c t="s" r="J195" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K195" s="7"/>
       <c r="L195" s="7"/>
       <c t="s" r="M195" s="7">
-        <v>321</v>
+        <v>322</v>
       </c>
     </row>
     <row r="196" ht="14.25" customHeight="1">
@@ -8000,7 +8010,7 @@
       </c>
       <c r="D196" s="7"/>
       <c t="s" r="E196" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F196" s="7">
         <v>321</v>
@@ -8009,10 +8019,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H196" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="I196" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J196" s="7">
         <v>259</v>
@@ -8033,22 +8043,22 @@
       </c>
       <c r="D197" s="7"/>
       <c t="s" r="E197" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F197" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G197" s="8">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c t="s" r="H197" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I197" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J197" s="7">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K197" s="7"/>
       <c r="L197" s="7"/>
@@ -8066,7 +8076,7 @@
       </c>
       <c r="D198" s="7"/>
       <c t="s" r="E198" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F198" s="7">
         <v>321</v>
@@ -8075,10 +8085,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H198" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="I198" s="7">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c t="s" r="J198" s="7">
         <v>203</v>
@@ -8099,19 +8109,19 @@
       </c>
       <c r="D199" s="7"/>
       <c t="s" r="E199" s="7">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F199" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G199" s="8">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c t="s" r="H199" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I199" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c t="s" r="J199" s="7">
         <v>237</v>
@@ -8147,13 +8157,13 @@
       </c>
       <c r="D201" s="7"/>
       <c t="s" r="E201" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F201" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G201" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H201" s="8">
         <v>252</v>
@@ -8167,7 +8177,7 @@
       <c r="K201" s="7"/>
       <c r="L201" s="7"/>
       <c t="s" r="M201" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="202" ht="14.25" customHeight="1">
@@ -8182,7 +8192,7 @@
       </c>
       <c r="D202" s="7"/>
       <c t="s" r="E202" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F202" s="7">
         <v>321</v>
@@ -8191,18 +8201,18 @@
         <v>252</v>
       </c>
       <c t="s" r="H202" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I202" s="7">
         <v>217</v>
       </c>
       <c t="s" r="J202" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K202" s="7"/>
       <c r="L202" s="7"/>
       <c t="s" r="M202" s="7">
-        <v>328</v>
+        <v>329</v>
       </c>
     </row>
     <row r="203" ht="14.25" customHeight="1">
@@ -8217,19 +8227,19 @@
       </c>
       <c r="D203" s="7"/>
       <c t="s" r="E203" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F203" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G203" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H203" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I203" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c t="s" r="J203" s="7">
         <v>49</v>
@@ -8250,7 +8260,7 @@
       </c>
       <c r="D204" s="7"/>
       <c t="s" r="E204" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F204" s="7">
         <v>321</v>
@@ -8259,13 +8269,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H204" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I204" s="7">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c t="s" r="J204" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K204" s="7"/>
       <c r="L204" s="7"/>
@@ -8283,22 +8293,22 @@
       </c>
       <c r="D205" s="7"/>
       <c t="s" r="E205" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F205" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G205" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H205" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I205" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J205" s="7">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K205" s="7"/>
       <c r="L205" s="7"/>
@@ -8316,7 +8326,7 @@
       </c>
       <c r="D206" s="7"/>
       <c t="s" r="E206" s="7">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F206" s="7">
         <v>321</v>
@@ -8325,10 +8335,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H206" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I206" s="7">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c t="s" r="J206" s="7">
         <v>174</v>
@@ -8364,7 +8374,7 @@
       </c>
       <c r="D208" s="7"/>
       <c t="s" r="E208" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F208" s="7">
         <v>321</v>
@@ -8376,7 +8386,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I208" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J208" s="7">
         <v>212</v>
@@ -8384,7 +8394,7 @@
       <c r="K208" s="7"/>
       <c r="L208" s="7"/>
       <c t="s" r="M208" s="7">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="209" ht="14.25" customHeight="1">
@@ -8399,7 +8409,7 @@
       </c>
       <c r="D209" s="7"/>
       <c t="s" r="E209" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F209" s="7">
         <v>321</v>
@@ -8419,7 +8429,7 @@
       <c r="K209" s="7"/>
       <c r="L209" s="7"/>
       <c t="s" r="M209" s="7">
-        <v>334</v>
+        <v>335</v>
       </c>
     </row>
     <row r="210" ht="15" customHeight="1">
@@ -8434,7 +8444,7 @@
       </c>
       <c r="D210" s="7"/>
       <c t="s" r="E210" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F210" s="7">
         <v>321</v>
@@ -8446,7 +8456,7 @@
         <v>17</v>
       </c>
       <c t="s" r="I210" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c t="s" r="J210" s="7">
         <v>34</v>
@@ -8454,7 +8464,7 @@
       <c r="K210" s="7"/>
       <c r="L210" s="7"/>
       <c t="s" r="M210" s="7">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="211" ht="14.25" customHeight="1">
@@ -8469,7 +8479,7 @@
       </c>
       <c r="D211" s="7"/>
       <c t="s" r="E211" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F211" s="7">
         <v>321</v>
@@ -8484,7 +8494,7 @@
         <v>225</v>
       </c>
       <c t="s" r="J211" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="K211" s="7"/>
       <c r="L211" s="7"/>
@@ -8502,7 +8512,7 @@
       </c>
       <c r="D212" s="7"/>
       <c t="s" r="E212" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F212" s="7">
         <v>321</v>
@@ -8511,13 +8521,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H212" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I212" s="7">
         <v>26</v>
       </c>
       <c t="s" r="J212" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K212" s="7"/>
       <c r="L212" s="7"/>
@@ -8535,13 +8545,13 @@
       </c>
       <c r="D213" s="7"/>
       <c t="s" r="E213" s="7">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="F213" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G213" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H213" s="8">
         <v>43</v>
@@ -8583,7 +8593,7 @@
       </c>
       <c r="D215" s="7"/>
       <c t="s" r="E215" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F215" s="7">
         <v>321</v>
@@ -8603,7 +8613,7 @@
       <c r="K215" s="7"/>
       <c r="L215" s="7"/>
       <c t="s" r="M215" s="7">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="216" ht="14.25" customHeight="1">
@@ -8618,7 +8628,7 @@
       </c>
       <c r="D216" s="7"/>
       <c t="s" r="E216" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F216" s="7">
         <v>321</v>
@@ -8636,11 +8646,11 @@
         <v>217</v>
       </c>
       <c t="s" r="K216" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="L216" s="7"/>
       <c t="s" r="M216" s="7">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="217" ht="14.25" customHeight="1">
@@ -8655,7 +8665,7 @@
       </c>
       <c r="D217" s="7"/>
       <c t="s" r="E217" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F217" s="7">
         <v>321</v>
@@ -8667,17 +8677,17 @@
         <v>177</v>
       </c>
       <c t="s" r="I217" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c t="s" r="J217" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="K217" s="7">
         <v>270</v>
       </c>
       <c r="L217" s="7"/>
       <c t="s" r="M217" s="7">
-        <v>236</v>
+        <v>105</v>
       </c>
     </row>
     <row r="218" ht="14.25" customHeight="1">
@@ -8692,7 +8702,7 @@
       </c>
       <c r="D218" s="7"/>
       <c t="s" r="E218" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F218" s="7">
         <v>321</v>
@@ -8704,10 +8714,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I218" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J218" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K218" s="7"/>
       <c r="L218" s="7"/>
@@ -8725,7 +8735,7 @@
       </c>
       <c r="D219" s="7"/>
       <c t="s" r="E219" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F219" s="7">
         <v>321</v>
@@ -8740,7 +8750,7 @@
         <v>28</v>
       </c>
       <c t="s" r="J219" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K219" s="7"/>
       <c r="L219" s="7"/>
@@ -8758,7 +8768,7 @@
       </c>
       <c r="D220" s="7"/>
       <c t="s" r="E220" s="7">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="F220" s="7">
         <v>321</v>
@@ -8770,7 +8780,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I220" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J220" s="7">
         <v>174</v>
@@ -8806,7 +8816,7 @@
       </c>
       <c r="D222" s="7"/>
       <c t="s" r="E222" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F222" s="7">
         <v>321</v>
@@ -8815,18 +8825,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H222" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="I222" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J222" s="7">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K222" s="7"/>
       <c r="L222" s="7"/>
       <c t="s" r="M222" s="7">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="223" ht="14.25" customHeight="1">
@@ -8841,29 +8851,29 @@
       </c>
       <c r="D223" s="7"/>
       <c t="s" r="E223" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F223" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G223" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="H223" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I223" s="7">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c t="s" r="J223" s="7">
         <v>232</v>
       </c>
       <c t="s" r="K223" s="7">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="L223" s="7"/>
       <c t="s" r="M223" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="224" ht="14.25" customHeight="1">
@@ -8878,7 +8888,7 @@
       </c>
       <c r="D224" s="7"/>
       <c t="s" r="E224" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F224" s="7">
         <v>321</v>
@@ -8890,15 +8900,15 @@
         <v>17</v>
       </c>
       <c t="s" r="I224" s="7">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c t="s" r="J224" s="7">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="K224" s="7"/>
       <c r="L224" s="7"/>
       <c t="s" r="M224" s="7">
-        <v>342</v>
+        <v>343</v>
       </c>
     </row>
     <row r="225" ht="15" customHeight="1">
@@ -8913,7 +8923,7 @@
       </c>
       <c r="D225" s="7"/>
       <c t="s" r="E225" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F225" s="7">
         <v>321</v>
@@ -8928,7 +8938,7 @@
         <v>165</v>
       </c>
       <c t="s" r="J225" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="K225" s="7"/>
       <c r="L225" s="7"/>
@@ -8946,7 +8956,7 @@
       </c>
       <c r="D226" s="7"/>
       <c t="s" r="E226" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F226" s="7">
         <v>321</v>
@@ -8955,13 +8965,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H226" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I226" s="7">
         <v>259</v>
       </c>
       <c t="s" r="J226" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K226" s="7"/>
       <c r="L226" s="7"/>
@@ -8979,13 +8989,13 @@
       </c>
       <c r="D227" s="7"/>
       <c t="s" r="E227" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F227" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G227" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H227" s="8">
         <v>27</v>
@@ -9012,7 +9022,7 @@
       </c>
       <c r="D228" s="7"/>
       <c t="s" r="E228" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F228" s="7">
         <v>321</v>
@@ -9021,13 +9031,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H228" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I228" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J228" s="7">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="K228" s="7"/>
       <c r="L228" s="7"/>
@@ -9045,22 +9055,22 @@
       </c>
       <c r="D229" s="7"/>
       <c t="s" r="E229" s="7">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="F229" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G229" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H229" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I229" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J229" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="K229" s="7"/>
       <c r="L229" s="7"/>
@@ -9093,7 +9103,7 @@
       </c>
       <c r="D231" s="7"/>
       <c t="s" r="E231" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F231" s="7">
         <v>321</v>
@@ -9108,12 +9118,12 @@
         <v>216</v>
       </c>
       <c t="s" r="J231" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K231" s="7"/>
       <c r="L231" s="7"/>
       <c t="s" r="M231" s="7">
-        <v>350</v>
+        <v>351</v>
       </c>
     </row>
     <row r="232" ht="14.25" customHeight="1">
@@ -9128,7 +9138,7 @@
       </c>
       <c r="D232" s="7"/>
       <c t="s" r="E232" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F232" s="7">
         <v>321</v>
@@ -9148,7 +9158,7 @@
       <c r="K232" s="7"/>
       <c r="L232" s="7"/>
       <c t="s" r="M232" s="7">
-        <v>351</v>
+        <v>352</v>
       </c>
     </row>
     <row r="233" ht="14.25" customHeight="1">
@@ -9163,7 +9173,7 @@
       </c>
       <c r="D233" s="7"/>
       <c t="s" r="E233" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F233" s="7">
         <v>321</v>
@@ -9172,13 +9182,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H233" s="8">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="I233" s="7">
         <v>259</v>
       </c>
       <c t="s" r="J233" s="7">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c r="K233" s="7"/>
       <c r="L233" s="7"/>
@@ -9196,22 +9206,22 @@
       </c>
       <c r="D234" s="7"/>
       <c t="s" r="E234" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F234" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G234" s="8">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c t="s" r="H234" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I234" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c t="s" r="J234" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K234" s="7"/>
       <c r="L234" s="7"/>
@@ -9229,7 +9239,7 @@
       </c>
       <c r="D235" s="7"/>
       <c t="s" r="E235" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F235" s="7">
         <v>321</v>
@@ -9238,13 +9248,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H235" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="I235" s="7">
         <v>208</v>
       </c>
       <c t="s" r="J235" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="K235" s="7"/>
       <c r="L235" s="7"/>
@@ -9262,22 +9272,22 @@
       </c>
       <c r="D236" s="7"/>
       <c t="s" r="E236" s="7">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="F236" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G236" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="H236" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I236" s="7">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c t="s" r="J236" s="7">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="K236" s="7"/>
       <c r="L236" s="7"/>
@@ -9310,7 +9320,7 @@
       </c>
       <c r="D238" s="7"/>
       <c t="s" r="E238" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F238" s="7">
         <v>321</v>
@@ -9319,10 +9329,10 @@
         <v>16</v>
       </c>
       <c t="s" r="H238" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I238" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J238" s="7">
         <v>184</v>
@@ -9330,7 +9340,7 @@
       <c r="K238" s="7"/>
       <c r="L238" s="7"/>
       <c t="s" r="M238" s="7">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="239" ht="14.25" customHeight="1">
@@ -9345,16 +9355,16 @@
       </c>
       <c r="D239" s="7"/>
       <c t="s" r="E239" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F239" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G239" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H239" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I239" s="7">
         <v>48</v>
@@ -9365,7 +9375,7 @@
       <c r="K239" s="7"/>
       <c r="L239" s="7"/>
       <c t="s" r="M239" s="7">
-        <v>360</v>
+        <v>361</v>
       </c>
     </row>
     <row r="240" ht="15" customHeight="1">
@@ -9380,22 +9390,22 @@
       </c>
       <c r="D240" s="7"/>
       <c t="s" r="E240" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F240" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G240" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H240" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I240" s="7">
         <v>248</v>
       </c>
       <c t="s" r="J240" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="K240" s="7"/>
       <c r="L240" s="7"/>
@@ -9413,22 +9423,22 @@
       </c>
       <c r="D241" s="7"/>
       <c t="s" r="E241" s="7">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F241" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G241" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H241" s="8">
         <v>16</v>
       </c>
       <c t="s" r="I241" s="7">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c t="s" r="J241" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="K241" s="7"/>
       <c r="L241" s="7"/>
@@ -9461,7 +9471,7 @@
       </c>
       <c r="D243" s="7"/>
       <c t="s" r="E243" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F243" s="7">
         <v>321</v>
@@ -9476,12 +9486,12 @@
         <v>19</v>
       </c>
       <c t="s" r="J243" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K243" s="7"/>
       <c r="L243" s="7"/>
       <c t="s" r="M243" s="7">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="244" ht="14.25" customHeight="1">
@@ -9496,7 +9506,7 @@
       </c>
       <c r="D244" s="7"/>
       <c t="s" r="E244" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F244" s="7">
         <v>321</v>
@@ -9529,7 +9539,7 @@
       </c>
       <c r="D245" s="7"/>
       <c t="s" r="E245" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F245" s="7">
         <v>321</v>
@@ -9541,7 +9551,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I245" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c t="s" r="J245" s="7">
         <v>261</v>
@@ -9562,7 +9572,7 @@
       </c>
       <c r="D246" s="7"/>
       <c t="s" r="E246" s="7">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F246" s="7">
         <v>321</v>
@@ -9577,7 +9587,7 @@
         <v>189</v>
       </c>
       <c t="s" r="J246" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K246" s="7"/>
       <c r="L246" s="7"/>
@@ -9610,7 +9620,7 @@
       </c>
       <c r="D248" s="7"/>
       <c t="s" r="E248" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F248" s="7">
         <v>321</v>
@@ -9619,18 +9629,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H248" s="8">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="I248" s="7">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c t="s" r="J248" s="7">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="K248" s="7"/>
       <c r="L248" s="7"/>
       <c t="s" r="M248" s="7">
-        <v>368</v>
+        <v>369</v>
       </c>
     </row>
     <row r="249" ht="14.25" customHeight="1">
@@ -9645,27 +9655,27 @@
       </c>
       <c r="D249" s="7"/>
       <c t="s" r="E249" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F249" s="7">
         <v>321</v>
       </c>
       <c t="s" r="G249" s="8">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c t="s" r="H249" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I249" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c t="s" r="J249" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K249" s="7"/>
       <c r="L249" s="7"/>
       <c t="s" r="M249" s="7">
-        <v>369</v>
+        <v>106</v>
       </c>
     </row>
     <row r="250" ht="15" customHeight="1">
@@ -9680,7 +9690,7 @@
       </c>
       <c r="D250" s="7"/>
       <c t="s" r="E250" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F250" s="7">
         <v>321</v>
@@ -9692,7 +9702,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I250" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J250" s="7">
         <v>29</v>
@@ -9713,7 +9723,7 @@
       </c>
       <c r="D251" s="7"/>
       <c t="s" r="E251" s="7">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F251" s="7">
         <v>321</v>
@@ -9725,7 +9735,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I251" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J251" s="7">
         <v>370</v>
@@ -9773,10 +9783,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I253" s="7">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c t="s" r="J253" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K253" s="7"/>
       <c r="L253" s="7"/>
@@ -9811,12 +9821,12 @@
         <v>254</v>
       </c>
       <c t="s" r="J254" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="K254" s="7"/>
       <c r="L254" s="7"/>
       <c t="s" r="M254" s="7">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="255" ht="15" customHeight="1">
@@ -9843,14 +9853,16 @@
         <v>17</v>
       </c>
       <c t="s" r="I255" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c t="s" r="J255" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K255" s="7"/>
       <c r="L255" s="7"/>
-      <c r="M255" s="7"/>
+      <c t="s" r="M255" s="7">
+        <v>374</v>
+      </c>
     </row>
     <row r="256" ht="14.25" customHeight="1">
       <c t="s" r="A256" s="6">
@@ -9912,7 +9924,7 @@
       </c>
       <c r="D258" s="7"/>
       <c t="s" r="E258" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F258" s="7">
         <v>321</v>
@@ -9924,7 +9936,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I258" s="7">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c t="s" r="J258" s="7">
         <v>187</v>
@@ -9932,7 +9944,7 @@
       <c r="K258" s="7"/>
       <c r="L258" s="7"/>
       <c t="s" r="M258" s="7">
-        <v>375</v>
+        <v>271</v>
       </c>
     </row>
     <row r="259" ht="14.25" customHeight="1">
@@ -9947,7 +9959,7 @@
       </c>
       <c r="D259" s="7"/>
       <c t="s" r="E259" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F259" s="7">
         <v>321</v>
@@ -9959,14 +9971,18 @@
         <v>177</v>
       </c>
       <c t="s" r="I259" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J259" s="7">
         <v>188</v>
       </c>
-      <c r="K259" s="7"/>
+      <c t="s" r="K259" s="7">
+        <v>90</v>
+      </c>
       <c r="L259" s="7"/>
-      <c r="M259" s="7"/>
+      <c t="s" r="M259" s="7">
+        <v>78</v>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1">
       <c t="s" r="A260" s="6">
@@ -9980,7 +9996,7 @@
       </c>
       <c r="D260" s="7"/>
       <c t="s" r="E260" s="7">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="F260" s="7">
         <v>321</v>
@@ -9995,11 +10011,15 @@
         <v>26</v>
       </c>
       <c t="s" r="J260" s="7">
-        <v>336</v>
-      </c>
-      <c r="K260" s="7"/>
+        <v>337</v>
+      </c>
+      <c t="s" r="K260" s="7">
+        <v>52</v>
+      </c>
       <c r="L260" s="7"/>
-      <c r="M260" s="7"/>
+      <c t="s" r="M260" s="7">
+        <v>53</v>
+      </c>
     </row>
     <row r="261" ht="14.25" customHeight="1">
       <c r="A261" s="6"/>
@@ -10034,7 +10054,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G262" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H262" s="8">
         <v>43</v>
@@ -10072,7 +10092,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H263" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I263" s="7">
         <v>230</v>
@@ -10104,7 +10124,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G264" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H264" s="8">
         <v>43</v>
@@ -10142,10 +10162,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H265" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I265" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c t="s" r="J265" s="7">
         <v>207</v>
@@ -10174,7 +10194,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G266" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H266" s="8">
         <v>43</v>
@@ -10212,7 +10232,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H267" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I267" s="7">
         <v>225</v>
@@ -10242,7 +10262,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G268" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H268" s="8">
         <v>37</v>
@@ -10251,7 +10271,7 @@
         <v>208</v>
       </c>
       <c t="s" r="J268" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="K268" s="7"/>
       <c r="L268" s="7"/>
@@ -10296,7 +10316,7 @@
         <v>384</v>
       </c>
       <c t="s" r="I270" s="7">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c t="s" r="J270" s="7">
         <v>379</v>
@@ -10485,7 +10505,7 @@
         <v>166</v>
       </c>
       <c t="s" r="J276" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K276" s="7"/>
       <c r="L276" s="7"/>
@@ -10517,10 +10537,10 @@
         <v>177</v>
       </c>
       <c t="s" r="I277" s="7">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c t="s" r="J277" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K277" s="7"/>
       <c r="L277" s="7"/>
@@ -10568,7 +10588,7 @@
         <v>243</v>
       </c>
       <c t="s" r="J279" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K279" s="7"/>
       <c r="L279" s="7"/>
@@ -10608,7 +10628,7 @@
       <c r="K280" s="7"/>
       <c r="L280" s="7"/>
       <c t="s" r="M280" s="7">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="281" ht="14.25" customHeight="1">
@@ -10635,7 +10655,7 @@
         <v>395</v>
       </c>
       <c t="s" r="I281" s="7">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c t="s" r="J281" s="7">
         <v>396</v>
@@ -10902,7 +10922,7 @@
         <v>408</v>
       </c>
       <c t="s" r="I290" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c t="s" r="J290" s="7">
         <v>207</v>
@@ -10972,7 +10992,7 @@
         <v>168</v>
       </c>
       <c t="s" r="I292" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J292" s="7">
         <v>405</v>
@@ -11008,7 +11028,7 @@
         <v>249</v>
       </c>
       <c t="s" r="J293" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="K293" s="7"/>
       <c r="L293" s="7"/>
@@ -11035,13 +11055,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H294" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I294" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c t="s" r="J294" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c t="s" r="K294" s="7">
         <v>410</v>
@@ -11090,15 +11110,15 @@
         <v>27</v>
       </c>
       <c t="s" r="I296" s="7">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c t="s" r="J296" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="K296" s="7"/>
       <c r="L296" s="7"/>
       <c t="s" r="M296" s="7">
-        <v>149</v>
+        <v>150</v>
       </c>
     </row>
     <row r="297" ht="14.25" customHeight="1">
@@ -11133,7 +11153,7 @@
       <c r="K297" s="7"/>
       <c r="L297" s="7"/>
       <c t="s" r="M297" s="7">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="298" ht="14.25" customHeight="1">
@@ -11163,7 +11183,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J298" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K298" s="7"/>
       <c r="L298" s="7"/>
@@ -11192,7 +11212,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H299" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="I299" s="7">
         <v>166</v>
@@ -11201,7 +11221,7 @@
         <v>46</v>
       </c>
       <c t="s" r="K299" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="L299" s="7"/>
       <c t="s" r="M299" s="7">
@@ -11226,7 +11246,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G300" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="H300" s="8">
         <v>27</v>
@@ -11242,7 +11262,7 @@
       </c>
       <c r="L300" s="7"/>
       <c t="s" r="M300" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="301" ht="14.25" customHeight="1">
@@ -11266,10 +11286,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H301" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="I301" s="7">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c t="s" r="J301" s="7">
         <v>414</v>
@@ -11296,7 +11316,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G302" s="8">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c t="s" r="H302" s="8">
         <v>27</v>
@@ -11350,10 +11370,10 @@
         <v>417</v>
       </c>
       <c t="s" r="I304" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J304" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K304" s="7"/>
       <c r="L304" s="7"/>
@@ -11417,13 +11437,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H306" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="I306" s="7">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c t="s" r="J306" s="7">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K306" s="7"/>
       <c r="L306" s="7"/>
@@ -11447,13 +11467,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G307" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="H307" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I307" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J307" s="7">
         <v>221</v>
@@ -11567,7 +11587,7 @@
         <v>425</v>
       </c>
       <c t="s" r="I311" s="7">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c t="s" r="J311" s="7">
         <v>193</v>
@@ -11602,7 +11622,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I312" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c t="s" r="J312" s="7">
         <v>244</v>
@@ -11634,13 +11654,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H313" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I313" s="7">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c t="s" r="J313" s="7">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="K313" s="7"/>
       <c r="L313" s="7"/>
@@ -11666,7 +11686,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G314" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H314" s="8">
         <v>27</v>
@@ -11710,10 +11730,10 @@
         <v>381</v>
       </c>
       <c t="s" r="J315" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="K315" s="7">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="L315" s="7"/>
       <c t="s" r="M315" s="7">
@@ -11750,7 +11770,7 @@
         <v>202</v>
       </c>
       <c t="s" r="K316" s="7">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="L316" s="7"/>
       <c t="s" r="M316" s="7">
@@ -11778,13 +11798,13 @@
         <v>27</v>
       </c>
       <c t="s" r="H317" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="I317" s="7">
         <v>429</v>
       </c>
       <c t="s" r="J317" s="7">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K317" s="7"/>
       <c r="L317" s="7"/>
@@ -11808,13 +11828,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G318" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="H318" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I318" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c t="s" r="J318" s="7">
         <v>430</v>
@@ -11862,17 +11882,17 @@
         <v>27</v>
       </c>
       <c t="s" r="I320" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c t="s" r="J320" s="7">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c t="s" r="K320" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="L320" s="7"/>
       <c t="s" r="M320" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="321" ht="14.25" customHeight="1">
@@ -11896,18 +11916,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H321" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="I321" s="7">
         <v>217</v>
       </c>
       <c t="s" r="J321" s="7">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="K321" s="7"/>
       <c r="L321" s="7"/>
       <c t="s" r="M321" s="7">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="322" ht="14.25" customHeight="1">
@@ -11928,16 +11948,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G322" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="H322" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I322" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c t="s" r="J322" s="7">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="K322" s="7"/>
       <c r="L322" s="7"/>
@@ -11967,7 +11987,7 @@
         <v>420</v>
       </c>
       <c t="s" r="I323" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c t="s" r="J323" s="7">
         <v>388</v>
@@ -12000,7 +12020,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I324" s="7">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c t="s" r="J324" s="7">
         <v>175</v>
@@ -12051,7 +12071,7 @@
         <v>232</v>
       </c>
       <c t="s" r="J326" s="7">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K326" s="7"/>
       <c r="L326" s="7"/>
@@ -12083,10 +12103,10 @@
         <v>435</v>
       </c>
       <c t="s" r="I327" s="7">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c t="s" r="J327" s="7">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="K327" s="7"/>
       <c r="L327" s="7"/>
@@ -12116,10 +12136,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I328" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J328" s="7">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="K328" s="7"/>
       <c r="L328" s="7"/>
@@ -12196,10 +12216,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H331" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="I331" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c t="s" r="J331" s="7">
         <v>187</v>
@@ -12228,16 +12248,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G332" s="8">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c t="s" r="H332" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I332" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c t="s" r="J332" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="K332" s="7"/>
       <c r="L332" s="7"/>
@@ -12267,10 +12287,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I333" s="7">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c t="s" r="J333" s="7">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K333" s="7"/>
       <c r="L333" s="7"/>
@@ -12297,10 +12317,10 @@
         <v>27</v>
       </c>
       <c t="s" r="H334" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="I334" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J334" s="7">
         <v>438</v>
@@ -12327,7 +12347,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G335" s="8">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c t="s" r="H335" s="8">
         <v>27</v>
@@ -12381,7 +12401,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I337" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J337" s="7">
         <v>178</v>
@@ -12413,13 +12433,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H338" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="I338" s="7">
         <v>443</v>
       </c>
       <c t="s" r="J338" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K338" s="7"/>
       <c r="L338" s="7"/>
@@ -12445,13 +12465,13 @@
         <v>321</v>
       </c>
       <c t="s" r="G339" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c t="s" r="H339" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I339" s="7">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c t="s" r="J339" s="7">
         <v>36</v>
@@ -12486,10 +12506,10 @@
         <v>446</v>
       </c>
       <c t="s" r="I340" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J340" s="7">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="K340" s="7"/>
       <c r="L340" s="7"/>
@@ -12564,13 +12584,13 @@
         <v>43</v>
       </c>
       <c t="s" r="H343" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I343" s="7">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c t="s" r="J343" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K343" s="7"/>
       <c r="L343" s="7"/>
@@ -12596,13 +12616,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G344" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H344" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I344" s="7">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c t="s" r="J344" s="7">
         <v>215</v>
@@ -12631,21 +12651,21 @@
         <v>320</v>
       </c>
       <c t="s" r="G345" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H345" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="I345" s="7">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c t="s" r="J345" s="7">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="K345" s="7"/>
       <c r="L345" s="7"/>
       <c t="s" r="M345" s="7">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="346" ht="14.25" customHeight="1">
@@ -12666,7 +12686,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G346" s="8">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c t="s" r="H346" s="8">
         <v>43</v>
@@ -12740,10 +12760,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I348" s="7">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c t="s" r="J348" s="7">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="K348" s="7"/>
       <c r="L348" s="7"/>
@@ -12770,10 +12790,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H349" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I349" s="7">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c t="s" r="J349" s="7">
         <v>370</v>
@@ -12800,13 +12820,13 @@
         <v>320</v>
       </c>
       <c t="s" r="G350" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H350" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I350" s="7">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c t="s" r="J350" s="7">
         <v>452</v>
@@ -12924,7 +12944,7 @@
         <v>456</v>
       </c>
       <c t="s" r="I354" s="7">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c t="s" r="J354" s="7">
         <v>457</v>
@@ -12957,7 +12977,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I355" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c t="s" r="J355" s="7">
         <v>458</v>
@@ -12999,7 +13019,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G357" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H357" s="8">
         <v>17</v>
@@ -13008,7 +13028,7 @@
         <v>217</v>
       </c>
       <c t="s" r="J357" s="7">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K357" s="7"/>
       <c r="L357" s="7"/>
@@ -13037,13 +13057,13 @@
         <v>17</v>
       </c>
       <c t="s" r="H358" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="I358" s="7">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c t="s" r="J358" s="7">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K358" s="7"/>
       <c r="L358" s="7"/>
@@ -13067,16 +13087,16 @@
         <v>321</v>
       </c>
       <c t="s" r="G359" s="8">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c t="s" r="H359" s="8">
         <v>43</v>
       </c>
       <c t="s" r="I359" s="7">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c t="s" r="J359" s="7">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="K359" s="7"/>
       <c r="L359" s="7"/>
@@ -13121,10 +13141,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I361" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c t="s" r="J361" s="7">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K361" s="7"/>
       <c r="L361" s="7"/>
@@ -13164,7 +13184,7 @@
       <c r="K362" s="7"/>
       <c r="L362" s="7"/>
       <c t="s" r="M362" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
     </row>
     <row r="363" ht="14.25" customHeight="1">
@@ -13194,7 +13214,7 @@
         <v>260</v>
       </c>
       <c t="s" r="J363" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K363" s="7"/>
       <c r="L363" s="7"/>
@@ -13304,10 +13324,10 @@
         <v>177</v>
       </c>
       <c t="s" r="H367" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="I367" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c t="s" r="J367" s="7">
         <v>169</v>
@@ -13336,7 +13356,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G368" s="8">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c t="s" r="H368" s="8">
         <v>177</v>
@@ -13345,7 +13365,7 @@
         <v>260</v>
       </c>
       <c t="s" r="J368" s="7">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="K368" s="7"/>
       <c r="L368" s="7"/>
@@ -13426,7 +13446,7 @@
         <v>18</v>
       </c>
       <c t="s" r="J371" s="7">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="K371" s="7"/>
       <c r="L371" s="7"/>
@@ -13461,7 +13481,7 @@
         <v>185</v>
       </c>
       <c t="s" r="J372" s="7">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="K372" s="7"/>
       <c r="L372" s="7"/>
@@ -13490,7 +13510,7 @@
         <v>43</v>
       </c>
       <c t="s" r="H373" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="I373" s="7">
         <v>219</v>
@@ -13520,7 +13540,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G374" s="8">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c t="s" r="H374" s="8">
         <v>43</v>
@@ -13559,10 +13579,10 @@
         <v>177</v>
       </c>
       <c t="s" r="I375" s="7">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c t="s" r="J375" s="7">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="K375" s="7"/>
       <c r="L375" s="7"/>
@@ -13592,10 +13612,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I376" s="7">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c t="s" r="J376" s="7">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="K376" s="7"/>
       <c r="L376" s="7"/>
@@ -13628,7 +13648,7 @@
         <v>469</v>
       </c>
       <c t="s" r="J377" s="7">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="K377" s="7"/>
       <c r="L377" s="7"/>
@@ -13670,7 +13690,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H379" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="I379" s="7">
         <v>212</v>
@@ -13702,7 +13722,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G380" s="8">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c t="s" r="H380" s="8">
         <v>27</v>
@@ -13743,10 +13763,10 @@
         <v>183</v>
       </c>
       <c t="s" r="I381" s="7">
-        <v>159</v>
+        <v>50</v>
       </c>
       <c t="s" r="J381" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K381" s="7"/>
       <c r="L381" s="7"/>
@@ -13778,7 +13798,7 @@
         <v>27</v>
       </c>
       <c t="s" r="I382" s="7">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c t="s" r="J382" s="7">
         <v>173</v>
@@ -13893,10 +13913,10 @@
         <v>43</v>
       </c>
       <c t="s" r="H386" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="I386" s="7">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c t="s" r="J386" s="7">
         <v>200</v>
@@ -13925,7 +13945,7 @@
         <v>320</v>
       </c>
       <c t="s" r="G387" s="8">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c t="s" r="H387" s="8">
         <v>43</v>
@@ -13967,7 +13987,7 @@
         <v>260</v>
       </c>
       <c t="s" r="J388" s="7">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="K388" s="7"/>
       <c r="L388" s="7"/>
@@ -14042,18 +14062,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H391" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I391" s="7">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c t="s" r="J391" s="7">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="K391" s="7"/>
       <c r="L391" s="7"/>
       <c t="s" r="M391" s="7">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="392" ht="14.25" customHeight="1">
@@ -14074,7 +14094,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G392" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H392" s="8">
         <v>168</v>
@@ -14112,13 +14132,13 @@
         <v>168</v>
       </c>
       <c t="s" r="H393" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="I393" s="7">
         <v>196</v>
       </c>
       <c t="s" r="J393" s="7">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="K393" s="7"/>
       <c r="L393" s="7"/>
@@ -14144,7 +14164,7 @@
         <v>321</v>
       </c>
       <c t="s" r="G394" s="8">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c t="s" r="H394" s="8">
         <v>27</v>
@@ -14153,7 +14173,7 @@
         <v>478</v>
       </c>
       <c t="s" r="J394" s="7">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="K394" s="7"/>
       <c r="L394" s="7"/>
@@ -14183,7 +14203,7 @@
         <v>479</v>
       </c>
       <c t="s" r="I395" s="7">
-        <v>480</v>
+        <v>272</v>
       </c>
       <c t="s" r="J395" s="7">
         <v>162</v>
@@ -14216,10 +14236,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I396" s="7">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c t="s" r="J396" s="7">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="K396" s="7"/>
       <c r="L396" s="7"/>
@@ -14252,7 +14272,7 @@
       </c>
       <c r="D398" s="7"/>
       <c t="s" r="E398" s="7">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F398" s="7">
         <v>330</v>
@@ -14264,10 +14284,10 @@
         <v>27</v>
       </c>
       <c t="s" r="I398" s="7">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c t="s" r="J398" s="7">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K398" s="7"/>
       <c r="L398" s="7"/>
@@ -14287,7 +14307,7 @@
       </c>
       <c r="D399" s="7"/>
       <c t="s" r="E399" s="7">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="F399" s="7">
         <v>330</v>
@@ -14299,7 +14319,7 @@
         <v>43</v>
       </c>
       <c t="s" r="I399" s="7">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c t="s" r="J399" s="7">
         <v>33</v>
@@ -14307,7 +14327,7 @@
       <c r="K399" s="7"/>
       <c r="L399" s="7"/>
       <c t="s" r="M399" s="7">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="400" ht="15" customHeight="1">
@@ -14337,7 +14357,7 @@
       </c>
       <c r="D401" s="7"/>
       <c t="s" r="E401" s="7">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F401" s="7">
         <v>330</v>
@@ -14346,18 +14366,18 @@
         <v>177</v>
       </c>
       <c t="s" r="H401" s="8">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c t="s" r="I401" s="7">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c t="s" r="J401" s="7">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="K401" s="7"/>
       <c r="L401" s="7"/>
       <c t="s" r="M401" s="7">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="402" ht="14.25" customHeight="1">
@@ -14372,19 +14392,19 @@
       </c>
       <c r="D402" s="7"/>
       <c t="s" r="E402" s="7">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F402" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G402" s="8">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c t="s" r="H402" s="8">
         <v>177</v>
       </c>
       <c t="s" r="I402" s="7">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c t="s" r="J402" s="7">
         <v>193</v>
@@ -14420,19 +14440,19 @@
       </c>
       <c r="D404" s="7"/>
       <c t="s" r="E404" s="7">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F404" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G404" s="8">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c t="s" r="H404" s="8">
         <v>27</v>
       </c>
       <c t="s" r="I404" s="7">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c t="s" r="J404" s="7">
         <v>25</v>
@@ -14440,7 +14460,7 @@
       <c r="K404" s="7"/>
       <c r="L404" s="7"/>
       <c t="s" r="M404" s="7">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="405" ht="15" customHeight="1">
@@ -14455,7 +14475,7 @@
       </c>
       <c r="D405" s="7"/>
       <c t="s" r="E405" s="7">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="F405" s="7">
         <v>330</v>
@@ -14464,7 +14484,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H405" s="8">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c t="s" r="I405" s="7">
         <v>203</v>
@@ -14499,11 +14519,11 @@
         <v>611</v>
       </c>
       <c t="s" r="C407" s="7">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D407" s="7"/>
       <c t="s" r="E407" s="7">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F407" s="7">
         <v>330</v>
@@ -14518,12 +14538,12 @@
         <v>243</v>
       </c>
       <c t="s" r="J407" s="7">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="K407" s="7"/>
       <c r="L407" s="7"/>
       <c t="s" r="M407" s="7">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="408" ht="14.25" customHeight="1">
@@ -14538,7 +14558,7 @@
       </c>
       <c r="D408" s="7"/>
       <c t="s" r="E408" s="7">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F408" s="7">
         <v>330</v>
@@ -14547,7 +14567,7 @@
         <v>27</v>
       </c>
       <c t="s" r="H408" s="8">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c t="s" r="I408" s="7">
         <v>19</v>
@@ -14558,7 +14578,7 @@
       <c r="K408" s="7"/>
       <c r="L408" s="7"/>
       <c t="s" r="M408" s="7">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="409" ht="14.25" customHeight="1">
@@ -14573,13 +14593,13 @@
       </c>
       <c r="D409" s="7"/>
       <c t="s" r="E409" s="7">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F409" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G409" s="8">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c t="s" r="H409" s="8">
         <v>27</v>
@@ -14621,7 +14641,7 @@
       </c>
       <c r="D411" s="7"/>
       <c t="s" r="E411" s="7">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F411" s="7">
         <v>330</v>
@@ -14630,13 +14650,13 @@
         <v>177</v>
       </c>
       <c t="s" r="H411" s="8">
+        <v>496</v>
+      </c>
+      <c t="s" r="I411" s="7">
         <v>497</v>
       </c>
-      <c t="s" r="I411" s="7">
-        <v>498</v>
-      </c>
       <c t="s" r="J411" s="7">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="K411" s="7"/>
       <c r="L411" s="7"/>
@@ -14656,19 +14676,19 @@
       </c>
       <c r="D412" s="7"/>
       <c t="s" r="E412" s="7">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F412" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G412" s="8">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c t="s" r="H412" s="8">
         <v>177</v>
       </c>
       <c t="s" r="I412" s="7">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c t="s" r="J412" s="7">
         <v>209</v>
@@ -14704,7 +14724,7 @@
       </c>
       <c r="D414" s="7"/>
       <c t="s" r="E414" s="7">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F414" s="7">
         <v>330</v>
@@ -14713,18 +14733,18 @@
         <v>27</v>
       </c>
       <c t="s" r="H414" s="8">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c t="s" r="I414" s="7">
         <v>216</v>
       </c>
       <c t="s" r="J414" s="7">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K414" s="7"/>
       <c r="L414" s="7"/>
       <c t="s" r="M414" s="7">
-        <v>79</v>
+        <v>500</v>
       </c>
     </row>
     <row r="415" ht="15" customHeight="1">
@@ -14739,13 +14759,13 @@
       </c>
       <c r="D415" s="7"/>
       <c t="s" r="E415" s="7">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F415" s="7">
         <v>330</v>
       </c>
       <c t="s" r="G415" s="8">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c t="s" r="H415" s="8">
         <v>27</v>
@@ -14802,7 +14822,7 @@
         <v>504</v>
       </c>
       <c t="s" r="J417" s="7">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="K417" s="7"/>
       <c r="L417" s="7"/>
@@ -14834,10 +14854,10 @@
         <v>17</v>
       </c>
       <c t="s" r="I418" s="7">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c t="s" r="J418" s="7">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K418" s="7"/>
       <c r="L418" s="7"/>
@@ -14882,10 +14902,10 @@
         <v>43</v>
       </c>
       <c t="s" r="I420" s="7">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c t="s" r="J420" s="7">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="K420" s="7"/>
       <c r="L420" s="7"/>
@@ -14918,7 +14938,7 @@
         <v>188</v>
       </c>
       <c t="s" r="J421" s="7">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="K421" s="7"/>
       <c r="L421" s="7"/>
